--- a/AAII_Financials/Quarterly/EPAC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/EPAC_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="92">
   <si>
     <t>EPAC</t>
   </si>
@@ -656,340 +656,352 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Z102"/>
+  <dimension ref="A5:AA102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45260</v>
+      </c>
+      <c r="E7" s="2">
         <v>45169</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45077</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44985</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44895</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44804</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44712</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44620</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44530</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44439</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44347</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44255</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44165</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44074</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>43982</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43890</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43799</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43708</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43616</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43524</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43434</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43343</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43251</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43159</v>
       </c>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>142000</v>
+      </c>
+      <c r="E8" s="3">
         <v>160600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>156300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>142000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>139400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>151800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>151900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>136600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>130900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>145400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>143100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>120700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>119400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>111400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>101900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>133400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>146700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>654800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>178100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>159800</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>158600</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>641300</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>317100</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>275200</v>
       </c>
     </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>81700</v>
+        <v>67600</v>
       </c>
       <c r="E9" s="3">
-        <v>78400</v>
+        <v>80800</v>
       </c>
       <c r="F9" s="3">
-        <v>71600</v>
+        <v>78000</v>
       </c>
       <c r="G9" s="3">
+        <v>71400</v>
+      </c>
+      <c r="H9" s="3">
         <v>71500</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>78100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>79800</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>76600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>71300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>79200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>76300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>65900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>64200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>66900</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>59900</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>71300</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>78000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>362100</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>96100</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>88500</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>88200</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>358000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>200600</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>185500</v>
       </c>
     </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>78900</v>
+        <v>74400</v>
       </c>
       <c r="E10" s="3">
-        <v>77900</v>
+        <v>79800</v>
       </c>
       <c r="F10" s="3">
+        <v>78300</v>
+      </c>
+      <c r="G10" s="3">
+        <v>70600</v>
+      </c>
+      <c r="H10" s="3">
+        <v>67900</v>
+      </c>
+      <c r="I10" s="3">
+        <v>73700</v>
+      </c>
+      <c r="J10" s="3">
+        <v>72100</v>
+      </c>
+      <c r="K10" s="3">
+        <v>60000</v>
+      </c>
+      <c r="L10" s="3">
+        <v>59600</v>
+      </c>
+      <c r="M10" s="3">
+        <v>66200</v>
+      </c>
+      <c r="N10" s="3">
+        <v>66800</v>
+      </c>
+      <c r="O10" s="3">
+        <v>54800</v>
+      </c>
+      <c r="P10" s="3">
+        <v>55200</v>
+      </c>
+      <c r="Q10" s="3">
+        <v>44500</v>
+      </c>
+      <c r="R10" s="3">
+        <v>42000</v>
+      </c>
+      <c r="S10" s="3">
+        <v>62100</v>
+      </c>
+      <c r="T10" s="3">
+        <v>68700</v>
+      </c>
+      <c r="U10" s="3">
+        <v>292700</v>
+      </c>
+      <c r="V10" s="3">
+        <v>82000</v>
+      </c>
+      <c r="W10" s="3">
+        <v>71300</v>
+      </c>
+      <c r="X10" s="3">
         <v>70400</v>
       </c>
-      <c r="G10" s="3">
-        <v>67900</v>
-      </c>
-      <c r="H10" s="3">
-        <v>73700</v>
-      </c>
-      <c r="I10" s="3">
-        <v>72100</v>
-      </c>
-      <c r="J10" s="3">
-        <v>60000</v>
-      </c>
-      <c r="K10" s="3">
-        <v>59600</v>
-      </c>
-      <c r="L10" s="3">
-        <v>66200</v>
-      </c>
-      <c r="M10" s="3">
-        <v>66800</v>
-      </c>
-      <c r="N10" s="3">
-        <v>54800</v>
-      </c>
-      <c r="O10" s="3">
-        <v>55200</v>
-      </c>
-      <c r="P10" s="3">
-        <v>44500</v>
-      </c>
-      <c r="Q10" s="3">
-        <v>42000</v>
-      </c>
-      <c r="R10" s="3">
-        <v>62100</v>
-      </c>
-      <c r="S10" s="3">
-        <v>68700</v>
-      </c>
-      <c r="T10" s="3">
-        <v>292700</v>
-      </c>
-      <c r="U10" s="3">
-        <v>82000</v>
-      </c>
-      <c r="V10" s="3">
-        <v>71300</v>
-      </c>
-      <c r="W10" s="3">
-        <v>70400</v>
-      </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>283300</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>116500</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>89700</v>
       </c>
     </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1016,8 +1028,9 @@
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA11" s="3"/>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1090,8 +1103,11 @@
       <c r="Z12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1164,114 +1180,120 @@
       <c r="Z13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>-5300</v>
+        <v>3700</v>
       </c>
       <c r="E14" s="3">
-        <v>2300</v>
+        <v>4000</v>
       </c>
       <c r="F14" s="3">
-        <v>3000</v>
+        <v>8200</v>
       </c>
       <c r="G14" s="3">
+        <v>14400</v>
+      </c>
+      <c r="H14" s="3">
+        <v>10400</v>
+      </c>
+      <c r="I14" s="3">
+        <v>4300</v>
+      </c>
+      <c r="J14" s="3">
+        <v>500</v>
+      </c>
+      <c r="K14" s="3">
+        <v>2900</v>
+      </c>
+      <c r="L14" s="3">
+        <v>2700</v>
+      </c>
+      <c r="M14" s="3">
+        <v>5600</v>
+      </c>
+      <c r="N14" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="O14" s="3">
+        <v>1100</v>
+      </c>
+      <c r="P14" s="3">
+        <v>300</v>
+      </c>
+      <c r="Q14" s="3">
+        <v>1400</v>
+      </c>
+      <c r="R14" s="3">
         <v>1000</v>
       </c>
-      <c r="H14" s="3">
-        <v>4300</v>
-      </c>
-      <c r="I14" s="3">
-        <v>500</v>
-      </c>
-      <c r="J14" s="3">
-        <v>2900</v>
-      </c>
-      <c r="K14" s="3">
-        <v>2700</v>
-      </c>
-      <c r="L14" s="3">
-        <v>5600</v>
-      </c>
-      <c r="M14" s="3">
-        <v>-3800</v>
-      </c>
-      <c r="N14" s="3">
-        <v>1100</v>
-      </c>
-      <c r="O14" s="3">
-        <v>300</v>
-      </c>
-      <c r="P14" s="3">
-        <v>1400</v>
-      </c>
-      <c r="Q14" s="3">
-        <v>1000</v>
-      </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>1200</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>600</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>27000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>-11900</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>3600</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>23400</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>13500</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>1200</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>6400</v>
       </c>
     </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>800</v>
+      </c>
+      <c r="E15" s="3">
         <v>1000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>1400</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>1300</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>1400</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>1600</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>1800</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>1900</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>2000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>1800</v>
-      </c>
-      <c r="M15" s="3">
-        <v>2100</v>
       </c>
       <c r="N15" s="3">
         <v>2100</v>
@@ -1280,40 +1302,43 @@
         <v>2100</v>
       </c>
       <c r="P15" s="3">
-        <v>2200</v>
+        <v>2100</v>
       </c>
       <c r="Q15" s="3">
         <v>2200</v>
       </c>
       <c r="R15" s="3">
+        <v>2200</v>
+      </c>
+      <c r="S15" s="3">
         <v>2100</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>1900</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>8900</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>2800</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>1900</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>2300</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>9300</v>
-      </c>
-      <c r="Y15" s="3">
-        <v>5200</v>
       </c>
       <c r="Z15" s="3">
         <v>5200</v>
       </c>
-    </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA15" s="3">
+        <v>5200</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1337,156 +1362,163 @@
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
-    </row>
-    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA16" s="3"/>
+    </row>
+    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>113300</v>
+      </c>
+      <c r="E17" s="3">
         <v>128400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>130800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>128000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>127100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>138700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>145300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>132100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>124500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>131800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>120400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>114900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>110400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>108100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>103900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>124800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>132300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>607200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>139900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>147300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>167100</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>591100</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>284400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>265400</v>
       </c>
     </row>
-    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>28700</v>
+      </c>
+      <c r="E18" s="3">
         <v>32200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>25500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>14000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>12300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>13100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>6600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>4500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>6400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>13600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>22700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>5800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>9000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>3300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-2000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>8600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>14400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>47600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>38200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>12500</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-8500</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>50200</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>32700</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>9800</v>
       </c>
     </row>
-    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1513,156 +1545,163 @@
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
-    </row>
-    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA19" s="3"/>
+    </row>
+    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="E20" s="3">
         <v>-3900</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-3800</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-3900</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-3500</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-3000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-1200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-1000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-1400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-1100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-1800</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-2200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-2000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-2200</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-3400</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-3900</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-7100</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-28800</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-6400</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-7700</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-7900</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-31000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-7700</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-8200</v>
       </c>
     </row>
-    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>27400</v>
+      </c>
+      <c r="E21" s="3">
         <v>32100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>25700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>14400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>13000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>14700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>10300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>8400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>10100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>17600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>26300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>9100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>12500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>6500</v>
       </c>
-      <c r="Q21" s="3">
-        <v>0</v>
-      </c>
       <c r="R21" s="3">
+        <v>0</v>
+      </c>
+      <c r="S21" s="3">
         <v>10000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>12100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>38900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>41100</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>16100</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-11300</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>39600</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>35400</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>11900</v>
       </c>
     </row>
-    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1735,156 +1774,165 @@
       <c r="Z22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>24000</v>
+      </c>
+      <c r="E23" s="3">
         <v>28300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>21700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>10100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>8800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>10100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>5400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>3500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>5000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>12400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>20900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>3600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>7100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-5300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>4700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>7300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>18700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>31800</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>4800</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-16400</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>19200</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>25000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>5700</v>
+      </c>
+      <c r="E24" s="3">
         <v>5200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>4700</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>3000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>2400</v>
       </c>
-      <c r="H24" s="3">
-        <v>-2100</v>
-      </c>
       <c r="I24" s="3">
+        <v>-100</v>
+      </c>
+      <c r="J24" s="3">
         <v>1400</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>1300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>1800</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-4400</v>
       </c>
-      <c r="N24" s="3">
-        <v>0</v>
-      </c>
       <c r="O24" s="3">
+        <v>0</v>
+      </c>
+      <c r="P24" s="3">
         <v>2300</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>3900</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>800</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>1000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>16500</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>5000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>4000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>100</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>14500</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-4000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>19800</v>
       </c>
     </row>
-    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1957,156 +2005,165 @@
       <c r="Z25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>18300</v>
+      </c>
+      <c r="E26" s="3">
         <v>23100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>17000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>7200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>6400</v>
       </c>
-      <c r="H26" s="3">
-        <v>12200</v>
-      </c>
       <c r="I26" s="3">
+        <v>10200</v>
+      </c>
+      <c r="J26" s="3">
         <v>4100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>2100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>3200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>12500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>25300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>3600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>4800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-2800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-4900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>3900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>6400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>2300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>26900</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-16400</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>4700</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>29000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-18200</v>
       </c>
     </row>
-    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>18300</v>
+      </c>
+      <c r="E27" s="3">
         <v>23100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>17000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>7200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>6400</v>
       </c>
-      <c r="H27" s="3">
-        <v>12200</v>
-      </c>
       <c r="I27" s="3">
+        <v>10200</v>
+      </c>
+      <c r="J27" s="3">
         <v>4100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>2100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>3200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>12500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>25300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>3600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>4800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-2800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-4900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>3900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>6400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>2300</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>26900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>800</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-16400</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>4700</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>29000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-18200</v>
       </c>
     </row>
-    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2179,82 +2236,88 @@
       <c r="Z28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E29" s="3">
         <v>-900</v>
       </c>
-      <c r="E29" s="3">
+      <c r="F29" s="3">
         <v>-4600</v>
       </c>
-      <c r="F29" s="3">
+      <c r="G29" s="3">
         <v>-2700</v>
       </c>
-      <c r="G29" s="3">
+      <c r="H29" s="3">
         <v>1000</v>
       </c>
-      <c r="H29" s="3">
-        <v>-2200</v>
-      </c>
       <c r="I29" s="3">
+        <v>-200</v>
+      </c>
+      <c r="J29" s="3">
         <v>-2400</v>
       </c>
-      <c r="J29" s="3">
+      <c r="K29" s="3">
         <v>-900</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>-400</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>-7300</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>-200</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>-400</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>-200</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>4200</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>-100</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <v>-1800</v>
       </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
         <v>-4300</v>
       </c>
-      <c r="T29" s="3">
+      <c r="U29" s="3">
         <v>-251400</v>
       </c>
-      <c r="U29" s="3">
+      <c r="V29" s="3">
         <v>5600</v>
       </c>
-      <c r="V29" s="3">
+      <c r="W29" s="3">
         <v>2000</v>
       </c>
-      <c r="W29" s="3">
+      <c r="X29" s="3">
         <v>-1000</v>
       </c>
-      <c r="X29" s="3">
+      <c r="Y29" s="3">
         <v>-31400</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Z29" s="3">
         <v>12900</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="AA29" s="3">
         <v>-8400</v>
       </c>
     </row>
-    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2327,8 +2390,11 @@
       <c r="Z30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2401,156 +2467,165 @@
       <c r="Z31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>4700</v>
+      </c>
+      <c r="E32" s="3">
         <v>3900</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>3800</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>3900</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>3500</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>3000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>1200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>1000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>1400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>1100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>1800</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>2200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>2000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>2200</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>3400</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>3900</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>7100</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>28800</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>6400</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>7700</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>7900</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>31000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>7700</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>8200</v>
       </c>
     </row>
-    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>17700</v>
+      </c>
+      <c r="E33" s="3">
         <v>22200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>12400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>4500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>7500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>10000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>1600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>2800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>5300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>25000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>3200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>4600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>1400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-5000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>2200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>2100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-249100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>32400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>2800</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-17500</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-26600</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>41900</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-26600</v>
       </c>
     </row>
-    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2623,161 +2698,170 @@
       <c r="Z34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>17700</v>
+      </c>
+      <c r="E35" s="3">
         <v>22200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>12400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>4500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>7500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>10000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>1600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>2800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>5300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>25000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>3200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>4600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>1400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-5000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>2200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>2100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-249100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>32400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>2800</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-17500</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-26600</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>41900</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-26600</v>
       </c>
     </row>
-    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45260</v>
+      </c>
+      <c r="E38" s="2">
         <v>45169</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45077</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44985</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44895</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44804</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44712</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44620</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44530</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44439</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44347</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44255</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44165</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44074</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>43982</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43890</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43799</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43708</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43616</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43524</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43434</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43343</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43251</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43159</v>
       </c>
     </row>
-    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2804,8 +2888,9 @@
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
-    </row>
-    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA39" s="3"/>
+    </row>
+    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2832,82 +2917,86 @@
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
-    </row>
-    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA40" s="3"/>
+    </row>
+    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>148000</v>
+      </c>
+      <c r="E41" s="3">
         <v>154400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>142000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>124700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>129200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>120700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>123700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>133400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>126500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>140400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>136300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>115300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>158600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>152200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>163600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>163400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>206800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>211200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>201300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>170400</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>203400</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>250500</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>189500</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>153600</v>
       </c>
     </row>
-    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2980,304 +3069,319 @@
       <c r="Z42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>101400</v>
+      </c>
+      <c r="E43" s="3">
         <v>101600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>106600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>101800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>99100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>109100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>120800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>116400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>114700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>111800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>119600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>102700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>95600</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>90300</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>98400</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>118500</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>127000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>125900</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>202800</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>210200</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>191200</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>123300</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>212300</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>210700</v>
       </c>
     </row>
-    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>80100</v>
+      </c>
+      <c r="E44" s="3">
         <v>74800</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>93000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>94200</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>90700</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>83700</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>86900</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>89500</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>83600</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>75300</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>74700</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>71800</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>70700</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>69200</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>78900</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>78000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>79500</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>77200</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>167600</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>161600</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>154800</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>72000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>167300</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>166200</v>
       </c>
     </row>
-    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>30500</v>
+      </c>
+      <c r="E45" s="3">
         <v>24800</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>31800</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>34600</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>33700</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>28900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>34900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>34700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>36200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>30000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>41200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>35700</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>32900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>29500</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>39000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>38200</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>39500</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>316100</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>44500</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>111000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>157900</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>625000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>58700</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>60600</v>
       </c>
     </row>
-    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>360000</v>
+      </c>
+      <c r="E46" s="3">
         <v>355600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>373400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>355300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>352700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>342400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>366300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>374100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>361100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>357400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>371800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>325400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>357800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>341100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>379800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>398200</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>452700</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>730300</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>616200</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>653200</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>707300</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>1047200</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>627800</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>591000</v>
       </c>
     </row>
-    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3350,156 +3454,165 @@
       <c r="Z47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>38000</v>
+      </c>
+      <c r="E48" s="3">
         <v>76700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>41800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>41200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>41800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>84600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>44400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>46500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>47700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>100200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>50100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>61300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>60200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>110100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>111600</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>116600</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>111700</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>56700</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>90000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>83100</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>79200</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>145200</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>100800</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>102400</v>
       </c>
     </row>
-    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>303800</v>
+        <v>304300</v>
       </c>
       <c r="E49" s="3">
         <v>303800</v>
       </c>
       <c r="F49" s="3">
+        <v>303800</v>
+      </c>
+      <c r="G49" s="3">
         <v>301900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>302700</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>299500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>312400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>322000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>324700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>332100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>344600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>343700</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>341100</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>343500</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>334000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>338300</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>315200</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>312800</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>649700</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>630200</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>630100</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>351800</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>749000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>762500</v>
       </c>
     </row>
-    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3572,8 +3685,11 @@
       <c r="Z50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3646,82 +3762,88 @@
       <c r="Z51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>63400</v>
+      </c>
+      <c r="E52" s="3">
         <v>26400</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>74100</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>74800</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>77300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>30800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>74200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>78900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>79000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>30500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>76200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>78600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>79500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>29500</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>26100</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>26200</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>28900</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>24400</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>37300</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>36500</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>33500</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>31200</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>27200</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>24300</v>
       </c>
     </row>
-    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3794,82 +3916,88 @@
       <c r="Z53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>765600</v>
+      </c>
+      <c r="E54" s="3">
         <v>762600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>793100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>773200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>774400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>757300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>797300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>821500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>812500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>820200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>842700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>809000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>838600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>824300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>851500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>879300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>908500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1124300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1393200</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1403100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1450000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1485200</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1504800</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1480300</v>
       </c>
     </row>
-    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3896,8 +4024,9 @@
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
-    </row>
-    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA55" s="3"/>
+    </row>
+    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3924,102 +4053,106 @@
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
-    </row>
-    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA56" s="3"/>
+    </row>
+    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>45500</v>
+      </c>
+      <c r="E57" s="3">
         <v>50500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>47200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>54300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>74700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>72500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>65700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>66400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>63500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>62000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>59900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>49700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>47000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>45100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>52100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>62300</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>68800</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>76900</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>126100</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>122500</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>124100</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>69600</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>142200</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>136900</v>
       </c>
     </row>
-    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>4400</v>
+      </c>
+      <c r="E58" s="3">
         <v>3800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>3100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>2500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>4000</v>
-      </c>
-      <c r="I58" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="J58" s="3" t="s">
         <v>8</v>
@@ -4036,8 +4169,8 @@
       <c r="N58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O58" s="3">
-        <v>0</v>
+      <c r="O58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P58" s="3">
         <v>0</v>
@@ -4052,13 +4185,13 @@
         <v>0</v>
       </c>
       <c r="T58" s="3">
+        <v>0</v>
+      </c>
+      <c r="U58" s="3">
         <v>7500</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>6300</v>
-      </c>
-      <c r="V58" s="3">
-        <v>30000</v>
       </c>
       <c r="W58" s="3">
         <v>30000</v>
@@ -4072,179 +4205,188 @@
       <c r="Z58" s="3">
         <v>30000</v>
       </c>
-    </row>
-    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA58" s="3">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>77100</v>
+      </c>
+      <c r="E59" s="3">
         <v>93900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>89900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>86600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>77600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>76700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>68800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>73900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>68200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>72800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>74500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>65500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>62800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>60500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>70400</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>67300</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>88500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>216000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>101200</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>125600</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>178300</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>298600</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>129100</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>107600</v>
       </c>
     </row>
-    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>127000</v>
+      </c>
+      <c r="E60" s="3">
         <v>148100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>140200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>143400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>154100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>153200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>134500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>140300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>131600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>134800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>134400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>115300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>109700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>105500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>122500</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>129600</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>157300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>300400</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>233600</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>278100</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>332400</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>354000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>301300</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>274500</v>
       </c>
     </row>
-    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>240100</v>
+      </c>
+      <c r="E61" s="3">
         <v>210300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>231500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>206800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>200400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>200000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>205000</v>
-      </c>
-      <c r="J61" s="3">
-        <v>175000</v>
       </c>
       <c r="K61" s="3">
         <v>175000</v>
@@ -4253,123 +4395,129 @@
         <v>175000</v>
       </c>
       <c r="M61" s="3">
+        <v>175000</v>
+      </c>
+      <c r="N61" s="3">
         <v>195000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>210000</v>
-      </c>
-      <c r="O61" s="3">
-        <v>255000</v>
       </c>
       <c r="P61" s="3">
         <v>255000</v>
       </c>
       <c r="Q61" s="3">
+        <v>255000</v>
+      </c>
+      <c r="R61" s="3">
         <v>286500</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>286400</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>286200</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>452900</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>469000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>455600</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>495400</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>502700</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>510000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>517300</v>
       </c>
     </row>
-    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>76800</v>
+      </c>
+      <c r="E62" s="3">
         <v>77500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>84700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>82200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>85600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>85500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>91500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>93100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>96000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>98300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>96300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>102400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>105900</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>104500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>106200</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>109000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>111800</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>69700</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>83200</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>83700</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>84700</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>69800</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>92400</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>99200</v>
       </c>
     </row>
-    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4442,8 +4590,11 @@
       <c r="Z63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4516,8 +4667,11 @@
       <c r="Z64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4590,82 +4744,88 @@
       <c r="Z65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>443900</v>
+      </c>
+      <c r="E66" s="3">
         <v>436000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>456500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>432400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>440100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>438700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>431000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>408400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>402700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>408000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>425800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>427600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>470600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>465100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>515300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>525000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>555300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>823100</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>785700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>817400</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>912500</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>926500</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>903800</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>891000</v>
       </c>
     </row>
-    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4692,8 +4852,9 @@
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
-    </row>
-    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA67" s="3"/>
+    </row>
+    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4766,8 +4927,11 @@
       <c r="Z68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4840,8 +5004,11 @@
       <c r="Z69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4914,8 +5081,11 @@
       <c r="Z70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4988,82 +5158,88 @@
       <c r="Z71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>1028900</v>
+      </c>
+      <c r="E72" s="3">
         <v>1011100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>991100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>978700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>974200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>966800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>959000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>957300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>956100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>953300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>950500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>925500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>922300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>917700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>918600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>923600</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>921500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>915500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>1184700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>1152300</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>1149600</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>1167000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>1207100</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>1178000</v>
       </c>
     </row>
-    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5136,8 +5312,11 @@
       <c r="Z73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5210,8 +5389,11 @@
       <c r="Z74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5284,82 +5466,88 @@
       <c r="Z75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>321700</v>
+      </c>
+      <c r="E76" s="3">
         <v>326600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>336600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>340800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>334300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>318600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>366300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>413000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>409800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>412200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>416900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>381400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>367900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>359200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>336300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>354400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>353300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>301200</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>607400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>585600</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>537600</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>558700</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>601000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>589300</v>
       </c>
     </row>
-    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5432,161 +5620,170 @@
       <c r="Z77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45260</v>
+      </c>
+      <c r="E80" s="2">
         <v>45169</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45077</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44985</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44895</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44804</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44712</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44620</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44530</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44439</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44347</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44255</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44165</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44074</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>43982</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43890</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43799</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43708</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43616</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43524</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43434</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43343</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43251</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43159</v>
       </c>
     </row>
-    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>17700</v>
+      </c>
+      <c r="E81" s="3">
         <v>22200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>12400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>4500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>7500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>10000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>1600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>2800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>5300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>25000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>3200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>4600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>1400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-5000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>2200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>2100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-249100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>32400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>2800</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-17500</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-26600</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>41900</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-26600</v>
       </c>
     </row>
-    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5613,40 +5810,41 @@
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
-    </row>
-    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA82" s="3"/>
+    </row>
+    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>3400</v>
+      </c>
+      <c r="E83" s="3">
         <v>3800</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>4100</v>
-      </c>
-      <c r="F83" s="3">
-        <v>4200</v>
       </c>
       <c r="G83" s="3">
         <v>4200</v>
       </c>
       <c r="H83" s="3">
+        <v>4200</v>
+      </c>
+      <c r="I83" s="3">
         <v>4600</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>4800</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>5000</v>
-      </c>
-      <c r="K83" s="3">
-        <v>5200</v>
       </c>
       <c r="L83" s="3">
         <v>5200</v>
       </c>
       <c r="M83" s="3">
-        <v>5500</v>
+        <v>5200</v>
       </c>
       <c r="N83" s="3">
         <v>5500</v>
@@ -5655,7 +5853,7 @@
         <v>5500</v>
       </c>
       <c r="P83" s="3">
-        <v>5300</v>
+        <v>5500</v>
       </c>
       <c r="Q83" s="3">
         <v>5300</v>
@@ -5664,31 +5862,34 @@
         <v>5300</v>
       </c>
       <c r="S83" s="3">
+        <v>5300</v>
+      </c>
+      <c r="T83" s="3">
         <v>4800</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>20200</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>9300</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>7500</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>8900</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>40700</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>10400</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>10300</v>
       </c>
     </row>
-    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5761,8 +5962,11 @@
       <c r="Z84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5835,8 +6039,11 @@
       <c r="Z85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5909,8 +6116,11 @@
       <c r="Z86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5983,8 +6193,11 @@
       <c r="Z87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6057,82 +6270,88 @@
       <c r="Z88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-6700</v>
+      </c>
+      <c r="E89" s="3">
         <v>50600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>17300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-7800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>17500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>44500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>2500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>9400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-4700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>29300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>11600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>4600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>8700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>12500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>13000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-5800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-22900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>53800</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>52500</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-22200</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-29100</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>106100</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>57700</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-1600</v>
       </c>
     </row>
-    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6159,82 +6378,86 @@
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
-    </row>
-    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA90" s="3"/>
+    </row>
+    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-2900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-2400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-3000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-2100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-3300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-2500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-3900</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-3700</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1900</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-2700</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-2300</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-3800</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-3200</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-14900</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-8100</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-11100</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-4600</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-11000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-6200</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-4600</v>
       </c>
     </row>
-    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6307,8 +6530,11 @@
       <c r="Z92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6381,82 +6607,88 @@
       <c r="Z93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="E94" s="3">
         <v>19100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-2900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-2300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-2500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-3200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-2500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>20800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-3200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-600</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-36800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>213300</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>11000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-6800</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>28200</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-7700</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-62800</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-11900</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-12300</v>
       </c>
     </row>
-    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6483,13 +6715,14 @@
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
-    </row>
-    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA95" s="3"/>
+    </row>
+    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>0</v>
+        <v>-2200</v>
       </c>
       <c r="E96" s="3">
         <v>0</v>
@@ -6498,11 +6731,11 @@
         <v>0</v>
       </c>
       <c r="G96" s="3">
+        <v>0</v>
+      </c>
+      <c r="H96" s="3">
         <v>-2300</v>
       </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
       <c r="I96" s="3">
         <v>0</v>
       </c>
@@ -6510,11 +6743,11 @@
         <v>0</v>
       </c>
       <c r="K96" s="3">
+        <v>0</v>
+      </c>
+      <c r="L96" s="3">
         <v>-2400</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
-      </c>
       <c r="M96" s="3">
         <v>0</v>
       </c>
@@ -6522,11 +6755,11 @@
         <v>0</v>
       </c>
       <c r="O96" s="3">
+        <v>0</v>
+      </c>
+      <c r="P96" s="3">
         <v>-2400</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
-      </c>
       <c r="Q96" s="3">
         <v>0</v>
       </c>
@@ -6534,31 +6767,34 @@
         <v>0</v>
       </c>
       <c r="S96" s="3">
-        <v>-2400</v>
+        <v>0</v>
       </c>
       <c r="T96" s="3">
         <v>-2400</v>
       </c>
       <c r="U96" s="3">
-        <v>0</v>
+        <v>-2400</v>
       </c>
       <c r="V96" s="3">
         <v>0</v>
       </c>
       <c r="W96" s="3">
-        <v>-2400</v>
+        <v>0</v>
       </c>
       <c r="X96" s="3">
         <v>-2400</v>
       </c>
       <c r="Y96" s="3">
-        <v>0</v>
+        <v>-2400</v>
       </c>
       <c r="Z96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6631,8 +6867,11 @@
       <c r="Z97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6705,8 +6944,11 @@
       <c r="Z98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6779,226 +7021,238 @@
       <c r="Z99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E100" s="3">
         <v>-57500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>4500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>5500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-5700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-40300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-6200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-1900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-3700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-19800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-13200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-46600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-1800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-32500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-10000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-1200</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-195200</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-99500</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-12100</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-40800</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-9600</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-18000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-7500</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>500</v>
+      </c>
+      <c r="E101" s="3">
         <v>200</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-1500</v>
       </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
       <c r="G101" s="3">
+        <v>0</v>
+      </c>
+      <c r="H101" s="3">
         <v>-800</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-5800</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-4900</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>900</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-2200</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-2900</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>1800</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>1900</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>1400</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>8400</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-2200</v>
-      </c>
-      <c r="R101" s="3">
-        <v>400</v>
       </c>
       <c r="S101" s="3">
         <v>400</v>
       </c>
       <c r="T101" s="3">
+        <v>400</v>
+      </c>
+      <c r="U101" s="3">
         <v>-4700</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-2700</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>1800</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-700</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-4400</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-2300</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>2700</v>
       </c>
     </row>
-    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-6500</v>
+      </c>
+      <c r="E102" s="3">
         <v>12400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>17300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-4600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>8500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-3000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-9700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>6900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-13800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>4100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>21000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-43300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>6400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-11400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-43300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-4400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-39300</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>30900</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-33100</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-47000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>20900</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>35900</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-11500</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/EPAC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/EPAC_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="92">
   <si>
     <t>EPAC</t>
   </si>
@@ -656,352 +656,365 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AA102"/>
+  <dimension ref="A5:AB102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45351</v>
+      </c>
+      <c r="E7" s="2">
         <v>45260</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45169</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45077</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44985</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44895</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44804</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44712</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44620</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44530</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44439</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44347</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44255</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44165</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44074</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43982</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43890</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43799</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43708</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43616</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43524</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43434</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43343</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43251</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43159</v>
       </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>138400</v>
+      </c>
+      <c r="E8" s="3">
         <v>142000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>160600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>156300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>142000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>139400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>151800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>151900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>136600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>130900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>145400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>143100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>120700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>119400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>111400</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>101900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>133400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>146700</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>654800</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>178100</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>159800</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>158600</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>641300</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>317100</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>275200</v>
       </c>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>66800</v>
+      </c>
+      <c r="E9" s="3">
         <v>67600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>80800</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>78000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>71400</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>71500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>78100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>79800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>76600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>71300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>79200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>76300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>65900</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>64200</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>66900</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>59900</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>71300</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>78000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>362100</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>96100</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>88500</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>88200</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>358000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>200600</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>185500</v>
       </c>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>71600</v>
+      </c>
+      <c r="E10" s="3">
         <v>74400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>79800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>78300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>70600</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>67900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>73700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>72100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>60000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>59600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>66200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>66800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>54800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>55200</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>44500</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>42000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>62100</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>68700</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>292700</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>82000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>71300</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>70400</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>283300</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>116500</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>89700</v>
       </c>
     </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1029,8 +1042,9 @@
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
-    </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB11" s="3"/>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1106,8 +1120,11 @@
       <c r="AA12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1183,85 +1200,91 @@
       <c r="AA13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E14" s="3">
         <v>3700</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>4000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>8200</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>14400</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>10400</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>4300</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>500</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>2900</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>2700</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>5600</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>-3800</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>1100</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>300</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>1400</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>1000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>1200</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>600</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>27000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>-11900</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>3600</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>23400</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>13500</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>1200</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>6400</v>
       </c>
     </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1269,34 +1292,34 @@
         <v>800</v>
       </c>
       <c r="E15" s="3">
+        <v>800</v>
+      </c>
+      <c r="F15" s="3">
         <v>1000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>1400</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>1300</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>1400</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>1600</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>1800</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>1900</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>2000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>1800</v>
-      </c>
-      <c r="N15" s="3">
-        <v>2100</v>
       </c>
       <c r="O15" s="3">
         <v>2100</v>
@@ -1305,40 +1328,43 @@
         <v>2100</v>
       </c>
       <c r="Q15" s="3">
-        <v>2200</v>
+        <v>2100</v>
       </c>
       <c r="R15" s="3">
         <v>2200</v>
       </c>
       <c r="S15" s="3">
+        <v>2200</v>
+      </c>
+      <c r="T15" s="3">
         <v>2100</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>1900</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>8900</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>2800</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>1900</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>2300</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>9300</v>
-      </c>
-      <c r="Z15" s="3">
-        <v>5200</v>
       </c>
       <c r="AA15" s="3">
         <v>5200</v>
       </c>
-    </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB15" s="3">
+        <v>5200</v>
+      </c>
+    </row>
+    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1363,162 +1389,169 @@
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
-    </row>
-    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB16" s="3"/>
+    </row>
+    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>108900</v>
+      </c>
+      <c r="E17" s="3">
         <v>113300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>128400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>130800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>128000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>127100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>138700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>145300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>132100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>124500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>131800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>120400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>114900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>110400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>108100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>103900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>124800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>132300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>607200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>139900</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>147300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>167100</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>591100</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>284400</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>265400</v>
       </c>
     </row>
-    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>29500</v>
+      </c>
+      <c r="E18" s="3">
         <v>28700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>32200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>25500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>14000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>12300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>13100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>6600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>4500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>6400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>13600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>22700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>5800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>9000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>3300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-2000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>8600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>14400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>47600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>38200</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>12500</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-8500</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>50200</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>32700</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>9800</v>
       </c>
     </row>
-    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1546,162 +1579,169 @@
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
-    </row>
-    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB19" s="3"/>
+    </row>
+    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="E20" s="3">
         <v>-4700</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-3900</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-3800</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-3900</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-3500</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-3000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-1200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-1000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-1400</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-1100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-1800</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-2200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-2000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-2200</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-3400</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-3900</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-7100</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-28800</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-6400</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-7700</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-7900</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-31000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-7700</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-8200</v>
       </c>
     </row>
-    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>28600</v>
+      </c>
+      <c r="E21" s="3">
         <v>27400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>32100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>25700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>14400</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>13000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>14700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>10300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>8400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>10100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>17600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>26300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>9100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>12500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>6500</v>
       </c>
-      <c r="R21" s="3">
-        <v>0</v>
-      </c>
       <c r="S21" s="3">
+        <v>0</v>
+      </c>
+      <c r="T21" s="3">
         <v>10000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>12100</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>38900</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>41100</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>16100</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-11300</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>39600</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>35400</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>11900</v>
       </c>
     </row>
-    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1777,162 +1817,171 @@
       <c r="AA22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>25300</v>
+      </c>
+      <c r="E23" s="3">
         <v>24000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>28300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>21700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>10100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>8800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>10100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>5400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>3500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>5000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>12400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>20900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>3600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>7100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>1100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-5300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>4700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>7300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>18700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>31800</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>4800</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-16400</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>19200</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>25000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>7400</v>
+      </c>
+      <c r="E24" s="3">
         <v>5700</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>5200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>4700</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>3000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>2400</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>1400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>1300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>1800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-4400</v>
       </c>
-      <c r="O24" s="3">
-        <v>0</v>
-      </c>
       <c r="P24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="3">
         <v>2300</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>3900</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-400</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>800</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>1000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>16500</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>5000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>4000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>100</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>14500</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-4000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>19800</v>
       </c>
     </row>
-    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2008,162 +2057,171 @@
       <c r="AA25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>17900</v>
+      </c>
+      <c r="E26" s="3">
         <v>18300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>23100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>17000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>7200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>6400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>10200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>4100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>2100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>3200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>12500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>25300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>3600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>4800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-2800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-4900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>3900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>6400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>2300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>26900</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-16400</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>4700</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>29000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-18200</v>
       </c>
     </row>
-    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>17900</v>
+      </c>
+      <c r="E27" s="3">
         <v>18300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>23100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>17000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>7200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>6400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>10200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>4100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>2100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>3200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>12500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>25300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>3600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>4800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-2800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-4900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>3900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>6400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>2300</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>26900</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>800</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-16400</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>4700</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>29000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-18200</v>
       </c>
     </row>
-    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2239,85 +2297,91 @@
       <c r="AA28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E29" s="3">
         <v>-600</v>
       </c>
-      <c r="E29" s="3">
+      <c r="F29" s="3">
         <v>-900</v>
       </c>
-      <c r="F29" s="3">
+      <c r="G29" s="3">
         <v>-4600</v>
       </c>
-      <c r="G29" s="3">
+      <c r="H29" s="3">
         <v>-2700</v>
       </c>
-      <c r="H29" s="3">
+      <c r="I29" s="3">
         <v>1000</v>
       </c>
-      <c r="I29" s="3">
+      <c r="J29" s="3">
         <v>-200</v>
       </c>
-      <c r="J29" s="3">
+      <c r="K29" s="3">
         <v>-2400</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>-900</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>-400</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>-7300</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>-200</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>-400</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>-200</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>4200</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <v>-100</v>
       </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
         <v>-1800</v>
       </c>
-      <c r="T29" s="3">
+      <c r="U29" s="3">
         <v>-4300</v>
       </c>
-      <c r="U29" s="3">
+      <c r="V29" s="3">
         <v>-251400</v>
       </c>
-      <c r="V29" s="3">
+      <c r="W29" s="3">
         <v>5600</v>
       </c>
-      <c r="W29" s="3">
+      <c r="X29" s="3">
         <v>2000</v>
       </c>
-      <c r="X29" s="3">
+      <c r="Y29" s="3">
         <v>-1000</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Z29" s="3">
         <v>-31400</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="AA29" s="3">
         <v>12900</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AB29" s="3">
         <v>-8400</v>
       </c>
     </row>
-    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2393,8 +2457,11 @@
       <c r="AA30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2470,162 +2537,171 @@
       <c r="AA31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E32" s="3">
         <v>4700</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>3900</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>3800</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>3900</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>3500</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>3000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>1200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>1000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>1400</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>1100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>1800</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>2200</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>2000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>2200</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>3400</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>3900</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>7100</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>28800</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>6400</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>7700</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>7900</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>31000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>7700</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>8200</v>
       </c>
     </row>
-    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>17800</v>
+      </c>
+      <c r="E33" s="3">
         <v>17700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>22200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>12400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>4500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>7500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>10000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>2800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>5300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>25000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>3200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>4600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>1400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-5000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>2200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>2100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-249100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>32400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>2800</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-17500</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-26600</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>41900</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-26600</v>
       </c>
     </row>
-    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2701,167 +2777,176 @@
       <c r="AA34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>17800</v>
+      </c>
+      <c r="E35" s="3">
         <v>17700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>22200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>12400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>4500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>7500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>10000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>2800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>5300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>25000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>3200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>4600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>1400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-5000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>2200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>2100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-249100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>32400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>2800</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-17500</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-26600</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>41900</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-26600</v>
       </c>
     </row>
-    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45351</v>
+      </c>
+      <c r="E38" s="2">
         <v>45260</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45169</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45077</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44985</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44895</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44804</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44712</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44620</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44530</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44439</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44347</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44255</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44165</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44074</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43982</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43890</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43799</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43708</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43616</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43524</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43434</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43343</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43251</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43159</v>
       </c>
     </row>
-    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2889,8 +2974,9 @@
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
-    </row>
-    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB39" s="3"/>
+    </row>
+    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2918,85 +3004,89 @@
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
-    </row>
-    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB40" s="3"/>
+    </row>
+    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>153700</v>
+      </c>
+      <c r="E41" s="3">
         <v>148000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>154400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>142000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>124700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>129200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>120700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>123700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>133400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>126500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>140400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>136300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>115300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>158600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>152200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>163600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>163400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>206800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>211200</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>201300</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>170400</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>203400</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>250500</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>189500</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>153600</v>
       </c>
     </row>
-    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3072,316 +3162,331 @@
       <c r="AA42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>102100</v>
+      </c>
+      <c r="E43" s="3">
         <v>101400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>101600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>106600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>101800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>99100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>109100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>120800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>116400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>114700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>111800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>119600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>102700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>95600</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>90300</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>98400</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>118500</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>127000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>125900</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>202800</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>210200</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>191200</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>123300</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>212300</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>210700</v>
       </c>
     </row>
-    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>82900</v>
+      </c>
+      <c r="E44" s="3">
         <v>80100</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>74800</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>93000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>94200</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>90700</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>83700</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>86900</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>89500</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>83600</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>75300</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>74700</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>71800</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>70700</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>69200</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>78900</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>78000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>79500</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>77200</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>167600</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>161600</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>154800</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>72000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>167300</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>166200</v>
       </c>
     </row>
-    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>28700</v>
+      </c>
+      <c r="E45" s="3">
         <v>30500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>24800</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>31800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>34600</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>33700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>28900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>34900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>34700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>36200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>30000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>41200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>35700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>32900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>29500</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>39000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>38200</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>39500</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>316100</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>44500</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>111000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>157900</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>625000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>58700</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>60600</v>
       </c>
     </row>
-    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>367300</v>
+      </c>
+      <c r="E46" s="3">
         <v>360000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>355600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>373400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>355300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>352700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>342400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>366300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>374100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>361100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>357400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>371800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>325400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>357800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>341100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>379800</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>398200</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>452700</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>730300</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>616200</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>653200</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>707300</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>1047200</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>627800</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>591000</v>
       </c>
     </row>
-    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3457,162 +3562,171 @@
       <c r="AA47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>37000</v>
+      </c>
+      <c r="E48" s="3">
         <v>38000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>76700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>41800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>41200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>41800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>84600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>44400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>46500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>47700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>100200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>50100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>61300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>60200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>110100</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>111600</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>116600</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>111700</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>56700</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>90000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>83100</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>79200</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>145200</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>100800</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>102400</v>
       </c>
     </row>
-    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>303000</v>
+      </c>
+      <c r="E49" s="3">
         <v>304300</v>
-      </c>
-      <c r="E49" s="3">
-        <v>303800</v>
       </c>
       <c r="F49" s="3">
         <v>303800</v>
       </c>
       <c r="G49" s="3">
+        <v>303800</v>
+      </c>
+      <c r="H49" s="3">
         <v>301900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>302700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>299500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>312400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>322000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>324700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>332100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>344600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>343700</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>341100</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>343500</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>334000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>338300</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>315200</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>312800</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>649700</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>630200</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>630100</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>351800</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>749000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>762500</v>
       </c>
     </row>
-    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3688,8 +3802,11 @@
       <c r="AA50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3765,85 +3882,91 @@
       <c r="AA51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>62000</v>
+      </c>
+      <c r="E52" s="3">
         <v>63400</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>26400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>74100</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>74800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>77300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>30800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>74200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>78900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>79000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>30500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>76200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>78600</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>79500</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>29500</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>26100</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>26200</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>28900</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>24400</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>37300</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>36500</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>33500</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>31200</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>27200</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>24300</v>
       </c>
     </row>
-    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3919,85 +4042,91 @@
       <c r="AA53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>769300</v>
+      </c>
+      <c r="E54" s="3">
         <v>765600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>762600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>793100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>773200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>774400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>757300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>797300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>821500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>812500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>820200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>842700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>809000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>838600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>824300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>851500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>879300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>908500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1124300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1393200</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1403100</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1450000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1485200</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1504800</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1480300</v>
       </c>
     </row>
-    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4025,8 +4154,9 @@
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
-    </row>
-    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB55" s="3"/>
+    </row>
+    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4054,108 +4184,112 @@
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
-    </row>
-    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB56" s="3"/>
+    </row>
+    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>44000</v>
+      </c>
+      <c r="E57" s="3">
         <v>45500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>50500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>47200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>54300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>74700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>72500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>65700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>66400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>63500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>62000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>59900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>49700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>47000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>45100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>52100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>62300</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>68800</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>76900</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>126100</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>122500</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>124100</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>69600</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>142200</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>136900</v>
       </c>
     </row>
-    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>5000</v>
+      </c>
+      <c r="E58" s="3">
         <v>4400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>3800</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>3100</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>2500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>4000</v>
-      </c>
-      <c r="J58" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="K58" s="3" t="s">
         <v>8</v>
@@ -4172,8 +4306,8 @@
       <c r="O58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P58" s="3">
-        <v>0</v>
+      <c r="P58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q58" s="3">
         <v>0</v>
@@ -4188,13 +4322,13 @@
         <v>0</v>
       </c>
       <c r="U58" s="3">
+        <v>0</v>
+      </c>
+      <c r="V58" s="3">
         <v>7500</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>6300</v>
-      </c>
-      <c r="W58" s="3">
-        <v>30000</v>
       </c>
       <c r="X58" s="3">
         <v>30000</v>
@@ -4208,188 +4342,197 @@
       <c r="AA58" s="3">
         <v>30000</v>
       </c>
-    </row>
-    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB58" s="3">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>69100</v>
+      </c>
+      <c r="E59" s="3">
         <v>77100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>93900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>89900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>86600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>77600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>76700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>68800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>73900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>68200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>72800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>74500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>65500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>62800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>60500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>70400</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>67300</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>88500</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>216000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>101200</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>125600</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>178300</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>298600</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>129100</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>107600</v>
       </c>
     </row>
-    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>118100</v>
+      </c>
+      <c r="E60" s="3">
         <v>127000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>148100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>140200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>143400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>154100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>153200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>134500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>140300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>131600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>134800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>134400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>115300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>109700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>105500</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>122500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>129600</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>157300</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>300400</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>233600</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>278100</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>332400</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>354000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>301300</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>274500</v>
       </c>
     </row>
-    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>239900</v>
+      </c>
+      <c r="E61" s="3">
         <v>240100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>210300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>231500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>206800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>200400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>200000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>205000</v>
-      </c>
-      <c r="K61" s="3">
-        <v>175000</v>
       </c>
       <c r="L61" s="3">
         <v>175000</v>
@@ -4398,126 +4541,132 @@
         <v>175000</v>
       </c>
       <c r="N61" s="3">
+        <v>175000</v>
+      </c>
+      <c r="O61" s="3">
         <v>195000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>210000</v>
-      </c>
-      <c r="P61" s="3">
-        <v>255000</v>
       </c>
       <c r="Q61" s="3">
         <v>255000</v>
       </c>
       <c r="R61" s="3">
+        <v>255000</v>
+      </c>
+      <c r="S61" s="3">
         <v>286500</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>286400</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>286200</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>452900</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>469000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>455600</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>495400</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>502700</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>510000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>517300</v>
       </c>
     </row>
-    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>74300</v>
+      </c>
+      <c r="E62" s="3">
         <v>76800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>77500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>84700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>82200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>85600</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>85500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>91500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>93100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>96000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>98300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>96300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>102400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>105900</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>104500</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>106200</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>109000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>111800</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>69700</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>83200</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>83700</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>84700</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>69800</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>92400</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>99200</v>
       </c>
     </row>
-    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4593,8 +4742,11 @@
       <c r="AA63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4670,8 +4822,11 @@
       <c r="AA64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4747,85 +4902,91 @@
       <c r="AA65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>432400</v>
+      </c>
+      <c r="E66" s="3">
         <v>443900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>436000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>456500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>432400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>440100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>438700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>431000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>408400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>402700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>408000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>425800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>427600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>470600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>465100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>515300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>525000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>555300</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>823100</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>785700</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>817400</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>912500</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>926500</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>903800</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>891000</v>
       </c>
     </row>
-    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4853,8 +5014,9 @@
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
-    </row>
-    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB67" s="3"/>
+    </row>
+    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4930,8 +5092,11 @@
       <c r="AA68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5007,8 +5172,11 @@
       <c r="AA69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5084,8 +5252,11 @@
       <c r="AA70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5161,85 +5332,91 @@
       <c r="AA71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>222000</v>
+      </c>
+      <c r="E72" s="3">
         <v>1028900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>1011100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>991100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>978700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>974200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>966800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>959000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>957300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>956100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>953300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>950500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>925500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>922300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>917700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>918600</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>923600</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>921500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>915500</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>1184700</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>1152300</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>1149600</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>1167000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>1207100</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>1178000</v>
       </c>
     </row>
-    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5315,8 +5492,11 @@
       <c r="AA73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5392,8 +5572,11 @@
       <c r="AA74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5469,85 +5652,91 @@
       <c r="AA75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>336900</v>
+      </c>
+      <c r="E76" s="3">
         <v>321700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>326600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>336600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>340800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>334300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>318600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>366300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>413000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>409800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>412200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>416900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>381400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>367900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>359200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>336300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>354400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>353300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>301200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>607400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>585600</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>537600</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>558700</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>601000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>589300</v>
       </c>
     </row>
-    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5623,167 +5812,176 @@
       <c r="AA77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45351</v>
+      </c>
+      <c r="E80" s="2">
         <v>45260</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45169</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45077</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44985</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44895</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44804</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44712</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44620</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44530</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44439</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44347</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44255</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44165</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44074</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43982</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43890</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43799</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43708</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43616</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43524</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43434</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43343</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43251</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43159</v>
       </c>
     </row>
-    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>17800</v>
+      </c>
+      <c r="E81" s="3">
         <v>17700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>22200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>12400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>4500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>7500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>10000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>2800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>5300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>25000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>3200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>4600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>1400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-5000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>2200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>2100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-249100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>32400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>2800</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-17500</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-26600</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>41900</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-26600</v>
       </c>
     </row>
-    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5811,43 +6009,44 @@
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
-    </row>
-    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB82" s="3"/>
+    </row>
+    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E83" s="3">
         <v>3400</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>3800</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>4100</v>
-      </c>
-      <c r="G83" s="3">
-        <v>4200</v>
       </c>
       <c r="H83" s="3">
         <v>4200</v>
       </c>
       <c r="I83" s="3">
+        <v>4200</v>
+      </c>
+      <c r="J83" s="3">
         <v>4600</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>4800</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>5000</v>
-      </c>
-      <c r="L83" s="3">
-        <v>5200</v>
       </c>
       <c r="M83" s="3">
         <v>5200</v>
       </c>
       <c r="N83" s="3">
-        <v>5500</v>
+        <v>5200</v>
       </c>
       <c r="O83" s="3">
         <v>5500</v>
@@ -5856,7 +6055,7 @@
         <v>5500</v>
       </c>
       <c r="Q83" s="3">
-        <v>5300</v>
+        <v>5500</v>
       </c>
       <c r="R83" s="3">
         <v>5300</v>
@@ -5865,31 +6064,34 @@
         <v>5300</v>
       </c>
       <c r="T83" s="3">
+        <v>5300</v>
+      </c>
+      <c r="U83" s="3">
         <v>4800</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>20200</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>9300</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>7500</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>8900</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>40700</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>10400</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>10300</v>
       </c>
     </row>
-    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5965,8 +6167,11 @@
       <c r="AA84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6042,8 +6247,11 @@
       <c r="AA85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6119,8 +6327,11 @@
       <c r="AA86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6196,8 +6407,11 @@
       <c r="AA87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6273,85 +6487,91 @@
       <c r="AA88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>13300</v>
+      </c>
+      <c r="E89" s="3">
         <v>-6700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>50600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>17300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-7800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>17500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>44500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>2500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>9400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-4700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>29300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>11600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>4600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>8700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>12500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>13000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-5800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-22900</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>53800</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>52500</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-22200</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-29100</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>106100</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>57700</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-1600</v>
       </c>
     </row>
-    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6379,8 +6599,9 @@
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
-    </row>
-    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB90" s="3"/>
+    </row>
+    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -6388,76 +6609,79 @@
         <v>-1600</v>
       </c>
       <c r="E91" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="F91" s="3">
         <v>-1000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-2900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-2400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-3000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-2100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1500</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-3300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-2500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-3900</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-3700</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-1900</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-2700</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-2300</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-3800</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-3200</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-14900</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-8100</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-11100</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-4600</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-11000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-6200</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-4600</v>
       </c>
     </row>
-    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6533,8 +6757,11 @@
       <c r="AA92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6610,85 +6837,91 @@
       <c r="AA93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-2600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>19100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-2900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-2300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-2500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-3200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-2500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>20800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-3200</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-1900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-600</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-36800</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>213300</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>11000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-6800</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>28200</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-7700</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-62800</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-11900</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-12300</v>
       </c>
     </row>
-    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6716,17 +6949,18 @@
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
-    </row>
-    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB95" s="3"/>
+    </row>
+    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>0</v>
+      </c>
+      <c r="E96" s="3">
         <v>-2200</v>
       </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
       <c r="F96" s="3">
         <v>0</v>
       </c>
@@ -6734,11 +6968,11 @@
         <v>0</v>
       </c>
       <c r="H96" s="3">
+        <v>0</v>
+      </c>
+      <c r="I96" s="3">
         <v>-2300</v>
       </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
       <c r="J96" s="3">
         <v>0</v>
       </c>
@@ -6746,11 +6980,11 @@
         <v>0</v>
       </c>
       <c r="L96" s="3">
+        <v>0</v>
+      </c>
+      <c r="M96" s="3">
         <v>-2400</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
-      </c>
       <c r="N96" s="3">
         <v>0</v>
       </c>
@@ -6758,11 +6992,11 @@
         <v>0</v>
       </c>
       <c r="P96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="3">
         <v>-2400</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
-      </c>
       <c r="R96" s="3">
         <v>0</v>
       </c>
@@ -6770,31 +7004,34 @@
         <v>0</v>
       </c>
       <c r="T96" s="3">
-        <v>-2400</v>
+        <v>0</v>
       </c>
       <c r="U96" s="3">
         <v>-2400</v>
       </c>
       <c r="V96" s="3">
-        <v>0</v>
+        <v>-2400</v>
       </c>
       <c r="W96" s="3">
         <v>0</v>
       </c>
       <c r="X96" s="3">
-        <v>-2400</v>
+        <v>0</v>
       </c>
       <c r="Y96" s="3">
         <v>-2400</v>
       </c>
       <c r="Z96" s="3">
-        <v>0</v>
+        <v>-2400</v>
       </c>
       <c r="AA96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6870,8 +7107,11 @@
       <c r="AA97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6947,8 +7187,11 @@
       <c r="AA98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7024,235 +7267,247 @@
       <c r="AA99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="E100" s="3">
         <v>2300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-57500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>4500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>5500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-5700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-40300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-6200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-3700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-19800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-13200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-46600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-1800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-32500</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-10000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-1200</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-195200</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-99500</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-12100</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-40800</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-9600</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-18000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-7500</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E101" s="3">
         <v>500</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>200</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-1500</v>
       </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
       <c r="H101" s="3">
+        <v>0</v>
+      </c>
+      <c r="I101" s="3">
         <v>-800</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-5800</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-4900</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>900</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-2200</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-2900</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>1800</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>1900</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>1400</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>8400</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-2200</v>
-      </c>
-      <c r="S101" s="3">
-        <v>400</v>
       </c>
       <c r="T101" s="3">
         <v>400</v>
       </c>
       <c r="U101" s="3">
+        <v>400</v>
+      </c>
+      <c r="V101" s="3">
         <v>-4700</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-2700</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>1800</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-700</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-4400</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-2300</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>2700</v>
       </c>
     </row>
-    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>5700</v>
+      </c>
+      <c r="E102" s="3">
         <v>-6500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>12400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>17300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-4600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>8500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-3000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-9700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>6900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-13800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>4100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>21000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-43300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>6400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-11400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-43300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-4400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-39300</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>30900</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-33100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-47000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>20900</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>35900</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-11500</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/EPAC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/EPAC_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="92">
   <si>
     <t>EPAC</t>
   </si>
@@ -656,365 +656,378 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AB102"/>
+  <dimension ref="A5:AC102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45443</v>
+      </c>
+      <c r="E7" s="2">
         <v>45351</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45260</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45169</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45077</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44985</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44895</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44804</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44712</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44620</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44530</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44439</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44347</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44255</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44165</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44074</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43982</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43890</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43799</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43708</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43616</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43524</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43434</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43343</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43251</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43159</v>
       </c>
     </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>150400</v>
+      </c>
+      <c r="E8" s="3">
         <v>138400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>142000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>160600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>156300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>142000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>139400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>151800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>151900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>136600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>130900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>145400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>143100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>120700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>119400</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>111400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>101900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>133400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>146700</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>654800</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>178100</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>159800</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>158600</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>641300</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>317100</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>275200</v>
       </c>
     </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>71900</v>
+      </c>
+      <c r="E9" s="3">
         <v>66800</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>67600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>80800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>78000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>71400</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>71500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>78100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>79800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>76600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>71300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>79200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>76300</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>65900</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>64200</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>66900</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>59900</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>71300</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>78000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>362100</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>96100</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>88500</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>88200</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>358000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>200600</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>185500</v>
       </c>
     </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>78500</v>
+      </c>
+      <c r="E10" s="3">
         <v>71600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>74400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>79800</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>78300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>70600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>67900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>73700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>72100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>60000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>59600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>66200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>66800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>54800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>55200</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>44500</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>42000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>62100</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>68700</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>292700</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>82000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>71300</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>70400</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>283300</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>116500</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>89700</v>
       </c>
     </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1043,8 +1056,9 @@
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
-    </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC11" s="3"/>
+    </row>
+    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1123,8 +1137,11 @@
       <c r="AB12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1203,88 +1220,94 @@
       <c r="AB13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>3700</v>
+      </c>
+      <c r="E14" s="3">
         <v>2000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>3700</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>4000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>8200</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>14400</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>10400</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>4300</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>500</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>2900</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>2700</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>5600</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>-3800</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>1100</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>300</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>1400</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>1000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>1200</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>600</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>27000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>-11900</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>3600</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>23400</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>13500</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>1200</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>6400</v>
       </c>
     </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1295,34 +1318,34 @@
         <v>800</v>
       </c>
       <c r="F15" s="3">
+        <v>800</v>
+      </c>
+      <c r="G15" s="3">
         <v>1000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>1400</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>1300</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>1400</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>1600</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>1800</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>1900</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>2000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>1800</v>
-      </c>
-      <c r="O15" s="3">
-        <v>2100</v>
       </c>
       <c r="P15" s="3">
         <v>2100</v>
@@ -1331,40 +1354,43 @@
         <v>2100</v>
       </c>
       <c r="R15" s="3">
-        <v>2200</v>
+        <v>2100</v>
       </c>
       <c r="S15" s="3">
         <v>2200</v>
       </c>
       <c r="T15" s="3">
+        <v>2200</v>
+      </c>
+      <c r="U15" s="3">
         <v>2100</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>1900</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>8900</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>2800</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>1900</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>2300</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>9300</v>
-      </c>
-      <c r="AA15" s="3">
-        <v>5200</v>
       </c>
       <c r="AB15" s="3">
         <v>5200</v>
       </c>
-    </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC15" s="3">
+        <v>5200</v>
+      </c>
+    </row>
+    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1390,168 +1416,175 @@
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
-    </row>
-    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC16" s="3"/>
+    </row>
+    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>117000</v>
+      </c>
+      <c r="E17" s="3">
         <v>108900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>113300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>128400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>130800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>128000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>127100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>138700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>145300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>132100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>124500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>131800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>120400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>114900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>110400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>108100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>103900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>124800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>132300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>607200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>139900</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>147300</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>167100</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>591100</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>284400</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>265400</v>
       </c>
     </row>
-    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>33400</v>
+      </c>
+      <c r="E18" s="3">
         <v>29500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>28700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>32200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>25500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>14000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>12300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>13100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>6600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>4500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>6400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>13600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>22700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>5800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>9000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>3300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-2000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>8600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>14400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>47600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>38200</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>12500</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-8500</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>50200</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>32700</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>9800</v>
       </c>
     </row>
-    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1580,168 +1613,175 @@
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
-    </row>
-    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC19" s="3"/>
+    </row>
+    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="E20" s="3">
         <v>-4200</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-4700</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-3900</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-3800</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-3900</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-3500</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-3000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-1200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-1000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-1400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-1100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-1800</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-2200</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-2000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-2200</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-3400</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-3900</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-7100</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-28800</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-6400</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-7700</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-7900</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-31000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-7700</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-8200</v>
       </c>
     </row>
-    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>32700</v>
+      </c>
+      <c r="E21" s="3">
         <v>28600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>27400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>32100</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>25700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>14400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>13000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>14700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>10300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>8400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>10100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>17600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>26300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>9100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>12500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>6500</v>
       </c>
-      <c r="S21" s="3">
-        <v>0</v>
-      </c>
       <c r="T21" s="3">
+        <v>0</v>
+      </c>
+      <c r="U21" s="3">
         <v>10000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>12100</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>38900</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>41100</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>16100</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-11300</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>39600</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>35400</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>11900</v>
       </c>
     </row>
-    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1820,168 +1860,177 @@
       <c r="AB22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>29400</v>
+      </c>
+      <c r="E23" s="3">
         <v>25300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>24000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>28300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>21700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>10100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>8800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>10100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>5400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>3500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>5000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>12400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>20900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>3600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>7100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>1100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-5300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>4700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>7300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>18700</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>31800</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>4800</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-16400</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>19200</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>25000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>6800</v>
+      </c>
+      <c r="E24" s="3">
         <v>7400</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>5700</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>5200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>4700</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>3000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>2400</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>1400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>1300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>1800</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-4400</v>
       </c>
-      <c r="P24" s="3">
-        <v>0</v>
-      </c>
       <c r="Q24" s="3">
+        <v>0</v>
+      </c>
+      <c r="R24" s="3">
         <v>2300</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>3900</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-400</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>800</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>1000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>16500</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>5000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>4000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>100</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>14500</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-4000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>19800</v>
       </c>
     </row>
-    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2060,168 +2109,177 @@
       <c r="AB25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>22600</v>
+      </c>
+      <c r="E26" s="3">
         <v>17900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>18300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>23100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>17000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>7200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>6400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>10200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>4100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>2100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>3200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>12500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>25300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>3600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>4800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-2800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-4900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>3900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>6400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>2300</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>26900</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>800</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-16400</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>4700</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>29000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-18200</v>
       </c>
     </row>
-    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>22600</v>
+      </c>
+      <c r="E27" s="3">
         <v>17900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>18300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>23100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>17000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>7200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>6400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>10200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>4100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>2100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>3200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>12500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>25300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>3600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>4800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-2800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-4900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>3900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>6400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>2300</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>26900</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>800</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-16400</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>4700</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>29000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-18200</v>
       </c>
     </row>
-    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2300,88 +2358,94 @@
       <c r="AB28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
+        <v>3200</v>
+      </c>
+      <c r="E29" s="3">
         <v>-100</v>
       </c>
-      <c r="E29" s="3">
+      <c r="F29" s="3">
         <v>-600</v>
       </c>
-      <c r="F29" s="3">
+      <c r="G29" s="3">
         <v>-900</v>
       </c>
-      <c r="G29" s="3">
+      <c r="H29" s="3">
         <v>-4600</v>
       </c>
-      <c r="H29" s="3">
+      <c r="I29" s="3">
         <v>-2700</v>
       </c>
-      <c r="I29" s="3">
+      <c r="J29" s="3">
         <v>1000</v>
       </c>
-      <c r="J29" s="3">
+      <c r="K29" s="3">
         <v>-200</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>-2400</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>-900</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>-400</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>-7300</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>-200</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>-400</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>-200</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <v>4200</v>
       </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
         <v>-100</v>
       </c>
-      <c r="T29" s="3">
+      <c r="U29" s="3">
         <v>-1800</v>
       </c>
-      <c r="U29" s="3">
+      <c r="V29" s="3">
         <v>-4300</v>
       </c>
-      <c r="V29" s="3">
+      <c r="W29" s="3">
         <v>-251400</v>
       </c>
-      <c r="W29" s="3">
+      <c r="X29" s="3">
         <v>5600</v>
       </c>
-      <c r="X29" s="3">
+      <c r="Y29" s="3">
         <v>2000</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Z29" s="3">
         <v>-1000</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="AA29" s="3">
         <v>-31400</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AB29" s="3">
         <v>12900</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AC29" s="3">
         <v>-8400</v>
       </c>
     </row>
-    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2460,8 +2524,11 @@
       <c r="AB30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2540,168 +2607,177 @@
       <c r="AB31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>3900</v>
+      </c>
+      <c r="E32" s="3">
         <v>4200</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>4700</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>3900</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>3800</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>3900</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>3500</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>3000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>1200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>1000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>1400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>1100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>1800</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>2200</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>2000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>2200</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>3400</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>3900</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>7100</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>28800</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>6400</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>7700</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>7900</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>31000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>7700</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>8200</v>
       </c>
     </row>
-    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>25800</v>
+      </c>
+      <c r="E33" s="3">
         <v>17800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>17700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>22200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>12400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>4500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>7500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>10000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>2800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>5300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>25000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>3200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>4600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>1400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-5000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>2200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>2100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-249100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>32400</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>2800</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-17500</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-26600</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>41900</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-26600</v>
       </c>
     </row>
-    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2780,173 +2856,182 @@
       <c r="AB34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>25800</v>
+      </c>
+      <c r="E35" s="3">
         <v>17800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>17700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>22200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>12400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>4500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>7500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>10000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>2800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>5300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>25000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>3200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>4600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>1400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-5000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>2200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>2100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-249100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>32400</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>2800</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-17500</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-26600</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>41900</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-26600</v>
       </c>
     </row>
-    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45443</v>
+      </c>
+      <c r="E38" s="2">
         <v>45351</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45260</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45169</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45077</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44985</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44895</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44804</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44712</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44620</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44530</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44439</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44347</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44255</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44165</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44074</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43982</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43890</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43799</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43708</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43616</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43524</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43434</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43343</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43251</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43159</v>
       </c>
     </row>
-    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2975,8 +3060,9 @@
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
-    </row>
-    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC39" s="3"/>
+    </row>
+    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3005,88 +3091,92 @@
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
-    </row>
-    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC40" s="3"/>
+    </row>
+    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>132400</v>
+      </c>
+      <c r="E41" s="3">
         <v>153700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>148000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>154400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>142000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>124700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>129200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>120700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>123700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>133400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>126500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>140400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>136300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>115300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>158600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>152200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>163600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>163400</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>206800</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>211200</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>201300</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>170400</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>203400</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>250500</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>189500</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>153600</v>
       </c>
     </row>
-    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3165,328 +3255,343 @@
       <c r="AB42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>113500</v>
+      </c>
+      <c r="E43" s="3">
         <v>102100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>101400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>101600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>106600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>101800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>99100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>109100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>120800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>116400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>114700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>111800</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>119600</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>102700</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>95600</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>90300</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>98400</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>118500</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>127000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>125900</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>202800</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>210200</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>191200</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>123300</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>212300</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>210700</v>
       </c>
     </row>
-    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>79100</v>
+      </c>
+      <c r="E44" s="3">
         <v>82900</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>80100</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>74800</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>93000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>94200</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>90700</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>83700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>86900</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>89500</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>83600</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>75300</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>74700</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>71800</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>70700</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>69200</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>78900</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>78000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>79500</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>77200</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>167600</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>161600</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>154800</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>72000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>167300</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>166200</v>
       </c>
     </row>
-    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>22900</v>
+      </c>
+      <c r="E45" s="3">
         <v>28700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>30500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>24800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>31800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>34600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>33700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>28900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>34900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>34700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>36200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>30000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>41200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>35700</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>32900</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>29500</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>39000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>38200</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>39500</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>316100</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>44500</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>111000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>157900</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>625000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>58700</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>60600</v>
       </c>
     </row>
-    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>347800</v>
+      </c>
+      <c r="E46" s="3">
         <v>367300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>360000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>355600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>373400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>355300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>352700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>342400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>366300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>374100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>361100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>357400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>371800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>325400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>357800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>341100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>379800</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>398200</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>452700</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>730300</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>616200</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>653200</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>707300</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>1047200</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>627800</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>591000</v>
       </c>
     </row>
-    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3565,168 +3670,177 @@
       <c r="AB47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>36200</v>
+      </c>
+      <c r="E48" s="3">
         <v>37000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>38000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>76700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>41800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>41200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>41800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>84600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>44400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>46500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>47700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>100200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>50100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>61300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>60200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>110100</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>111600</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>116600</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>111700</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>56700</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>90000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>83100</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>79200</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>145200</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>100800</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>102400</v>
       </c>
     </row>
-    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>303100</v>
+      </c>
+      <c r="E49" s="3">
         <v>303000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>304300</v>
-      </c>
-      <c r="F49" s="3">
-        <v>303800</v>
       </c>
       <c r="G49" s="3">
         <v>303800</v>
       </c>
       <c r="H49" s="3">
+        <v>303800</v>
+      </c>
+      <c r="I49" s="3">
         <v>301900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>302700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>299500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>312400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>322000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>324700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>332100</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>344600</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>343700</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>341100</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>343500</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>334000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>338300</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>315200</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>312800</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>649700</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>630200</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>630100</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>351800</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>749000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>762500</v>
       </c>
     </row>
-    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3805,8 +3919,11 @@
       <c r="AB50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3885,88 +4002,94 @@
       <c r="AB51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>62400</v>
+      </c>
+      <c r="E52" s="3">
         <v>62000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>63400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>26400</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>74100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>74800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>77300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>30800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>74200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>78900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>79000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>30500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>76200</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>78600</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>79500</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>29500</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>26100</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>26200</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>28900</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>24400</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>37300</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>36500</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>33500</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>31200</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>27200</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>24300</v>
       </c>
     </row>
-    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4045,88 +4168,94 @@
       <c r="AB53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>749500</v>
+      </c>
+      <c r="E54" s="3">
         <v>769300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>765600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>762600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>793100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>773200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>774400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>757300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>797300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>821500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>812500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>820200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>842700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>809000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>838600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>824300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>851500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>879300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>908500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1124300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1393200</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1403100</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1450000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1485200</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1504800</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1480300</v>
       </c>
     </row>
-    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4155,8 +4284,9 @@
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
-    </row>
-    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC55" s="3"/>
+    </row>
+    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4185,88 +4315,92 @@
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
-    </row>
-    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC56" s="3"/>
+    </row>
+    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>41700</v>
+      </c>
+      <c r="E57" s="3">
         <v>44000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>45500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>50500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>47200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>54300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>74700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>72500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>65700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>66400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>63500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>62000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>59900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>49700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>47000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>45100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>52100</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>62300</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>68800</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>76900</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>126100</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>122500</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>124100</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>69600</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>142200</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>136900</v>
       </c>
     </row>
-    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4274,25 +4408,25 @@
         <v>5000</v>
       </c>
       <c r="E58" s="3">
+        <v>5000</v>
+      </c>
+      <c r="F58" s="3">
         <v>4400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>3800</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>3100</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>2500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>4000</v>
-      </c>
-      <c r="K58" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="L58" s="3" t="s">
         <v>8</v>
@@ -4309,8 +4443,8 @@
       <c r="P58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q58" s="3">
-        <v>0</v>
+      <c r="Q58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R58" s="3">
         <v>0</v>
@@ -4325,13 +4459,13 @@
         <v>0</v>
       </c>
       <c r="V58" s="3">
+        <v>0</v>
+      </c>
+      <c r="W58" s="3">
         <v>7500</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>6300</v>
-      </c>
-      <c r="X58" s="3">
-        <v>30000</v>
       </c>
       <c r="Y58" s="3">
         <v>30000</v>
@@ -4345,197 +4479,206 @@
       <c r="AB58" s="3">
         <v>30000</v>
       </c>
-    </row>
-    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC58" s="3">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>75300</v>
+      </c>
+      <c r="E59" s="3">
         <v>69100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>77100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>93900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>89900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>86600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>77600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>76700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>68800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>73900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>68200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>72800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>74500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>65500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>62800</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>60500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>70400</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>67300</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>88500</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>216000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>101200</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>125600</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>178300</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>298600</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>129100</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>107600</v>
       </c>
     </row>
-    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>122000</v>
+      </c>
+      <c r="E60" s="3">
         <v>118100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>127000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>148100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>140200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>143400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>154100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>153200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>134500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>140300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>131600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>134800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>134400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>115300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>109700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>105500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>122500</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>129600</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>157300</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>300400</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>233600</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>278100</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>332400</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>354000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>301300</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>274500</v>
       </c>
     </row>
-    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>190700</v>
+      </c>
+      <c r="E61" s="3">
         <v>239900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>240100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>210300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>231500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>206800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>200400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>200000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>205000</v>
-      </c>
-      <c r="L61" s="3">
-        <v>175000</v>
       </c>
       <c r="M61" s="3">
         <v>175000</v>
@@ -4544,129 +4687,135 @@
         <v>175000</v>
       </c>
       <c r="O61" s="3">
+        <v>175000</v>
+      </c>
+      <c r="P61" s="3">
         <v>195000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>210000</v>
-      </c>
-      <c r="Q61" s="3">
-        <v>255000</v>
       </c>
       <c r="R61" s="3">
         <v>255000</v>
       </c>
       <c r="S61" s="3">
+        <v>255000</v>
+      </c>
+      <c r="T61" s="3">
         <v>286500</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>286400</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>286200</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>452900</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>469000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>455600</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>495400</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>502700</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>510000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>517300</v>
       </c>
     </row>
-    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>71000</v>
+      </c>
+      <c r="E62" s="3">
         <v>74300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>76800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>77500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>84700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>82200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>85600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>85500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>91500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>93100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>96000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>98300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>96300</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>102400</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>105900</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>104500</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>106200</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>109000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>111800</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>69700</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>83200</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>83700</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>84700</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>69800</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>92400</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>99200</v>
       </c>
     </row>
-    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4745,8 +4894,11 @@
       <c r="AB63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4825,8 +4977,11 @@
       <c r="AB64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4905,88 +5060,94 @@
       <c r="AB65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>383700</v>
+      </c>
+      <c r="E66" s="3">
         <v>432400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>443900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>436000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>456500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>432400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>440100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>438700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>431000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>408400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>402700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>408000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>425800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>427600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>470600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>465100</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>515300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>525000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>555300</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>823100</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>785700</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>817400</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>912500</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>926500</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>903800</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>891000</v>
       </c>
     </row>
-    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5015,8 +5176,9 @@
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
-    </row>
-    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC67" s="3"/>
+    </row>
+    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5095,8 +5257,11 @@
       <c r="AB68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5175,8 +5340,11 @@
       <c r="AB69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5255,8 +5423,11 @@
       <c r="AB70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5335,88 +5506,94 @@
       <c r="AB71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>245300</v>
+      </c>
+      <c r="E72" s="3">
         <v>222000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>1028900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>1011100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>991100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>978700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>974200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>966800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>959000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>957300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>956100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>953300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>950500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>925500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>922300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>917700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>918600</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>923600</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>921500</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>915500</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>1184700</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>1152300</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>1149600</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>1167000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>1207100</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>1178000</v>
       </c>
     </row>
-    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5495,8 +5672,11 @@
       <c r="AB73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5575,8 +5755,11 @@
       <c r="AB74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5655,88 +5838,94 @@
       <c r="AB75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>365800</v>
+      </c>
+      <c r="E76" s="3">
         <v>336900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>321700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>326600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>336600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>340800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>334300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>318600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>366300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>413000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>409800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>412200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>416900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>381400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>367900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>359200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>336300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>354400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>353300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>301200</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>607400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>585600</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>537600</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>558700</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>601000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>589300</v>
       </c>
     </row>
-    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5815,173 +6004,182 @@
       <c r="AB77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45443</v>
+      </c>
+      <c r="E80" s="2">
         <v>45351</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45260</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45169</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45077</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44985</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44895</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44804</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44712</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44620</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44530</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44439</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44347</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44255</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44165</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44074</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43982</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43890</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43799</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43708</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43616</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43524</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43434</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43343</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43251</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43159</v>
       </c>
     </row>
-    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>25800</v>
+      </c>
+      <c r="E81" s="3">
         <v>17800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>17700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>22200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>12400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>4500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>7500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>10000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>2800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>5300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>25000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>3200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>4600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>1400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-5000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>2200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>2100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-249100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>32400</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>2800</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-17500</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-26600</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>41900</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-26600</v>
       </c>
     </row>
-    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6010,46 +6208,47 @@
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
-    </row>
-    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC82" s="3"/>
+    </row>
+    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>3200</v>
+      </c>
+      <c r="E83" s="3">
         <v>3300</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>3400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>3800</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>4100</v>
-      </c>
-      <c r="H83" s="3">
-        <v>4200</v>
       </c>
       <c r="I83" s="3">
         <v>4200</v>
       </c>
       <c r="J83" s="3">
+        <v>4200</v>
+      </c>
+      <c r="K83" s="3">
         <v>4600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>4800</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>5000</v>
-      </c>
-      <c r="M83" s="3">
-        <v>5200</v>
       </c>
       <c r="N83" s="3">
         <v>5200</v>
       </c>
       <c r="O83" s="3">
-        <v>5500</v>
+        <v>5200</v>
       </c>
       <c r="P83" s="3">
         <v>5500</v>
@@ -6058,7 +6257,7 @@
         <v>5500</v>
       </c>
       <c r="R83" s="3">
-        <v>5300</v>
+        <v>5500</v>
       </c>
       <c r="S83" s="3">
         <v>5300</v>
@@ -6067,31 +6266,34 @@
         <v>5300</v>
       </c>
       <c r="U83" s="3">
+        <v>5300</v>
+      </c>
+      <c r="V83" s="3">
         <v>4800</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>20200</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>9300</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>7500</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>8900</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>40700</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>10400</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>10300</v>
       </c>
     </row>
-    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6170,8 +6372,11 @@
       <c r="AB84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6250,8 +6455,11 @@
       <c r="AB85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6330,8 +6538,11 @@
       <c r="AB86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6410,8 +6621,11 @@
       <c r="AB87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6490,88 +6704,94 @@
       <c r="AB88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>30300</v>
+      </c>
+      <c r="E89" s="3">
         <v>13300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-6700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>50600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>17300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-7800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>17500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>44500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>2500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>9400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-4700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>29300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>11600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>4600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>8700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>12500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>13000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-5800</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-22900</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>53800</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>52500</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-22200</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-29100</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>106100</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>57700</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-1600</v>
       </c>
     </row>
-    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6600,88 +6820,92 @@
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
-    </row>
-    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC90" s="3"/>
+    </row>
+    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-1600</v>
+        <v>-1800</v>
       </c>
       <c r="E91" s="3">
         <v>-1600</v>
       </c>
       <c r="F91" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="G91" s="3">
         <v>-1000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-2900</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-2400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-3000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-2100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-3300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-2500</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-3900</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-3700</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-1900</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-2700</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-2300</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-3800</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-3200</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-14900</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-8100</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-11100</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-4600</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-11000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-6200</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-4600</v>
       </c>
     </row>
-    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6760,8 +6984,11 @@
       <c r="AB92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6840,88 +7067,94 @@
       <c r="AB93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="E94" s="3">
         <v>-3100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-2600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>19100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-2900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-2300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-2500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-3200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-2500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>20800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-3200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-1900</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-600</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-36800</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>213300</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>11000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-6800</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>28200</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-7700</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-62800</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-11900</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-12300</v>
       </c>
     </row>
-    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6950,8 +7183,9 @@
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
-    </row>
-    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC95" s="3"/>
+    </row>
+    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6959,11 +7193,11 @@
         <v>0</v>
       </c>
       <c r="E96" s="3">
+        <v>0</v>
+      </c>
+      <c r="F96" s="3">
         <v>-2200</v>
       </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
       <c r="G96" s="3">
         <v>0</v>
       </c>
@@ -6971,11 +7205,11 @@
         <v>0</v>
       </c>
       <c r="I96" s="3">
+        <v>0</v>
+      </c>
+      <c r="J96" s="3">
         <v>-2300</v>
       </c>
-      <c r="J96" s="3">
-        <v>0</v>
-      </c>
       <c r="K96" s="3">
         <v>0</v>
       </c>
@@ -6983,11 +7217,11 @@
         <v>0</v>
       </c>
       <c r="M96" s="3">
+        <v>0</v>
+      </c>
+      <c r="N96" s="3">
         <v>-2400</v>
       </c>
-      <c r="N96" s="3">
-        <v>0</v>
-      </c>
       <c r="O96" s="3">
         <v>0</v>
       </c>
@@ -6995,11 +7229,11 @@
         <v>0</v>
       </c>
       <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+      <c r="R96" s="3">
         <v>-2400</v>
       </c>
-      <c r="R96" s="3">
-        <v>0</v>
-      </c>
       <c r="S96" s="3">
         <v>0</v>
       </c>
@@ -7007,31 +7241,34 @@
         <v>0</v>
       </c>
       <c r="U96" s="3">
-        <v>-2400</v>
+        <v>0</v>
       </c>
       <c r="V96" s="3">
         <v>-2400</v>
       </c>
       <c r="W96" s="3">
-        <v>0</v>
+        <v>-2400</v>
       </c>
       <c r="X96" s="3">
         <v>0</v>
       </c>
       <c r="Y96" s="3">
-        <v>-2400</v>
+        <v>0</v>
       </c>
       <c r="Z96" s="3">
         <v>-2400</v>
       </c>
       <c r="AA96" s="3">
-        <v>0</v>
+        <v>-2400</v>
       </c>
       <c r="AB96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7110,8 +7347,11 @@
       <c r="AB97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7190,8 +7430,11 @@
       <c r="AB98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7270,244 +7513,256 @@
       <c r="AB99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-49700</v>
+      </c>
+      <c r="E100" s="3">
         <v>-4100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>2300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-57500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>4500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>5500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-5700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-40300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-6200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-1900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-3700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-19800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-13200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-46600</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-1800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-32500</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-10000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-1200</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-195200</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-99500</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-12100</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-40800</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-9600</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-18000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-7500</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E101" s="3">
         <v>-400</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>500</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>200</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-1500</v>
       </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
       <c r="I101" s="3">
+        <v>0</v>
+      </c>
+      <c r="J101" s="3">
         <v>-800</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-5800</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-4900</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>900</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-2200</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-2900</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>1800</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>1900</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>1400</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>8400</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-2200</v>
-      </c>
-      <c r="T101" s="3">
-        <v>400</v>
       </c>
       <c r="U101" s="3">
         <v>400</v>
       </c>
       <c r="V101" s="3">
+        <v>400</v>
+      </c>
+      <c r="W101" s="3">
         <v>-4700</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-2700</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>1800</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-700</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-4400</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-2300</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>2700</v>
       </c>
     </row>
-    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-21300</v>
+      </c>
+      <c r="E102" s="3">
         <v>5700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-6500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>12400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>17300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-4600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>8500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-3000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-9700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>6900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-13800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>4100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>21000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-43300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>6400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-11400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-43300</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-4400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-39300</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>30900</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-33100</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-47000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>20900</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>35900</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-11500</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/EPAC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/EPAC_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="92">
   <si>
     <t>EPAC</t>
   </si>
@@ -656,378 +656,391 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AC102"/>
+  <dimension ref="A5:AD102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45535</v>
+      </c>
+      <c r="E7" s="2">
         <v>45443</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45351</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45260</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45169</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45077</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44985</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44895</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44804</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44712</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44620</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44530</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44439</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44347</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44255</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44165</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44074</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43982</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43890</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43799</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43708</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43616</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43524</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43434</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43343</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43251</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43159</v>
       </c>
     </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>158700</v>
+      </c>
+      <c r="E8" s="3">
         <v>150400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>138400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>142000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>160600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>156300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>142000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>139400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>151800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>151900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>136600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>130900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>145400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>143100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>120700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>119400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>111400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>101900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>133400</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>146700</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>654800</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>178100</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>159800</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>158600</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>641300</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>317100</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>275200</v>
       </c>
     </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>81300</v>
+      </c>
+      <c r="E9" s="3">
         <v>71900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>66800</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>67600</v>
       </c>
-      <c r="G9" s="3">
-        <v>80800</v>
-      </c>
       <c r="H9" s="3">
+        <v>81400</v>
+      </c>
+      <c r="I9" s="3">
         <v>78000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>71400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>71500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>78100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>79800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>76600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>71300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>79200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>76300</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>65900</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>64200</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>66900</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>59900</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>71300</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>78000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>362100</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>96100</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>88500</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>88200</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>358000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>200600</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>185500</v>
       </c>
     </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>77400</v>
+      </c>
+      <c r="E10" s="3">
         <v>78500</v>
       </c>
-      <c r="E10" s="3">
-        <v>71600</v>
-      </c>
       <c r="F10" s="3">
+        <v>71700</v>
+      </c>
+      <c r="G10" s="3">
         <v>74400</v>
       </c>
-      <c r="G10" s="3">
-        <v>79800</v>
-      </c>
       <c r="H10" s="3">
+        <v>79200</v>
+      </c>
+      <c r="I10" s="3">
         <v>78300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>70600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>67900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>73700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>72100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>60000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>59600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>66200</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>66800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>54800</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>55200</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>44500</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>42000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>62100</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>68700</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>292700</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>82000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>71300</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>70400</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>283300</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>116500</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>89700</v>
       </c>
     </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1057,13 +1070,14 @@
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
-    </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD11" s="3"/>
+    </row>
+    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>8</v>
+      <c r="D12" s="3">
+        <v>12400</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>8</v>
@@ -1074,8 +1088,8 @@
       <c r="G12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H12" s="3" t="s">
-        <v>8</v>
+      <c r="H12" s="3">
+        <v>9000</v>
       </c>
       <c r="I12" s="3" t="s">
         <v>8</v>
@@ -1140,8 +1154,11 @@
       <c r="AC12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1223,91 +1240,97 @@
       <c r="AC13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>7200</v>
+      </c>
+      <c r="E14" s="3">
         <v>3700</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>2000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>3700</v>
       </c>
-      <c r="G14" s="3">
-        <v>4000</v>
-      </c>
       <c r="H14" s="3">
+        <v>3400</v>
+      </c>
+      <c r="I14" s="3">
         <v>8200</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>14400</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>10400</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>4300</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>500</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>2900</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>2700</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>5600</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>-3800</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>1100</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>300</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>1400</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>1000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>1200</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>600</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>27000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>-11900</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>3600</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>23400</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>13500</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>1200</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>6400</v>
       </c>
     </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1321,34 +1344,34 @@
         <v>800</v>
       </c>
       <c r="G15" s="3">
+        <v>800</v>
+      </c>
+      <c r="H15" s="3">
         <v>1000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>1400</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>1300</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>1400</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>1600</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>1800</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>1900</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>2000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>1800</v>
-      </c>
-      <c r="P15" s="3">
-        <v>2100</v>
       </c>
       <c r="Q15" s="3">
         <v>2100</v>
@@ -1357,40 +1380,43 @@
         <v>2100</v>
       </c>
       <c r="S15" s="3">
-        <v>2200</v>
+        <v>2100</v>
       </c>
       <c r="T15" s="3">
         <v>2200</v>
       </c>
       <c r="U15" s="3">
+        <v>2200</v>
+      </c>
+      <c r="V15" s="3">
         <v>2100</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>1900</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>8900</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>2800</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>1900</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>2300</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>9300</v>
-      </c>
-      <c r="AB15" s="3">
-        <v>5200</v>
       </c>
       <c r="AC15" s="3">
         <v>5200</v>
       </c>
-    </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD15" s="3">
+        <v>5200</v>
+      </c>
+    </row>
+    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1417,174 +1443,181 @@
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
-    </row>
-    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD16" s="3"/>
+    </row>
+    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>117000</v>
+        <v>122400</v>
       </c>
       <c r="E17" s="3">
-        <v>108900</v>
+        <v>113300</v>
       </c>
       <c r="F17" s="3">
-        <v>113300</v>
+        <v>106900</v>
       </c>
       <c r="G17" s="3">
-        <v>128400</v>
+        <v>109600</v>
       </c>
       <c r="H17" s="3">
-        <v>130800</v>
+        <v>125900</v>
       </c>
       <c r="I17" s="3">
-        <v>128000</v>
+        <v>122700</v>
       </c>
       <c r="J17" s="3">
+        <v>113600</v>
+      </c>
+      <c r="K17" s="3">
         <v>127100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>138700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>145300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>132100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>124500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>131800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>120400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>114900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>110400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>108100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>103900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>124800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>132300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>607200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>139900</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>147300</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>167100</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>591100</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>284400</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>265400</v>
       </c>
     </row>
-    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>33400</v>
+        <v>36300</v>
       </c>
       <c r="E18" s="3">
-        <v>29500</v>
+        <v>37100</v>
       </c>
       <c r="F18" s="3">
-        <v>28700</v>
+        <v>31500</v>
       </c>
       <c r="G18" s="3">
-        <v>32200</v>
+        <v>32400</v>
       </c>
       <c r="H18" s="3">
-        <v>25500</v>
+        <v>34700</v>
       </c>
       <c r="I18" s="3">
-        <v>14000</v>
+        <v>33600</v>
       </c>
       <c r="J18" s="3">
+        <v>28400</v>
+      </c>
+      <c r="K18" s="3">
         <v>12300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>13100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>6600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>4500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>6400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>13600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>22700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>5800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>9000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>3300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-2000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>8600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>14400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>47600</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>38200</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>12500</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-8500</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>50200</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>32700</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>9800</v>
       </c>
     </row>
-    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1614,197 +1647,204 @@
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
-    </row>
-    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD19" s="3"/>
+    </row>
+    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>500</v>
+      </c>
+      <c r="E20" s="3">
+        <v>500</v>
+      </c>
+      <c r="F20" s="3">
+        <v>500</v>
+      </c>
+      <c r="G20" s="3">
+        <v>1000</v>
+      </c>
+      <c r="H20" s="3">
+        <v>700</v>
+      </c>
+      <c r="I20" s="3">
+        <v>500</v>
+      </c>
+      <c r="J20" s="3">
+        <v>700</v>
+      </c>
+      <c r="K20" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="L20" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="M20" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="N20" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="O20" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="P20" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="Q20" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="R20" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="S20" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="T20" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="U20" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="V20" s="3">
         <v>-3900</v>
       </c>
-      <c r="E20" s="3">
-        <v>-4200</v>
-      </c>
-      <c r="F20" s="3">
-        <v>-4700</v>
-      </c>
-      <c r="G20" s="3">
-        <v>-3900</v>
-      </c>
-      <c r="H20" s="3">
-        <v>-3800</v>
-      </c>
-      <c r="I20" s="3">
-        <v>-3900</v>
-      </c>
-      <c r="J20" s="3">
-        <v>-3500</v>
-      </c>
-      <c r="K20" s="3">
-        <v>-3000</v>
-      </c>
-      <c r="L20" s="3">
-        <v>-1200</v>
-      </c>
-      <c r="M20" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="N20" s="3">
-        <v>-1400</v>
-      </c>
-      <c r="O20" s="3">
-        <v>-1100</v>
-      </c>
-      <c r="P20" s="3">
-        <v>-1800</v>
-      </c>
-      <c r="Q20" s="3">
-        <v>-2200</v>
-      </c>
-      <c r="R20" s="3">
-        <v>-2000</v>
-      </c>
-      <c r="S20" s="3">
-        <v>-2200</v>
-      </c>
-      <c r="T20" s="3">
-        <v>-3400</v>
-      </c>
-      <c r="U20" s="3">
-        <v>-3900</v>
-      </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-7100</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-28800</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-6400</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-7700</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-7900</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-31000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-7700</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-8200</v>
       </c>
     </row>
-    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>32700</v>
+        <v>36700</v>
       </c>
       <c r="E21" s="3">
-        <v>28600</v>
+        <v>37300</v>
       </c>
       <c r="F21" s="3">
-        <v>27400</v>
+        <v>31800</v>
       </c>
       <c r="G21" s="3">
-        <v>32100</v>
+        <v>32200</v>
       </c>
       <c r="H21" s="3">
-        <v>25700</v>
+        <v>35100</v>
       </c>
       <c r="I21" s="3">
-        <v>14400</v>
+        <v>34400</v>
       </c>
       <c r="J21" s="3">
+        <v>29000</v>
+      </c>
+      <c r="K21" s="3">
         <v>13000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>14700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>10300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>8400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>10100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>17600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>26300</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>9100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>12500</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>6500</v>
       </c>
-      <c r="T21" s="3">
-        <v>0</v>
-      </c>
       <c r="U21" s="3">
+        <v>0</v>
+      </c>
+      <c r="V21" s="3">
         <v>10000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>12100</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>38900</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>41100</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>16100</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-11300</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>39600</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>35400</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>11900</v>
       </c>
     </row>
-    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>0</v>
+        <v>4300</v>
       </c>
       <c r="E22" s="3">
-        <v>0</v>
+        <v>3400</v>
       </c>
       <c r="F22" s="3">
-        <v>0</v>
+        <v>3700</v>
       </c>
       <c r="G22" s="3">
-        <v>0</v>
+        <v>3700</v>
       </c>
       <c r="H22" s="3">
-        <v>0</v>
+        <v>4900</v>
       </c>
       <c r="I22" s="3">
-        <v>0</v>
+        <v>3300</v>
       </c>
       <c r="J22" s="3">
-        <v>0</v>
+        <v>3100</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -1863,174 +1903,183 @@
       <c r="AC22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>26800</v>
+      </c>
+      <c r="E23" s="3">
         <v>29400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>25300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>24000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>28300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>21700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>10100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>8800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>10100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>5400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>3500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>5000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>12400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>20900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>3600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>7100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>1100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-5300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>4700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>7300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>18700</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>31800</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>4800</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-16400</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>19200</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>25000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>3400</v>
+      </c>
+      <c r="E24" s="3">
         <v>6800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>7400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>5700</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>5200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>4700</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>3000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>2400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>1400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>1300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>1800</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-4400</v>
       </c>
-      <c r="Q24" s="3">
-        <v>0</v>
-      </c>
       <c r="R24" s="3">
+        <v>0</v>
+      </c>
+      <c r="S24" s="3">
         <v>2300</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>3900</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-400</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>800</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>1000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>16500</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>5000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>4000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>100</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>14500</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-4000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>19800</v>
       </c>
     </row>
-    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2112,174 +2161,183 @@
       <c r="AC25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>23400</v>
+      </c>
+      <c r="E26" s="3">
         <v>22600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>17900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>18300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>23100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>17000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>7200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>6400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>10200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>4100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>2100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>3200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>12500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>25300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>3600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>4800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-2800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-4900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>3900</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>6400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>2300</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>26900</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>800</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-16400</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>4700</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>29000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-18200</v>
       </c>
     </row>
-    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>22600</v>
+        <v>24400</v>
       </c>
       <c r="E27" s="3">
-        <v>17900</v>
+        <v>25800</v>
       </c>
       <c r="F27" s="3">
-        <v>18300</v>
+        <v>17800</v>
       </c>
       <c r="G27" s="3">
-        <v>23100</v>
+        <v>17700</v>
       </c>
       <c r="H27" s="3">
-        <v>17000</v>
+        <v>22200</v>
       </c>
       <c r="I27" s="3">
-        <v>7200</v>
+        <v>12400</v>
       </c>
       <c r="J27" s="3">
+        <v>4500</v>
+      </c>
+      <c r="K27" s="3">
         <v>6400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>10200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>4100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>2100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>3200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>12500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>25300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>3600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>4800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-2800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-4900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>3900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>6400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>2300</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>26900</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>800</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-16400</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>4700</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>29000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-18200</v>
       </c>
     </row>
-    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2361,91 +2419,97 @@
       <c r="AC28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E29" s="3">
         <v>3200</v>
       </c>
-      <c r="E29" s="3">
+      <c r="F29" s="3">
         <v>-100</v>
       </c>
-      <c r="F29" s="3">
+      <c r="G29" s="3">
         <v>-600</v>
       </c>
-      <c r="G29" s="3">
+      <c r="H29" s="3">
         <v>-900</v>
       </c>
-      <c r="H29" s="3">
+      <c r="I29" s="3">
         <v>-4600</v>
       </c>
-      <c r="I29" s="3">
+      <c r="J29" s="3">
         <v>-2700</v>
       </c>
-      <c r="J29" s="3">
+      <c r="K29" s="3">
         <v>1000</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>-200</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>-2400</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>-900</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>-400</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>-7300</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>-200</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>-400</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <v>-200</v>
       </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
         <v>4200</v>
       </c>
-      <c r="T29" s="3">
+      <c r="U29" s="3">
         <v>-100</v>
       </c>
-      <c r="U29" s="3">
+      <c r="V29" s="3">
         <v>-1800</v>
       </c>
-      <c r="V29" s="3">
+      <c r="W29" s="3">
         <v>-4300</v>
       </c>
-      <c r="W29" s="3">
+      <c r="X29" s="3">
         <v>-251400</v>
       </c>
-      <c r="X29" s="3">
+      <c r="Y29" s="3">
         <v>5600</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Z29" s="3">
         <v>2000</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="AA29" s="3">
         <v>-1000</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AB29" s="3">
         <v>-31400</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AC29" s="3">
         <v>12900</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AD29" s="3">
         <v>-8400</v>
       </c>
     </row>
-    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2527,8 +2591,11 @@
       <c r="AC30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2610,174 +2677,183 @@
       <c r="AC31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E32" s="3">
+        <v>-500</v>
+      </c>
+      <c r="F32" s="3">
+        <v>-500</v>
+      </c>
+      <c r="G32" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="H32" s="3">
+        <v>-700</v>
+      </c>
+      <c r="I32" s="3">
+        <v>-500</v>
+      </c>
+      <c r="J32" s="3">
+        <v>-700</v>
+      </c>
+      <c r="K32" s="3">
+        <v>3500</v>
+      </c>
+      <c r="L32" s="3">
+        <v>3000</v>
+      </c>
+      <c r="M32" s="3">
+        <v>1200</v>
+      </c>
+      <c r="N32" s="3">
+        <v>1000</v>
+      </c>
+      <c r="O32" s="3">
+        <v>1400</v>
+      </c>
+      <c r="P32" s="3">
+        <v>1100</v>
+      </c>
+      <c r="Q32" s="3">
+        <v>1800</v>
+      </c>
+      <c r="R32" s="3">
+        <v>2200</v>
+      </c>
+      <c r="S32" s="3">
+        <v>2000</v>
+      </c>
+      <c r="T32" s="3">
+        <v>2200</v>
+      </c>
+      <c r="U32" s="3">
+        <v>3400</v>
+      </c>
+      <c r="V32" s="3">
         <v>3900</v>
       </c>
-      <c r="E32" s="3">
-        <v>4200</v>
-      </c>
-      <c r="F32" s="3">
-        <v>4700</v>
-      </c>
-      <c r="G32" s="3">
-        <v>3900</v>
-      </c>
-      <c r="H32" s="3">
-        <v>3800</v>
-      </c>
-      <c r="I32" s="3">
-        <v>3900</v>
-      </c>
-      <c r="J32" s="3">
-        <v>3500</v>
-      </c>
-      <c r="K32" s="3">
-        <v>3000</v>
-      </c>
-      <c r="L32" s="3">
-        <v>1200</v>
-      </c>
-      <c r="M32" s="3">
-        <v>1000</v>
-      </c>
-      <c r="N32" s="3">
-        <v>1400</v>
-      </c>
-      <c r="O32" s="3">
-        <v>1100</v>
-      </c>
-      <c r="P32" s="3">
-        <v>1800</v>
-      </c>
-      <c r="Q32" s="3">
-        <v>2200</v>
-      </c>
-      <c r="R32" s="3">
-        <v>2000</v>
-      </c>
-      <c r="S32" s="3">
-        <v>2200</v>
-      </c>
-      <c r="T32" s="3">
-        <v>3400</v>
-      </c>
-      <c r="U32" s="3">
-        <v>3900</v>
-      </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>7100</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>28800</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>6400</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>7700</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>7900</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>31000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>7700</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>8200</v>
       </c>
     </row>
-    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>24400</v>
+      </c>
+      <c r="E33" s="3">
         <v>25800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>17800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>17700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>22200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>12400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>4500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>7500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>10000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>2800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>5300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>25000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>3200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>4600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>1400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-5000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>2200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>2100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-249100</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>32400</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>2800</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-17500</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-26600</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>41900</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-26600</v>
       </c>
     </row>
-    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2859,179 +2935,188 @@
       <c r="AC34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>24400</v>
+      </c>
+      <c r="E35" s="3">
         <v>25800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>17800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>17700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>22200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>12400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>4500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>7500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>10000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>2800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>5300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>25000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>3200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>4600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>1400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-5000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>2200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>2100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-249100</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>32400</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>2800</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-17500</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-26600</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>41900</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-26600</v>
       </c>
     </row>
-    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45535</v>
+      </c>
+      <c r="E38" s="2">
         <v>45443</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45351</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45260</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45169</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45077</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44985</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44895</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44804</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44712</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44620</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44530</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44439</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44347</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44255</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44165</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44074</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43982</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43890</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43799</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43708</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43616</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43524</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43434</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43343</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43251</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43159</v>
       </c>
     </row>
-    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3061,8 +3146,9 @@
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
-    </row>
-    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD39" s="3"/>
+    </row>
+    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3092,91 +3178,95 @@
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
-    </row>
-    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD40" s="3"/>
+    </row>
+    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>167100</v>
+      </c>
+      <c r="E41" s="3">
         <v>132400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>153700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>148000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>154400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>142000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>124700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>129200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>120700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>123700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>133400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>126500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>140400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>136300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>115300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>158600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>152200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>163600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>163400</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>206800</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>211200</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>201300</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>170400</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>203400</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>250500</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>189500</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>153600</v>
       </c>
     </row>
-    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3258,363 +3348,378 @@
       <c r="AC42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>108900</v>
+      </c>
+      <c r="E43" s="3">
         <v>113500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>102100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>101400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>101600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>106600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>101800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>99100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>109100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>120800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>116400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>114700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>111800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>119600</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>102700</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>95600</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>90300</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>98400</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>118500</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>127000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>125900</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>202800</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>210200</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>191200</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>123300</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>212300</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>210700</v>
       </c>
     </row>
-    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>72900</v>
+      </c>
+      <c r="E44" s="3">
         <v>79100</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>82900</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>80100</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>74800</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>93000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>94200</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>90700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>83700</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>86900</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>89500</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>83600</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>75300</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>74700</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>71800</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>70700</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>69200</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>78900</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>78000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>79500</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>77200</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>167600</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>161600</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>154800</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>72000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>167300</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>166200</v>
       </c>
     </row>
-    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>23400</v>
+      </c>
+      <c r="E45" s="3">
         <v>22900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>28700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>30500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>24800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>31800</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>34600</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>33700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>28900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>34900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>34700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>36200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>30000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>41200</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>35700</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>32900</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>29500</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>39000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>38200</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>39500</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>316100</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>44500</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>111000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>157900</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>625000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>58700</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>60600</v>
       </c>
     </row>
-    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>372300</v>
+      </c>
+      <c r="E46" s="3">
         <v>347800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>367300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>360000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>355600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>373400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>355300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>352700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>342400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>366300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>374100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>361100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>357400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>371800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>325400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>357800</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>341100</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>379800</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>398200</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>452700</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>730300</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>616200</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>653200</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>707300</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>1047200</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>627800</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>591000</v>
       </c>
     </row>
-    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -3673,174 +3778,183 @@
       <c r="AC47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>73200</v>
+      </c>
+      <c r="E48" s="3">
         <v>36200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>37000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>38000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>76700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>41800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>41200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>41800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>84600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>44400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>46500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>47700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>100200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>50100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>61300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>60200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>110100</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>111600</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>116600</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>111700</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>56700</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>90000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>83100</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>79200</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>145200</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>100800</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>102400</v>
       </c>
     </row>
-    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>305700</v>
+      </c>
+      <c r="E49" s="3">
         <v>303100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>303000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>304300</v>
-      </c>
-      <c r="G49" s="3">
-        <v>303800</v>
       </c>
       <c r="H49" s="3">
         <v>303800</v>
       </c>
       <c r="I49" s="3">
+        <v>303800</v>
+      </c>
+      <c r="J49" s="3">
         <v>301900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>302700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>299500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>312400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>322000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>324700</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>332100</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>344600</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>343700</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>341100</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>343500</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>334000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>338300</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>315200</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>312800</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>649700</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>630200</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>630100</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>351800</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>749000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>762500</v>
       </c>
     </row>
-    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3922,8 +4036,11 @@
       <c r="AC50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4005,91 +4122,97 @@
       <c r="AC51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>11500</v>
+      </c>
+      <c r="E52" s="3">
         <v>62400</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>62000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>63400</v>
       </c>
-      <c r="G52" s="3">
-        <v>26400</v>
-      </c>
       <c r="H52" s="3">
+        <v>10700</v>
+      </c>
+      <c r="I52" s="3">
         <v>74100</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>74800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>77300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>30800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>74200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>78900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>79000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>30500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>76200</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>78600</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>79500</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>29500</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>26100</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>26200</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>28900</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>24400</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>37300</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>36500</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>33500</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>31200</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>27200</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>24300</v>
       </c>
     </row>
-    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4171,91 +4294,97 @@
       <c r="AC53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>777300</v>
+      </c>
+      <c r="E54" s="3">
         <v>749500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>769300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>765600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>762600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>793100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>773200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>774400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>757300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>797300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>821500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>812500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>820200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>842700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>809000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>838600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>824300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>851500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>879300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>908500</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1124300</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1393200</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1403100</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1450000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1485200</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1504800</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>1480300</v>
       </c>
     </row>
-    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4285,8 +4414,9 @@
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
-    </row>
-    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD55" s="3"/>
+    </row>
+    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4316,120 +4446,124 @@
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
-    </row>
-    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD56" s="3"/>
+    </row>
+    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>43400</v>
+      </c>
+      <c r="E57" s="3">
         <v>41700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>44000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>45500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>50500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>47200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>54300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>74700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>72500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>65700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>66400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>63500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>62000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>59900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>49700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>47000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>45100</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>52100</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>62300</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>68800</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>76900</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>126100</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>122500</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>124100</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>69600</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>142200</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>136900</v>
       </c>
     </row>
-    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>5000</v>
+        <v>14500</v>
       </c>
       <c r="E58" s="3">
         <v>5000</v>
       </c>
       <c r="F58" s="3">
+        <v>5000</v>
+      </c>
+      <c r="G58" s="3">
         <v>4400</v>
       </c>
-      <c r="G58" s="3">
-        <v>3800</v>
-      </c>
       <c r="H58" s="3">
+        <v>13500</v>
+      </c>
+      <c r="I58" s="3">
         <v>3100</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>2500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>4000</v>
-      </c>
-      <c r="L58" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="M58" s="3" t="s">
         <v>8</v>
@@ -4446,8 +4580,8 @@
       <c r="Q58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R58" s="3">
-        <v>0</v>
+      <c r="R58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="S58" s="3">
         <v>0</v>
@@ -4462,13 +4596,13 @@
         <v>0</v>
       </c>
       <c r="W58" s="3">
+        <v>0</v>
+      </c>
+      <c r="X58" s="3">
         <v>7500</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>6300</v>
-      </c>
-      <c r="Y58" s="3">
-        <v>30000</v>
       </c>
       <c r="Z58" s="3">
         <v>30000</v>
@@ -4482,206 +4616,215 @@
       <c r="AC58" s="3">
         <v>30000</v>
       </c>
-    </row>
-    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD58" s="3">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>75300</v>
+        <v>45700</v>
       </c>
       <c r="E59" s="3">
-        <v>69100</v>
+        <v>51000</v>
       </c>
       <c r="F59" s="3">
-        <v>77100</v>
+        <v>48700</v>
       </c>
       <c r="G59" s="3">
-        <v>93900</v>
+        <v>55300</v>
       </c>
       <c r="H59" s="3">
-        <v>89900</v>
+        <v>50900</v>
       </c>
       <c r="I59" s="3">
-        <v>86600</v>
+        <v>61400</v>
       </c>
       <c r="J59" s="3">
+        <v>62400</v>
+      </c>
+      <c r="K59" s="3">
         <v>77600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>76700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>68800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>73900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>68200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>72800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>74500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>65500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>62800</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>60500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>70400</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>67300</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>88500</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>216000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>101200</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>125600</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>178300</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>298600</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>129100</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>107600</v>
       </c>
     </row>
-    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>129400</v>
+      </c>
+      <c r="E60" s="3">
         <v>122000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>118100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>127000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>148100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>140200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>143400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>154100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>153200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>134500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>140300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>131600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>134800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>134400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>115300</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>109700</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>105500</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>122500</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>129600</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>157300</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>300400</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>233600</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>278100</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>332400</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>354000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>301300</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>274500</v>
       </c>
     </row>
-    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>214700</v>
+      </c>
+      <c r="E61" s="3">
         <v>190700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>239900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>240100</v>
       </c>
-      <c r="G61" s="3">
-        <v>210300</v>
-      </c>
       <c r="H61" s="3">
+        <v>239600</v>
+      </c>
+      <c r="I61" s="3">
         <v>231500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>206800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>200400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>200000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>205000</v>
-      </c>
-      <c r="M61" s="3">
-        <v>175000</v>
       </c>
       <c r="N61" s="3">
         <v>175000</v>
@@ -4690,132 +4833,138 @@
         <v>175000</v>
       </c>
       <c r="P61" s="3">
+        <v>175000</v>
+      </c>
+      <c r="Q61" s="3">
         <v>195000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>210000</v>
-      </c>
-      <c r="R61" s="3">
-        <v>255000</v>
       </c>
       <c r="S61" s="3">
         <v>255000</v>
       </c>
       <c r="T61" s="3">
+        <v>255000</v>
+      </c>
+      <c r="U61" s="3">
         <v>286500</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>286400</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>286200</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>452900</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>469000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>455600</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>495400</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>502700</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>510000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>517300</v>
       </c>
     </row>
-    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>71000</v>
+        <v>27500</v>
       </c>
       <c r="E62" s="3">
-        <v>74300</v>
+        <v>57500</v>
       </c>
       <c r="F62" s="3">
-        <v>76800</v>
+        <v>57600</v>
       </c>
       <c r="G62" s="3">
-        <v>77500</v>
+        <v>60600</v>
       </c>
       <c r="H62" s="3">
+        <v>32400</v>
+      </c>
+      <c r="I62" s="3">
+        <v>65000</v>
+      </c>
+      <c r="J62" s="3">
+        <v>62000</v>
+      </c>
+      <c r="K62" s="3">
+        <v>85600</v>
+      </c>
+      <c r="L62" s="3">
+        <v>85500</v>
+      </c>
+      <c r="M62" s="3">
+        <v>91500</v>
+      </c>
+      <c r="N62" s="3">
+        <v>93100</v>
+      </c>
+      <c r="O62" s="3">
+        <v>96000</v>
+      </c>
+      <c r="P62" s="3">
+        <v>98300</v>
+      </c>
+      <c r="Q62" s="3">
+        <v>96300</v>
+      </c>
+      <c r="R62" s="3">
+        <v>102400</v>
+      </c>
+      <c r="S62" s="3">
+        <v>105900</v>
+      </c>
+      <c r="T62" s="3">
+        <v>104500</v>
+      </c>
+      <c r="U62" s="3">
+        <v>106200</v>
+      </c>
+      <c r="V62" s="3">
+        <v>109000</v>
+      </c>
+      <c r="W62" s="3">
+        <v>111800</v>
+      </c>
+      <c r="X62" s="3">
+        <v>69700</v>
+      </c>
+      <c r="Y62" s="3">
+        <v>83200</v>
+      </c>
+      <c r="Z62" s="3">
+        <v>83700</v>
+      </c>
+      <c r="AA62" s="3">
         <v>84700</v>
       </c>
-      <c r="I62" s="3">
-        <v>82200</v>
-      </c>
-      <c r="J62" s="3">
-        <v>85600</v>
-      </c>
-      <c r="K62" s="3">
-        <v>85500</v>
-      </c>
-      <c r="L62" s="3">
-        <v>91500</v>
-      </c>
-      <c r="M62" s="3">
-        <v>93100</v>
-      </c>
-      <c r="N62" s="3">
-        <v>96000</v>
-      </c>
-      <c r="O62" s="3">
-        <v>98300</v>
-      </c>
-      <c r="P62" s="3">
-        <v>96300</v>
-      </c>
-      <c r="Q62" s="3">
-        <v>102400</v>
-      </c>
-      <c r="R62" s="3">
-        <v>105900</v>
-      </c>
-      <c r="S62" s="3">
-        <v>104500</v>
-      </c>
-      <c r="T62" s="3">
-        <v>106200</v>
-      </c>
-      <c r="U62" s="3">
-        <v>109000</v>
-      </c>
-      <c r="V62" s="3">
-        <v>111800</v>
-      </c>
-      <c r="W62" s="3">
-        <v>69700</v>
-      </c>
-      <c r="X62" s="3">
-        <v>83200</v>
-      </c>
-      <c r="Y62" s="3">
-        <v>83700</v>
-      </c>
-      <c r="Z62" s="3">
-        <v>84700</v>
-      </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>69800</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>92400</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>99200</v>
       </c>
     </row>
-    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4897,8 +5046,11 @@
       <c r="AC63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4980,8 +5132,11 @@
       <c r="AC64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5063,91 +5218,97 @@
       <c r="AC65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>385300</v>
+      </c>
+      <c r="E66" s="3">
         <v>383700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>432400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>443900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>436000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>456500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>432400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>440100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>438700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>431000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>408400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>402700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>408000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>425800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>427600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>470600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>465100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>515300</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>525000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>555300</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>823100</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>785700</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>817400</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>912500</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>926500</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>903800</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>891000</v>
       </c>
     </row>
-    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5177,8 +5338,9 @@
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
-    </row>
-    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD67" s="3"/>
+    </row>
+    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5260,8 +5422,11 @@
       <c r="AC68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5343,8 +5508,11 @@
       <c r="AC69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5426,8 +5594,11 @@
       <c r="AC70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5509,91 +5680,97 @@
       <c r="AC71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>261900</v>
+      </c>
+      <c r="E72" s="3">
         <v>245300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>222000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>1028900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>1011100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>991100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>978700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>974200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>966800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>959000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>957300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>956100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>953300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>950500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>925500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>922300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>917700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>918600</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>923600</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>921500</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>915500</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>1184700</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>1152300</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>1149600</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>1167000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>1207100</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>1178000</v>
       </c>
     </row>
-    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5675,8 +5852,11 @@
       <c r="AC73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5758,8 +5938,11 @@
       <c r="AC74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5841,91 +6024,97 @@
       <c r="AC75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>392000</v>
+      </c>
+      <c r="E76" s="3">
         <v>365800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>336900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>321700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>326600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>336600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>340800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>334300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>318600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>366300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>413000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>409800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>412200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>416900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>381400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>367900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>359200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>336300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>354400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>353300</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>301200</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>607400</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>585600</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>537600</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>558700</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>601000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>589300</v>
       </c>
     </row>
-    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6007,179 +6196,188 @@
       <c r="AC77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45535</v>
+      </c>
+      <c r="E80" s="2">
         <v>45443</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45351</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45260</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45169</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45077</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44985</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44895</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44804</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44712</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44620</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44530</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44439</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44347</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44255</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44165</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44074</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43982</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43890</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43799</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43708</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43616</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43524</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43434</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43343</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43251</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43159</v>
       </c>
     </row>
-    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>24400</v>
+      </c>
+      <c r="E81" s="3">
         <v>25800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>17800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>17700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>22200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>12400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>4500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>7500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>10000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>2800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>5300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>25000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>3200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>4600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>1400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-5000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>2200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>2100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-249100</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>32400</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>2800</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-17500</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-26600</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>41900</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-26600</v>
       </c>
     </row>
-    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6209,49 +6407,50 @@
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
-    </row>
-    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD82" s="3"/>
+    </row>
+    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>3200</v>
+        <v>2800</v>
       </c>
       <c r="E83" s="3">
-        <v>3300</v>
+        <v>2700</v>
       </c>
       <c r="F83" s="3">
-        <v>3400</v>
+        <v>2900</v>
       </c>
       <c r="G83" s="3">
-        <v>3800</v>
+        <v>2800</v>
       </c>
       <c r="H83" s="3">
-        <v>4100</v>
+        <v>3000</v>
       </c>
       <c r="I83" s="3">
+        <v>3000</v>
+      </c>
+      <c r="J83" s="3">
+        <v>3100</v>
+      </c>
+      <c r="K83" s="3">
         <v>4200</v>
       </c>
-      <c r="J83" s="3">
-        <v>4200</v>
-      </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>4600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>4800</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>5000</v>
-      </c>
-      <c r="N83" s="3">
-        <v>5200</v>
       </c>
       <c r="O83" s="3">
         <v>5200</v>
       </c>
       <c r="P83" s="3">
-        <v>5500</v>
+        <v>5200</v>
       </c>
       <c r="Q83" s="3">
         <v>5500</v>
@@ -6260,7 +6459,7 @@
         <v>5500</v>
       </c>
       <c r="S83" s="3">
-        <v>5300</v>
+        <v>5500</v>
       </c>
       <c r="T83" s="3">
         <v>5300</v>
@@ -6269,31 +6468,34 @@
         <v>5300</v>
       </c>
       <c r="V83" s="3">
+        <v>5300</v>
+      </c>
+      <c r="W83" s="3">
         <v>4800</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>20200</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>9300</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>7500</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>8900</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>40700</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>10400</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>10300</v>
       </c>
     </row>
-    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6375,8 +6577,11 @@
       <c r="AC84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6458,8 +6663,11 @@
       <c r="AC85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6541,8 +6749,11 @@
       <c r="AC86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6624,8 +6835,11 @@
       <c r="AC87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6707,91 +6921,97 @@
       <c r="AC88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>44400</v>
+      </c>
+      <c r="E89" s="3">
         <v>30300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>13300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-6700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>50600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>17300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-7800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>17500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>44500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>2500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>9400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-4700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>29300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>11600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>4600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>8700</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>12500</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>13000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-5800</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-22900</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>53800</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>52500</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-22200</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-29100</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>106100</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>57700</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-1600</v>
       </c>
     </row>
-    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6821,91 +7041,95 @@
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
-    </row>
-    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD90" s="3"/>
+    </row>
+    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-6400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="G91" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="H91" s="3">
         <v>-1600</v>
       </c>
-      <c r="F91" s="3">
-        <v>-1600</v>
-      </c>
-      <c r="G91" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="J91" s="3">
         <v>-2900</v>
       </c>
-      <c r="I91" s="3">
-        <v>-2400</v>
-      </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-3000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-2100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-3300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-2500</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-3900</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-3700</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-1900</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-2700</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-2300</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-3800</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-3200</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-14900</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-8100</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-11100</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-4600</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-11000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-6200</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-4600</v>
       </c>
     </row>
-    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6987,8 +7211,11 @@
       <c r="AC92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7070,91 +7297,97 @@
       <c r="AC93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-6400</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-3100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-2600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>19100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-2900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-2300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-2500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-3200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-2500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>20800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-3200</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-1900</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-600</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-36800</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>213300</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>11000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-6800</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>28200</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-7700</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-62800</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-11900</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-12300</v>
       </c>
     </row>
-    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7184,8 +7417,9 @@
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
-    </row>
-    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD95" s="3"/>
+    </row>
+    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7196,10 +7430,10 @@
         <v>0</v>
       </c>
       <c r="F96" s="3">
-        <v>-2200</v>
+        <v>0</v>
       </c>
       <c r="G96" s="3">
-        <v>0</v>
+        <v>2200</v>
       </c>
       <c r="H96" s="3">
         <v>0</v>
@@ -7208,11 +7442,11 @@
         <v>0</v>
       </c>
       <c r="J96" s="3">
+        <v>0</v>
+      </c>
+      <c r="K96" s="3">
         <v>-2300</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
       <c r="L96" s="3">
         <v>0</v>
       </c>
@@ -7220,11 +7454,11 @@
         <v>0</v>
       </c>
       <c r="N96" s="3">
+        <v>0</v>
+      </c>
+      <c r="O96" s="3">
         <v>-2400</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
       <c r="P96" s="3">
         <v>0</v>
       </c>
@@ -7232,11 +7466,11 @@
         <v>0</v>
       </c>
       <c r="R96" s="3">
+        <v>0</v>
+      </c>
+      <c r="S96" s="3">
         <v>-2400</v>
       </c>
-      <c r="S96" s="3">
-        <v>0</v>
-      </c>
       <c r="T96" s="3">
         <v>0</v>
       </c>
@@ -7244,31 +7478,34 @@
         <v>0</v>
       </c>
       <c r="V96" s="3">
-        <v>-2400</v>
+        <v>0</v>
       </c>
       <c r="W96" s="3">
         <v>-2400</v>
       </c>
       <c r="X96" s="3">
-        <v>0</v>
+        <v>-2400</v>
       </c>
       <c r="Y96" s="3">
         <v>0</v>
       </c>
       <c r="Z96" s="3">
-        <v>-2400</v>
+        <v>0</v>
       </c>
       <c r="AA96" s="3">
         <v>-2400</v>
       </c>
       <c r="AB96" s="3">
-        <v>0</v>
+        <v>-2400</v>
       </c>
       <c r="AC96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7350,8 +7587,11 @@
       <c r="AC97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7433,8 +7673,11 @@
       <c r="AC98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7516,253 +7759,265 @@
       <c r="AC99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-4900</v>
+      </c>
+      <c r="E100" s="3">
         <v>-49700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-4100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>2300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-57500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>4500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>5500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-5700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-40300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-6200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-1900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-3700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-19800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-13200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-46600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-1800</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-32500</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-10000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-1200</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-195200</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-99500</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-12100</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-40800</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-9600</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-18000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-7500</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-200</v>
+        <v>200</v>
       </c>
       <c r="E101" s="3">
-        <v>-400</v>
+        <v>-1500</v>
       </c>
       <c r="F101" s="3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="G101" s="3">
-        <v>200</v>
+        <v>-800</v>
       </c>
       <c r="H101" s="3">
-        <v>-1500</v>
+        <v>-5800</v>
       </c>
       <c r="I101" s="3">
-        <v>0</v>
+        <v>-4900</v>
       </c>
       <c r="J101" s="3">
+        <v>900</v>
+      </c>
+      <c r="K101" s="3">
         <v>-800</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-5800</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-4900</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>900</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-2200</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-2900</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>1800</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>1900</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>1400</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>8400</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-2200</v>
-      </c>
-      <c r="U101" s="3">
-        <v>400</v>
       </c>
       <c r="V101" s="3">
         <v>400</v>
       </c>
       <c r="W101" s="3">
+        <v>400</v>
+      </c>
+      <c r="X101" s="3">
         <v>-4700</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-2700</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>1800</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-700</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-4400</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-2300</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>2700</v>
       </c>
     </row>
-    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>34700</v>
+      </c>
+      <c r="E102" s="3">
         <v>-21300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>5700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-6500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>12400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>17300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-4600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>8500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-3000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-9700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>6900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-13800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>4100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>21000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-43300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>6400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-11400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-43300</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-4400</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-39300</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>30900</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-33100</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-47000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>20900</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>35900</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-11500</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/EPAC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/EPAC_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="92">
   <si>
     <t>EPAC</t>
   </si>
@@ -656,391 +656,403 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AD102"/>
+  <dimension ref="A5:AE102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45626</v>
+      </c>
+      <c r="E7" s="2">
         <v>45535</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45443</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45351</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45260</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45169</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45077</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44985</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44895</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44804</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44712</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44620</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44530</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44439</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44347</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44255</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44165</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44074</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43982</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43890</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43799</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43708</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43616</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43524</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43434</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43343</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43251</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43159</v>
       </c>
     </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>145200</v>
+      </c>
+      <c r="E8" s="3">
         <v>158700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>150400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>138400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>142000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>160600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>156300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>142000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>139400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>151800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>151900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>136600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>130900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>145400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>143100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>120700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>119400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>111400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>101900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>133400</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>146700</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>654800</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>178100</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>159800</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>158600</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>641300</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>317100</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>275200</v>
       </c>
     </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>70500</v>
+      </c>
+      <c r="E9" s="3">
         <v>81300</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>71900</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>66800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>67600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>81400</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>78000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>71400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>71500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>78100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>79800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>76600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>71300</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>79200</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>76300</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>65900</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>64200</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>66900</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>59900</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>71300</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>78000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>362100</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>96100</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>88500</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>88200</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>358000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>200600</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>185500</v>
       </c>
     </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>74700</v>
+      </c>
+      <c r="E10" s="3">
         <v>77400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>78500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>71700</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>74400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>79200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>78300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>70600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>67900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>73700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>72100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>60000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>59600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>66200</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>66800</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>54800</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>55200</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>44500</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>42000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>62100</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>68700</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>292700</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>82000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>71300</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>70400</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>283300</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>116500</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>89700</v>
       </c>
     </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1071,16 +1083,17 @@
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
-    </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE11" s="3"/>
+    </row>
+    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="3">
+      <c r="D12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E12" s="3">
         <v>12400</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>8</v>
@@ -1088,11 +1101,11 @@
       <c r="G12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H12" s="3">
+      <c r="H12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I12" s="3">
         <v>9000</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>8</v>
@@ -1157,8 +1170,11 @@
       <c r="AD12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1243,99 +1259,105 @@
       <c r="AD13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="3">
         <v>7200</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>3700</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>2000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>3700</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>3400</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>8200</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>14400</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>10400</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>4300</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>500</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>2900</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>2700</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>5600</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>-3800</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>1100</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>300</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>1400</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>1000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>1200</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>600</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>27000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>-11900</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>3600</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>23400</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>13500</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>1200</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>6400</v>
       </c>
     </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>800</v>
+        <v>1200</v>
       </c>
       <c r="E15" s="3">
         <v>800</v>
@@ -1347,34 +1369,34 @@
         <v>800</v>
       </c>
       <c r="H15" s="3">
+        <v>800</v>
+      </c>
+      <c r="I15" s="3">
         <v>1000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>1400</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>1300</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>1400</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>1600</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>1800</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>1900</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>2000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>1800</v>
-      </c>
-      <c r="Q15" s="3">
-        <v>2100</v>
       </c>
       <c r="R15" s="3">
         <v>2100</v>
@@ -1383,40 +1405,43 @@
         <v>2100</v>
       </c>
       <c r="T15" s="3">
-        <v>2200</v>
+        <v>2100</v>
       </c>
       <c r="U15" s="3">
         <v>2200</v>
       </c>
       <c r="V15" s="3">
+        <v>2200</v>
+      </c>
+      <c r="W15" s="3">
         <v>2100</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>1900</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>8900</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>2800</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>1900</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>2300</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>9300</v>
-      </c>
-      <c r="AC15" s="3">
-        <v>5200</v>
       </c>
       <c r="AD15" s="3">
         <v>5200</v>
       </c>
-    </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE15" s="3">
+        <v>5200</v>
+      </c>
+    </row>
+    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1444,180 +1469,187 @@
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
-    </row>
-    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE16" s="3"/>
+    </row>
+    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>114100</v>
+      </c>
+      <c r="E17" s="3">
         <v>122400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>113300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>106900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>109600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>125900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>122700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>113600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>127100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>138700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>145300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>132100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>124500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>131800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>120400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>114900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>110400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>108100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>103900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>124800</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>132300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>607200</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>139900</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>147300</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>167100</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>591100</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>284400</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>265400</v>
       </c>
     </row>
-    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>31100</v>
+      </c>
+      <c r="E18" s="3">
         <v>36300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>37100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>31500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>32400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>34700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>33600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>28400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>12300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>13100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>6600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>4500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>6400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>13600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>22700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>5800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>9000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>3300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-2000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>8600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>14400</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>47600</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>38200</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>12500</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-8500</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>50200</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>32700</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>9800</v>
       </c>
     </row>
-    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1648,8 +1680,9 @@
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
-    </row>
-    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE19" s="3"/>
+    </row>
+    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1663,192 +1696,198 @@
         <v>500</v>
       </c>
       <c r="G20" s="3">
+        <v>500</v>
+      </c>
+      <c r="H20" s="3">
         <v>1000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>700</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>500</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>700</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-3500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-3000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-1200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-1000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-1400</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-1100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-1800</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-2200</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-2000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-2200</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-3400</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-3900</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-7100</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-28800</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-6400</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-7700</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-7900</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-31000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-7700</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-8200</v>
       </c>
     </row>
-    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>31800</v>
+      </c>
+      <c r="E21" s="3">
         <v>36700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>37300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>31800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>32200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>35100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>34400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>29000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>13000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>14700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>10300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>8400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>10100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>17600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>26300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>9100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>12500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>6500</v>
       </c>
-      <c r="U21" s="3">
-        <v>0</v>
-      </c>
       <c r="V21" s="3">
+        <v>0</v>
+      </c>
+      <c r="W21" s="3">
         <v>10000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>12100</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>38900</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>41100</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>16100</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-11300</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>39600</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>35400</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>11900</v>
       </c>
     </row>
-    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E22" s="3">
         <v>4300</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>3400</v>
-      </c>
-      <c r="F22" s="3">
-        <v>3700</v>
       </c>
       <c r="G22" s="3">
         <v>3700</v>
       </c>
       <c r="H22" s="3">
+        <v>3700</v>
+      </c>
+      <c r="I22" s="3">
         <v>4900</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>3300</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>3100</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
-      </c>
       <c r="L22" s="3">
         <v>0</v>
       </c>
@@ -1906,180 +1945,189 @@
       <c r="AD22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>27900</v>
+      </c>
+      <c r="E23" s="3">
         <v>26800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>29400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>25300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>24000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>28300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>21700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>10100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>8800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>10100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>5400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>3500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>5000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>12400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>20900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>3600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>7100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>1100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-5300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>4700</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>7300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>18700</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>31800</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>4800</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-16400</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>19200</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>25000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>6200</v>
+      </c>
+      <c r="E24" s="3">
         <v>3400</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>6800</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>7400</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>5700</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>5200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>4700</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>3000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>2400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>1400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>1300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>1800</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-4400</v>
       </c>
-      <c r="R24" s="3">
-        <v>0</v>
-      </c>
       <c r="S24" s="3">
+        <v>0</v>
+      </c>
+      <c r="T24" s="3">
         <v>2300</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>3900</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-400</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>800</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>1000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>16500</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>5000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>4000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>100</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>14500</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-4000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>19800</v>
       </c>
     </row>
-    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2164,180 +2212,189 @@
       <c r="AD25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>21700</v>
+      </c>
+      <c r="E26" s="3">
         <v>23400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>22600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>17900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>18300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>23100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>17000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>7200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>6400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>10200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>4100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>2100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>3200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>12500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>25300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>3600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>4800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-2800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-4900</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>3900</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>6400</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>2300</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>26900</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>800</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-16400</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>4700</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>29000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-18200</v>
       </c>
     </row>
-    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>21700</v>
+      </c>
+      <c r="E27" s="3">
         <v>24400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>25800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>17800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>17700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>22200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>12400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>4500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>6400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>10200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>4100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>2100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>3200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>12500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>25300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>3600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>4800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-2800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-4900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>3900</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>6400</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>2300</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>26900</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>800</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-16400</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>4700</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>29000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-18200</v>
       </c>
     </row>
-    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2422,94 +2479,100 @@
       <c r="AD28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3">
         <v>1000</v>
       </c>
-      <c r="E29" s="3">
+      <c r="F29" s="3">
         <v>3200</v>
       </c>
-      <c r="F29" s="3">
+      <c r="G29" s="3">
         <v>-100</v>
       </c>
-      <c r="G29" s="3">
+      <c r="H29" s="3">
         <v>-600</v>
       </c>
-      <c r="H29" s="3">
+      <c r="I29" s="3">
         <v>-900</v>
       </c>
-      <c r="I29" s="3">
+      <c r="J29" s="3">
         <v>-4600</v>
       </c>
-      <c r="J29" s="3">
+      <c r="K29" s="3">
         <v>-2700</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>1000</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>-200</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>-2400</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>-900</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>-400</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>-7300</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>-200</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <v>-400</v>
       </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
         <v>-200</v>
       </c>
-      <c r="T29" s="3">
+      <c r="U29" s="3">
         <v>4200</v>
       </c>
-      <c r="U29" s="3">
+      <c r="V29" s="3">
         <v>-100</v>
       </c>
-      <c r="V29" s="3">
+      <c r="W29" s="3">
         <v>-1800</v>
       </c>
-      <c r="W29" s="3">
+      <c r="X29" s="3">
         <v>-4300</v>
       </c>
-      <c r="X29" s="3">
+      <c r="Y29" s="3">
         <v>-251400</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Z29" s="3">
         <v>5600</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="AA29" s="3">
         <v>2000</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AB29" s="3">
         <v>-1000</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AC29" s="3">
         <v>-31400</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AD29" s="3">
         <v>12900</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AE29" s="3">
         <v>-8400</v>
       </c>
     </row>
-    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2594,8 +2657,11 @@
       <c r="AD30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2680,8 +2746,11 @@
       <c r="AD31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2695,165 +2764,171 @@
         <v>-500</v>
       </c>
       <c r="G32" s="3">
+        <v>-500</v>
+      </c>
+      <c r="H32" s="3">
         <v>-1000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-700</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-500</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-700</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>3500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>3000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>1200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>1000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>1400</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>1100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>1800</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>2200</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>2000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>2200</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>3400</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>3900</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>7100</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>28800</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>6400</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>7700</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>7900</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>31000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>7700</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>8200</v>
       </c>
     </row>
-    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>21700</v>
+      </c>
+      <c r="E33" s="3">
         <v>24400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>25800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>17800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>17700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>22200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>12400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>4500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>7500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>10000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>2800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>5300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>25000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>3200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>4600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>1400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-5000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>2200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>2100</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-249100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>32400</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>2800</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-17500</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-26600</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>41900</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-26600</v>
       </c>
     </row>
-    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2938,185 +3013,194 @@
       <c r="AD34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>21700</v>
+      </c>
+      <c r="E35" s="3">
         <v>24400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>25800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>17800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>17700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>22200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>12400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>4500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>7500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>10000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>2800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>5300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>25000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>3200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>4600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>1400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-5000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>2200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>2100</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-249100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>32400</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>2800</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-17500</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-26600</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>41900</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-26600</v>
       </c>
     </row>
-    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45626</v>
+      </c>
+      <c r="E38" s="2">
         <v>45535</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45443</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45351</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45260</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45169</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45077</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44985</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44895</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44804</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44712</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44620</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44530</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44439</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44347</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44255</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44165</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44074</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43982</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43890</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43799</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43708</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43616</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43524</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43434</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43343</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43251</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43159</v>
       </c>
     </row>
-    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3147,8 +3231,9 @@
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
-    </row>
-    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE39" s="3"/>
+    </row>
+    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3179,94 +3264,98 @@
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
-    </row>
-    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE40" s="3"/>
+    </row>
+    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>130700</v>
+      </c>
+      <c r="E41" s="3">
         <v>167100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>132400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>153700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>148000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>154400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>142000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>124700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>129200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>120700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>123700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>133400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>126500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>140400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>136300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>115300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>158600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>152200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>163600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>163400</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>206800</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>211200</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>201300</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>170400</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>203400</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>250500</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>189500</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>153600</v>
       </c>
     </row>
-    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3351,352 +3440,367 @@
       <c r="AD42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>107400</v>
+      </c>
+      <c r="E43" s="3">
         <v>108900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>113500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>102100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>101400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>101600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>106600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>101800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>99100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>109100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>120800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>116400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>114700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>111800</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>119600</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>102700</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>95600</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>90300</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>98400</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>118500</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>127000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>125900</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>202800</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>210200</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>191200</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>123300</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>212300</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>210700</v>
       </c>
     </row>
-    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>81200</v>
+      </c>
+      <c r="E44" s="3">
         <v>72900</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>79100</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>82900</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>80100</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>74800</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>93000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>94200</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>90700</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>83700</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>86900</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>89500</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>83600</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>75300</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>74700</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>71800</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>70700</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>69200</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>78900</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>78000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>79500</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>77200</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>167600</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>161600</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>154800</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>72000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>167300</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>166200</v>
       </c>
     </row>
-    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>30400</v>
+      </c>
+      <c r="E45" s="3">
         <v>23400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>22900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>28700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>30500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>24800</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>31800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>34600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>33700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>28900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>34900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>34700</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>36200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>30000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>41200</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>35700</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>32900</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>29500</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>39000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>38200</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>39500</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>316100</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>44500</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>111000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>157900</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>625000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>58700</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>60600</v>
       </c>
     </row>
-    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>349800</v>
+      </c>
+      <c r="E46" s="3">
         <v>372300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>347800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>367300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>360000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>355600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>373400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>355300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>352700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>342400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>366300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>374100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>361100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>357400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>371800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>325400</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>357800</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>341100</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>379800</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>398200</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>452700</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>730300</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>616200</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>653200</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>707300</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>1047200</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>627800</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>591000</v>
       </c>
     </row>
-    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3721,8 +3825,8 @@
       <c r="J47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L47" s="3">
         <v>0</v>
@@ -3781,180 +3885,189 @@
       <c r="AD47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>45800</v>
+      </c>
+      <c r="E48" s="3">
         <v>73200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>36200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>37000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>38000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>76700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>41800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>41200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>41800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>84600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>44400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>46500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>47700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>100200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>50100</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>61300</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>60200</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>110100</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>111600</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>116600</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>111700</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>56700</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>90000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>83100</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>79200</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>145200</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>100800</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>102400</v>
       </c>
     </row>
-    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>322000</v>
+      </c>
+      <c r="E49" s="3">
         <v>305700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>303100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>303000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>304300</v>
-      </c>
-      <c r="H49" s="3">
-        <v>303800</v>
       </c>
       <c r="I49" s="3">
         <v>303800</v>
       </c>
       <c r="J49" s="3">
+        <v>303800</v>
+      </c>
+      <c r="K49" s="3">
         <v>301900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>302700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>299500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>312400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>322000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>324700</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>332100</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>344600</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>343700</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>341100</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>343500</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>334000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>338300</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>315200</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>312800</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>649700</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>630200</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>630100</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>351800</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>749000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>762500</v>
       </c>
     </row>
-    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4039,8 +4152,11 @@
       <c r="AD50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4125,94 +4241,100 @@
       <c r="AD51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>57800</v>
+      </c>
+      <c r="E52" s="3">
         <v>11500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>62400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>62000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>63400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>10700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>74100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>74800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>77300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>30800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>74200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>78900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>79000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>30500</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>76200</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>78600</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>79500</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>29500</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>26100</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>26200</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>28900</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>24400</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>37300</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>36500</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>33500</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>31200</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>27200</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>24300</v>
       </c>
     </row>
-    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4297,94 +4419,100 @@
       <c r="AD53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>775400</v>
+      </c>
+      <c r="E54" s="3">
         <v>777300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>749500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>769300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>765600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>762600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>793100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>773200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>774400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>757300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>797300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>821500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>812500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>820200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>842700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>809000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>838600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>824300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>851500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>879300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>908500</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1124300</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1393200</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1403100</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1450000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1485200</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>1504800</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>1480300</v>
       </c>
     </row>
-    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4415,8 +4543,9 @@
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
-    </row>
-    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE55" s="3"/>
+    </row>
+    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4447,126 +4576,130 @@
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
-    </row>
-    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE56" s="3"/>
+    </row>
+    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>46900</v>
+      </c>
+      <c r="E57" s="3">
         <v>43400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>41700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>44000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>45500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>50500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>47200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>54300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>74700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>72500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>65700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>66400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>63500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>62000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>59900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>49700</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>47000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>45100</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>52100</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>62300</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>68800</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>76900</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>126100</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>122500</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>124100</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>69600</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>142200</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>136900</v>
       </c>
     </row>
-    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>5000</v>
+      </c>
+      <c r="E58" s="3">
         <v>14500</v>
-      </c>
-      <c r="E58" s="3">
-        <v>5000</v>
       </c>
       <c r="F58" s="3">
         <v>5000</v>
       </c>
       <c r="G58" s="3">
+        <v>5000</v>
+      </c>
+      <c r="H58" s="3">
         <v>4400</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>13500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>3100</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>2500</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1900</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>4000</v>
-      </c>
-      <c r="M58" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="N58" s="3" t="s">
         <v>8</v>
@@ -4583,8 +4716,8 @@
       <c r="R58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S58" s="3">
-        <v>0</v>
+      <c r="S58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="T58" s="3">
         <v>0</v>
@@ -4599,13 +4732,13 @@
         <v>0</v>
       </c>
       <c r="X58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y58" s="3">
         <v>7500</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>6300</v>
-      </c>
-      <c r="Z58" s="3">
-        <v>30000</v>
       </c>
       <c r="AA58" s="3">
         <v>30000</v>
@@ -4619,215 +4752,224 @@
       <c r="AD58" s="3">
         <v>30000</v>
       </c>
-    </row>
-    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE58" s="3">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>49600</v>
+      </c>
+      <c r="E59" s="3">
         <v>45700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>51000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>48700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>55300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>50900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>61400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>62400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>77600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>76700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>68800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>73900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>68200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>72800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>74500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>65500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>62800</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>60500</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>70400</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>67300</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>88500</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>216000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>101200</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>125600</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>178300</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>298600</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>129100</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>107600</v>
       </c>
     </row>
-    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>119900</v>
+      </c>
+      <c r="E60" s="3">
         <v>129400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>122000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>118100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>127000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>148100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>140200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>143400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>154100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>153200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>134500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>140300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>131600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>134800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>134400</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>115300</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>109700</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>105500</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>122500</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>129600</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>157300</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>300400</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>233600</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>278100</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>332400</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>354000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>301300</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>274500</v>
       </c>
     </row>
-    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>188300</v>
+      </c>
+      <c r="E61" s="3">
         <v>214700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>190700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>239900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>240100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>239600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>231500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>206800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>200400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>200000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>205000</v>
-      </c>
-      <c r="N61" s="3">
-        <v>175000</v>
       </c>
       <c r="O61" s="3">
         <v>175000</v>
@@ -4836,135 +4978,141 @@
         <v>175000</v>
       </c>
       <c r="Q61" s="3">
+        <v>175000</v>
+      </c>
+      <c r="R61" s="3">
         <v>195000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>210000</v>
-      </c>
-      <c r="S61" s="3">
-        <v>255000</v>
       </c>
       <c r="T61" s="3">
         <v>255000</v>
       </c>
       <c r="U61" s="3">
+        <v>255000</v>
+      </c>
+      <c r="V61" s="3">
         <v>286500</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>286400</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>286200</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>452900</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>469000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>455600</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>495400</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>502700</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>510000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>517300</v>
       </c>
     </row>
-    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>53900</v>
+      </c>
+      <c r="E62" s="3">
         <v>27500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>57500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>57600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>60600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>32400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>65000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>62000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>85600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>85500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>91500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>93100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>96000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>98300</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>96300</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>102400</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>105900</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>104500</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>106200</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>109000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>111800</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>69700</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>83200</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>83700</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>84700</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>69800</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>92400</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>99200</v>
       </c>
     </row>
-    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5049,8 +5197,11 @@
       <c r="AD63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5135,8 +5286,11 @@
       <c r="AD64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5221,94 +5375,100 @@
       <c r="AD65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>377300</v>
+      </c>
+      <c r="E66" s="3">
         <v>385300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>383700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>432400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>443900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>436000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>456500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>432400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>440100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>438700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>431000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>408400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>402700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>408000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>425800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>427600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>470600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>465100</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>515300</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>525000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>555300</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>823100</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>785700</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>817400</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>912500</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>926500</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>903800</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>891000</v>
       </c>
     </row>
-    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5339,8 +5499,9 @@
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
-    </row>
-    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE67" s="3"/>
+    </row>
+    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5425,8 +5586,11 @@
       <c r="AD68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5511,8 +5675,11 @@
       <c r="AD69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5597,8 +5764,11 @@
       <c r="AD70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5683,94 +5853,100 @@
       <c r="AD71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>279200</v>
+      </c>
+      <c r="E72" s="3">
         <v>261900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>245300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>222000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>1028900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>1011100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>991100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>978700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>974200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>966800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>959000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>957300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>956100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>953300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>950500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>925500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>922300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>917700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>918600</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>923600</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>921500</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>915500</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>1184700</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>1152300</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>1149600</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>1167000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>1207100</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>1178000</v>
       </c>
     </row>
-    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5855,8 +6031,11 @@
       <c r="AD73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5941,8 +6120,11 @@
       <c r="AD74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6027,94 +6209,100 @@
       <c r="AD75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>398000</v>
+      </c>
+      <c r="E76" s="3">
         <v>392000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>365800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>336900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>321700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>326600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>336600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>340800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>334300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>318600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>366300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>413000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>409800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>412200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>416900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>381400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>367900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>359200</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>336300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>354400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>353300</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>301200</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>607400</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>585600</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>537600</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>558700</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>601000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>589300</v>
       </c>
     </row>
-    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6199,185 +6387,194 @@
       <c r="AD77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45626</v>
+      </c>
+      <c r="E80" s="2">
         <v>45535</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45443</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45351</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45260</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45169</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45077</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44985</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44895</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44804</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44712</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44620</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44530</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44439</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44347</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44255</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44165</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44074</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43982</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43890</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43799</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43708</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43616</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43524</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43434</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43343</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43251</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43159</v>
       </c>
     </row>
-    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>21700</v>
+      </c>
+      <c r="E81" s="3">
         <v>24400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>25800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>17800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>17700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>22200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>12400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>4500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>7500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>10000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>2800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>5300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>25000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>3200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>4600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>1400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-5000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>2200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>2100</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-249100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>32400</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>2800</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-17500</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-26600</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>41900</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-26600</v>
       </c>
     </row>
-    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6408,52 +6605,53 @@
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
-    </row>
-    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE82" s="3"/>
+    </row>
+    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E83" s="3">
         <v>2800</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>2700</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>2900</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>2800</v>
-      </c>
-      <c r="H83" s="3">
-        <v>3000</v>
       </c>
       <c r="I83" s="3">
         <v>3000</v>
       </c>
       <c r="J83" s="3">
+        <v>3000</v>
+      </c>
+      <c r="K83" s="3">
         <v>3100</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>4200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>4600</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>4800</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>5000</v>
-      </c>
-      <c r="O83" s="3">
-        <v>5200</v>
       </c>
       <c r="P83" s="3">
         <v>5200</v>
       </c>
       <c r="Q83" s="3">
-        <v>5500</v>
+        <v>5200</v>
       </c>
       <c r="R83" s="3">
         <v>5500</v>
@@ -6462,7 +6660,7 @@
         <v>5500</v>
       </c>
       <c r="T83" s="3">
-        <v>5300</v>
+        <v>5500</v>
       </c>
       <c r="U83" s="3">
         <v>5300</v>
@@ -6471,31 +6669,34 @@
         <v>5300</v>
       </c>
       <c r="W83" s="3">
+        <v>5300</v>
+      </c>
+      <c r="X83" s="3">
         <v>4800</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>20200</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>9300</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>7500</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>8900</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>40700</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>10400</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>10300</v>
       </c>
     </row>
-    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6580,8 +6781,11 @@
       <c r="AD84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6666,8 +6870,11 @@
       <c r="AD85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6752,8 +6959,11 @@
       <c r="AD86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6838,8 +7048,11 @@
       <c r="AD87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6924,94 +7137,100 @@
       <c r="AD88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>8600</v>
+      </c>
+      <c r="E89" s="3">
         <v>44400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>30300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>13300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-6700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>50600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>17300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-7800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>17500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>44500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>2500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>9400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-4700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>29300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>11600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>4600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>8700</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>12500</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>13000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-5800</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-22900</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>53800</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>52500</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-22200</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-29100</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>106100</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>57700</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-1600</v>
       </c>
     </row>
-    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7042,94 +7261,98 @@
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
-    </row>
-    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE90" s="3"/>
+    </row>
+    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-5900</v>
+      </c>
+      <c r="E91" s="3">
         <v>-6400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-2000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-2600</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-2300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-2900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-3000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-2100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-1500</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-3300</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-2500</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-3900</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-3700</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-1900</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-2700</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-2300</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-3800</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-3200</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-14900</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-8100</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-11100</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-4600</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-11000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-6200</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-4600</v>
       </c>
     </row>
-    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7214,8 +7437,11 @@
       <c r="AD92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7300,94 +7526,100 @@
       <c r="AD93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-33100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-6400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-3100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-2600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>19100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-2900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-2300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-2500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-3200</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-2500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>20800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-3200</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-1900</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>100</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-600</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-36800</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>213300</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>11000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-6800</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>28200</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-7700</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-62800</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-11900</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-12300</v>
       </c>
     </row>
-    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7418,13 +7650,14 @@
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
-    </row>
-    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE95" s="3"/>
+    </row>
+    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>0</v>
+        <v>2200</v>
       </c>
       <c r="E96" s="3">
         <v>0</v>
@@ -7433,11 +7666,11 @@
         <v>0</v>
       </c>
       <c r="G96" s="3">
+        <v>0</v>
+      </c>
+      <c r="H96" s="3">
         <v>2200</v>
       </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
       <c r="I96" s="3">
         <v>0</v>
       </c>
@@ -7445,11 +7678,11 @@
         <v>0</v>
       </c>
       <c r="K96" s="3">
+        <v>0</v>
+      </c>
+      <c r="L96" s="3">
         <v>-2300</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
-      </c>
       <c r="M96" s="3">
         <v>0</v>
       </c>
@@ -7457,11 +7690,11 @@
         <v>0</v>
       </c>
       <c r="O96" s="3">
+        <v>0</v>
+      </c>
+      <c r="P96" s="3">
         <v>-2400</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
-      </c>
       <c r="Q96" s="3">
         <v>0</v>
       </c>
@@ -7469,11 +7702,11 @@
         <v>0</v>
       </c>
       <c r="S96" s="3">
+        <v>0</v>
+      </c>
+      <c r="T96" s="3">
         <v>-2400</v>
       </c>
-      <c r="T96" s="3">
-        <v>0</v>
-      </c>
       <c r="U96" s="3">
         <v>0</v>
       </c>
@@ -7481,31 +7714,34 @@
         <v>0</v>
       </c>
       <c r="W96" s="3">
-        <v>-2400</v>
+        <v>0</v>
       </c>
       <c r="X96" s="3">
         <v>-2400</v>
       </c>
       <c r="Y96" s="3">
-        <v>0</v>
+        <v>-2400</v>
       </c>
       <c r="Z96" s="3">
         <v>0</v>
       </c>
       <c r="AA96" s="3">
-        <v>-2400</v>
+        <v>0</v>
       </c>
       <c r="AB96" s="3">
         <v>-2400</v>
       </c>
       <c r="AC96" s="3">
-        <v>0</v>
+        <v>-2400</v>
       </c>
       <c r="AD96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7590,8 +7826,11 @@
       <c r="AD97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7676,8 +7915,11 @@
       <c r="AD98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7762,262 +8004,274 @@
       <c r="AD99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-12800</v>
+      </c>
+      <c r="E100" s="3">
         <v>-4900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-49700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-4100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>2300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-57500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>4500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>5500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-5700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-40300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-6200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-1900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-3700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-19800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-13200</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-46600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-1800</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-32500</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-10000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-1200</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-195200</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-99500</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-12100</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-40800</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-9600</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-18000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-7500</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>500</v>
+      </c>
+      <c r="E101" s="3">
         <v>200</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-1500</v>
       </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
       <c r="G101" s="3">
+        <v>0</v>
+      </c>
+      <c r="H101" s="3">
         <v>-800</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-5800</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-4900</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>900</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-800</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-5800</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-4900</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>900</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-2200</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-2900</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>1800</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>1900</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>1400</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>8400</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-2200</v>
-      </c>
-      <c r="V101" s="3">
-        <v>400</v>
       </c>
       <c r="W101" s="3">
         <v>400</v>
       </c>
       <c r="X101" s="3">
+        <v>400</v>
+      </c>
+      <c r="Y101" s="3">
         <v>-4700</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-2700</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>1800</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-700</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-4400</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-2300</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>2700</v>
       </c>
     </row>
-    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-36400</v>
+      </c>
+      <c r="E102" s="3">
         <v>34700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-21300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>5700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-6500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>12400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>17300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-4600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>8500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-3000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-9700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>6900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-13800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>4100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>21000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-43300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>6400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-11400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>200</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-43300</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-4400</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-39300</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>30900</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-33100</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-47000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>20900</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>35900</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-11500</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/EPAC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/EPAC_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="92">
   <si>
     <t>EPAC</t>
   </si>
@@ -656,403 +656,416 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AE102"/>
+  <dimension ref="A5:AF102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45716</v>
+      </c>
+      <c r="E7" s="2">
         <v>45626</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45535</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45443</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45351</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45260</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45169</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45077</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44985</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44895</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44804</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44712</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44620</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44530</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44439</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44347</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44255</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44165</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44074</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43982</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43890</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43799</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43708</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43616</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43524</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43434</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43343</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43251</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43159</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>145500</v>
+      </c>
+      <c r="E8" s="3">
         <v>145200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>158700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>150400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>138400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>142000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>160600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>156300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>142000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>139400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>151800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>151900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>136600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>130900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>145400</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>143100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>120700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>119400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>111400</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>101900</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>133400</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>146700</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>654800</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>178100</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>159800</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>158600</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>641300</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>317100</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>275200</v>
       </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>72100</v>
+      </c>
+      <c r="E9" s="3">
         <v>70500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>81300</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>71900</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>66800</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>67600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>81400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>78000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>71400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>71500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>78100</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>79800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>76600</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>71300</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>79200</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>76300</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>65900</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>64200</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>66900</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>59900</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>71300</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>78000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>362100</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>96100</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>88500</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>88200</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>358000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>200600</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>185500</v>
       </c>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>73400</v>
+      </c>
+      <c r="E10" s="3">
         <v>74700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>77400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>78500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>71700</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>74400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>79200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>78300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>70600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>67900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>73700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>72100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>60000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>59600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>66200</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>66800</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>54800</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>55200</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>44500</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>42000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>62100</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>68700</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>292700</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>82000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>71300</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>70400</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>283300</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>116500</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>89700</v>
       </c>
     </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1084,19 +1097,20 @@
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
-    </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF11" s="3"/>
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E12" s="3">
+      <c r="E12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" s="3">
         <v>12400</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>8</v>
@@ -1104,11 +1118,11 @@
       <c r="H12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I12" s="3">
+      <c r="I12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J12" s="3">
         <v>9000</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>8</v>
@@ -1173,8 +1187,11 @@
       <c r="AE12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1262,97 +1279,103 @@
       <c r="AE13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" s="3">
         <v>7200</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>3700</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>2000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>3700</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>3400</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>8200</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>14400</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>10400</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>4300</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>500</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>2900</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>2700</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>5600</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>-3800</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>1100</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>300</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>1400</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>1000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>1200</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>600</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>27000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>-11900</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>3600</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>23400</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>13500</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>1200</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>6400</v>
       </c>
     </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1360,7 +1383,7 @@
         <v>1200</v>
       </c>
       <c r="E15" s="3">
-        <v>800</v>
+        <v>1200</v>
       </c>
       <c r="F15" s="3">
         <v>800</v>
@@ -1372,34 +1395,34 @@
         <v>800</v>
       </c>
       <c r="I15" s="3">
+        <v>800</v>
+      </c>
+      <c r="J15" s="3">
         <v>1000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>1400</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>1300</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>1400</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>1600</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>1800</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>1900</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>2000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>1800</v>
-      </c>
-      <c r="R15" s="3">
-        <v>2100</v>
       </c>
       <c r="S15" s="3">
         <v>2100</v>
@@ -1408,40 +1431,43 @@
         <v>2100</v>
       </c>
       <c r="U15" s="3">
-        <v>2200</v>
+        <v>2100</v>
       </c>
       <c r="V15" s="3">
         <v>2200</v>
       </c>
       <c r="W15" s="3">
+        <v>2200</v>
+      </c>
+      <c r="X15" s="3">
         <v>2100</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>1900</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>8900</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>2800</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>1900</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>2300</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>9300</v>
-      </c>
-      <c r="AD15" s="3">
-        <v>5200</v>
       </c>
       <c r="AE15" s="3">
         <v>5200</v>
       </c>
-    </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF15" s="3">
+        <v>5200</v>
+      </c>
+    </row>
+    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1470,186 +1496,193 @@
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
-    </row>
-    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF16" s="3"/>
+    </row>
+    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>114700</v>
+      </c>
+      <c r="E17" s="3">
         <v>114100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>122400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>113300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>106900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>109600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>125900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>122700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>113600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>127100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>138700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>145300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>132100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>124500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>131800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>120400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>114900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>110400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>108100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>103900</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>124800</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>132300</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>607200</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>139900</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>147300</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>167100</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>591100</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>284400</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>265400</v>
       </c>
     </row>
-    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>30800</v>
+      </c>
+      <c r="E18" s="3">
         <v>31100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>36300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>37100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>31500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>32400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>34700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>33600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>28400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>12300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>13100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>6600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>4500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>6400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>13600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>22700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>5800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>9000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>3300</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-2000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>8600</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>14400</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>47600</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>38200</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>12500</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-8500</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>50200</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>32700</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>9800</v>
       </c>
     </row>
-    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1681,13 +1714,14 @@
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
-    </row>
-    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF19" s="3"/>
+    </row>
+    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>500</v>
+        <v>800</v>
       </c>
       <c r="E20" s="3">
         <v>500</v>
@@ -1699,198 +1733,204 @@
         <v>500</v>
       </c>
       <c r="H20" s="3">
+        <v>500</v>
+      </c>
+      <c r="I20" s="3">
         <v>1000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>700</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>700</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-3500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-3000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-1200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-1000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-1100</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-1800</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-2200</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-2000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-2200</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-3400</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-3900</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-7100</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-28800</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-6400</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-7700</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-7900</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-31000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-7700</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-8200</v>
       </c>
     </row>
-    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>31300</v>
+      </c>
+      <c r="E21" s="3">
         <v>31800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>36700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>37300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>31800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>32200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>35100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>34400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>29000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>13000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>14700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>10300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>8400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>10100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>17600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>26300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>9100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>12500</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>6500</v>
       </c>
-      <c r="V21" s="3">
-        <v>0</v>
-      </c>
       <c r="W21" s="3">
+        <v>0</v>
+      </c>
+      <c r="X21" s="3">
         <v>10000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>12100</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>38900</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>41100</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>16100</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-11300</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>39600</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>35400</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>11900</v>
       </c>
     </row>
-    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E22" s="3">
         <v>2800</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>4300</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>3400</v>
-      </c>
-      <c r="G22" s="3">
-        <v>3700</v>
       </c>
       <c r="H22" s="3">
         <v>3700</v>
       </c>
       <c r="I22" s="3">
+        <v>3700</v>
+      </c>
+      <c r="J22" s="3">
         <v>4900</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>3300</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>3100</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
-      </c>
       <c r="M22" s="3">
         <v>0</v>
       </c>
@@ -1948,186 +1988,195 @@
       <c r="AE22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>27700</v>
+      </c>
+      <c r="E23" s="3">
         <v>27900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>26800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>29400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>25300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>24000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>28300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>21700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>10100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>8800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>10100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>5400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>3500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>5000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>12400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>20900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>3600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>7100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>1100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-5300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>4700</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>7300</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>18700</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>31800</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>4800</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-16400</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>19200</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>25000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>6800</v>
+      </c>
+      <c r="E24" s="3">
         <v>6200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>3400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>6800</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>7400</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>5700</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>5200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>4700</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>3000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>2400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>1400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>1300</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>1800</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-100</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-4400</v>
       </c>
-      <c r="S24" s="3">
-        <v>0</v>
-      </c>
       <c r="T24" s="3">
+        <v>0</v>
+      </c>
+      <c r="U24" s="3">
         <v>2300</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>3900</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-400</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>800</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>1000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>16500</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>5000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>4000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>100</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>14500</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>-4000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>19800</v>
       </c>
     </row>
-    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2215,186 +2264,195 @@
       <c r="AE25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>20900</v>
+      </c>
+      <c r="E26" s="3">
         <v>21700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>23400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>22600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>17900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>18300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>23100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>17000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>7200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>6400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>10200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>4100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>2100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>3200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>12500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>25300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>3600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>4800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-2800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-4900</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>3900</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>6400</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>2300</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>26900</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>800</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-16400</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>4700</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>29000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-18200</v>
       </c>
     </row>
-    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>20900</v>
+      </c>
+      <c r="E27" s="3">
         <v>21700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>24400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>25800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>17800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>17700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>22200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>12400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>4500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>6400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>10200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>4100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>2100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>3200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>12500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>25300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>3600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>4800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-2800</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-4900</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>3900</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>6400</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>2300</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>26900</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>800</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-16400</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>4700</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>29000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-18200</v>
       </c>
     </row>
-    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2482,8 +2540,11 @@
       <c r="AE28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2491,88 +2552,91 @@
         <v>0</v>
       </c>
       <c r="E29" s="3">
+        <v>0</v>
+      </c>
+      <c r="F29" s="3">
         <v>1000</v>
       </c>
-      <c r="F29" s="3">
+      <c r="G29" s="3">
         <v>3200</v>
       </c>
-      <c r="G29" s="3">
+      <c r="H29" s="3">
         <v>-100</v>
       </c>
-      <c r="H29" s="3">
+      <c r="I29" s="3">
         <v>-600</v>
       </c>
-      <c r="I29" s="3">
+      <c r="J29" s="3">
         <v>-900</v>
       </c>
-      <c r="J29" s="3">
+      <c r="K29" s="3">
         <v>-4600</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>-2700</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>1000</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>-200</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>-2400</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>-900</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>-400</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>-7300</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <v>-200</v>
       </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
         <v>-400</v>
       </c>
-      <c r="T29" s="3">
+      <c r="U29" s="3">
         <v>-200</v>
       </c>
-      <c r="U29" s="3">
+      <c r="V29" s="3">
         <v>4200</v>
       </c>
-      <c r="V29" s="3">
+      <c r="W29" s="3">
         <v>-100</v>
       </c>
-      <c r="W29" s="3">
+      <c r="X29" s="3">
         <v>-1800</v>
       </c>
-      <c r="X29" s="3">
+      <c r="Y29" s="3">
         <v>-4300</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Z29" s="3">
         <v>-251400</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="AA29" s="3">
         <v>5600</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AB29" s="3">
         <v>2000</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AC29" s="3">
         <v>-1000</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AD29" s="3">
         <v>-31400</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AE29" s="3">
         <v>12900</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AF29" s="3">
         <v>-8400</v>
       </c>
     </row>
-    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2660,8 +2724,11 @@
       <c r="AE30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2749,13 +2816,16 @@
       <c r="AE31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-500</v>
+        <v>-800</v>
       </c>
       <c r="E32" s="3">
         <v>-500</v>
@@ -2767,168 +2837,174 @@
         <v>-500</v>
       </c>
       <c r="H32" s="3">
+        <v>-500</v>
+      </c>
+      <c r="I32" s="3">
         <v>-1000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-700</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-700</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>3500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>3000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>1200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>1000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>1400</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>1100</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>1800</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>2200</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>2000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>2200</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>3400</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>3900</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>7100</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>28800</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>6400</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>7700</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>7900</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>31000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>7700</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>8200</v>
       </c>
     </row>
-    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>20900</v>
+      </c>
+      <c r="E33" s="3">
         <v>21700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>24400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>25800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>17800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>17700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>22200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>12400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>4500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>7500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>10000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>2800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>5300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>25000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>3200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>4600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>1400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-5000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>2200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>2100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-249100</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>32400</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>2800</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-17500</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-26600</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>41900</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-26600</v>
       </c>
     </row>
-    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3016,191 +3092,200 @@
       <c r="AE34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>20900</v>
+      </c>
+      <c r="E35" s="3">
         <v>21700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>24400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>25800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>17800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>17700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>22200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>12400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>4500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>7500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>10000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>2800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>5300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>25000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>3200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>4600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>1400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-5000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>2200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>2100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-249100</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>32400</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>2800</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-17500</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-26600</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>41900</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-26600</v>
       </c>
     </row>
-    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45716</v>
+      </c>
+      <c r="E38" s="2">
         <v>45626</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45535</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45443</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45351</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45260</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45169</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45077</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44985</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44895</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44804</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44712</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44620</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44530</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44439</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44347</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44255</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44165</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44074</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43982</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43890</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43799</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43708</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43616</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43524</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43434</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43343</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43251</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43159</v>
       </c>
     </row>
-    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3232,8 +3317,9 @@
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
-    </row>
-    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF39" s="3"/>
+    </row>
+    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3265,97 +3351,101 @@
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
-    </row>
-    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF40" s="3"/>
+    </row>
+    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>119500</v>
+      </c>
+      <c r="E41" s="3">
         <v>130700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>167100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>132400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>153700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>148000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>154400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>142000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>124700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>129200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>120700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>123700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>133400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>126500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>140400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>136300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>115300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>158600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>152200</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>163600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>163400</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>206800</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>211200</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>201300</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>170400</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>203400</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>250500</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>189500</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>153600</v>
       </c>
     </row>
-    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3443,364 +3533,379 @@
       <c r="AE42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>115000</v>
+      </c>
+      <c r="E43" s="3">
         <v>107400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>108900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>113500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>102100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>101400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>101600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>106600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>101800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>99100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>109100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>120800</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>116400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>114700</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>111800</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>119600</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>102700</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>95600</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>90300</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>98400</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>118500</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>127000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>125900</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>202800</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>210200</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>191200</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>123300</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>212300</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>210700</v>
       </c>
     </row>
-    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>80400</v>
+      </c>
+      <c r="E44" s="3">
         <v>81200</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>72900</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>79100</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>82900</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>80100</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>74800</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>93000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>94200</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>90700</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>83700</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>86900</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>89500</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>83600</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>75300</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>74700</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>71800</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>70700</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>69200</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>78900</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>78000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>79500</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>77200</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>167600</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>161600</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>154800</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>72000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>167300</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>166200</v>
       </c>
     </row>
-    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>34500</v>
+      </c>
+      <c r="E45" s="3">
         <v>30400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>23400</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>22900</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>28700</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>30500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>24800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>31800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>34600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>33700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>28900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>34900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>34700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>36200</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>30000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>41200</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>35700</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>32900</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>29500</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>39000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>38200</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>39500</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>316100</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>44500</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>111000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>157900</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>625000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>58700</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>60600</v>
       </c>
     </row>
-    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>349400</v>
+      </c>
+      <c r="E46" s="3">
         <v>349800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>372300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>347800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>367300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>360000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>355600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>373400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>355300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>352700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>342400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>366300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>374100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>361100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>357400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>371800</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>325400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>357800</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>341100</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>379800</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>398200</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>452700</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>730300</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>616200</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>653200</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>707300</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>1047200</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>627800</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>591000</v>
       </c>
     </row>
-    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3828,8 +3933,8 @@
       <c r="K47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
+      <c r="L47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
@@ -3888,186 +3993,195 @@
       <c r="AE47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>49000</v>
+      </c>
+      <c r="E48" s="3">
         <v>45800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>73200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>36200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>37000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>38000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>76700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>41800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>41200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>41800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>84600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>44400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>46500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>47700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>100200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>50100</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>61300</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>60200</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>110100</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>111600</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>116600</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>111700</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>56700</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>90000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>83100</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>79200</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>145200</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>100800</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>102400</v>
       </c>
     </row>
-    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>323900</v>
+      </c>
+      <c r="E49" s="3">
         <v>322000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>305700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>303100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>303000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>304300</v>
-      </c>
-      <c r="I49" s="3">
-        <v>303800</v>
       </c>
       <c r="J49" s="3">
         <v>303800</v>
       </c>
       <c r="K49" s="3">
+        <v>303800</v>
+      </c>
+      <c r="L49" s="3">
         <v>301900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>302700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>299500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>312400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>322000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>324700</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>332100</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>344600</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>343700</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>341100</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>343500</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>334000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>338300</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>315200</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>312800</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>649700</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>630200</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>630100</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>351800</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>749000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>762500</v>
       </c>
     </row>
-    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4155,8 +4269,11 @@
       <c r="AE50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4244,97 +4361,103 @@
       <c r="AE51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>54300</v>
+      </c>
+      <c r="E52" s="3">
         <v>57800</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>11500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>62400</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>62000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>63400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>10700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>74100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>74800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>77300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>30800</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>74200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>78900</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>79000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>30500</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>76200</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>78600</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>79500</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>29500</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>26100</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>26200</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>28900</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>24400</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>37300</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>36500</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>33500</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>31200</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>27200</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>24300</v>
       </c>
     </row>
-    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4422,97 +4545,103 @@
       <c r="AE53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>776600</v>
+      </c>
+      <c r="E54" s="3">
         <v>775400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>777300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>749500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>769300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>765600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>762600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>793100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>773200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>774400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>757300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>797300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>821500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>812500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>820200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>842700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>809000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>838600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>824300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>851500</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>879300</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>908500</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1124300</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1393200</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1403100</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1450000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>1485200</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>1504800</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>1480300</v>
       </c>
     </row>
-    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4544,8 +4673,9 @@
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
-    </row>
-    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF55" s="3"/>
+    </row>
+    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4577,97 +4707,101 @@
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
-    </row>
-    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF56" s="3"/>
+    </row>
+    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>43900</v>
+      </c>
+      <c r="E57" s="3">
         <v>46900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>43400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>41700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>44000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>45500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>50500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>47200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>54300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>74700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>72500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>65700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>66400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>63500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>62000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>59900</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>49700</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>47000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>45100</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>52100</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>62300</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>68800</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>76900</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>126100</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>122500</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>124100</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>69600</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>142200</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>136900</v>
       </c>
     </row>
-    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4675,34 +4809,34 @@
         <v>5000</v>
       </c>
       <c r="E58" s="3">
+        <v>5000</v>
+      </c>
+      <c r="F58" s="3">
         <v>14500</v>
-      </c>
-      <c r="F58" s="3">
-        <v>5000</v>
       </c>
       <c r="G58" s="3">
         <v>5000</v>
       </c>
       <c r="H58" s="3">
+        <v>5000</v>
+      </c>
+      <c r="I58" s="3">
         <v>4400</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>13500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>3100</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>2500</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1900</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>4000</v>
-      </c>
-      <c r="N58" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="O58" s="3" t="s">
         <v>8</v>
@@ -4719,8 +4853,8 @@
       <c r="S58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T58" s="3">
-        <v>0</v>
+      <c r="T58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="U58" s="3">
         <v>0</v>
@@ -4735,13 +4869,13 @@
         <v>0</v>
       </c>
       <c r="Y58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z58" s="3">
         <v>7500</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>6300</v>
-      </c>
-      <c r="AA58" s="3">
-        <v>30000</v>
       </c>
       <c r="AB58" s="3">
         <v>30000</v>
@@ -4755,224 +4889,233 @@
       <c r="AE58" s="3">
         <v>30000</v>
       </c>
-    </row>
-    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF58" s="3">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>46000</v>
+      </c>
+      <c r="E59" s="3">
         <v>49600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>45700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>51000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>48700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>55300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>50900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>61400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>62400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>77600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>76700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>68800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>73900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>68200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>72800</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>74500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>65500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>62800</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>60500</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>70400</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>67300</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>88500</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>216000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>101200</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>125600</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>178300</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>298600</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>129100</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>107600</v>
       </c>
     </row>
-    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>114000</v>
+      </c>
+      <c r="E60" s="3">
         <v>119900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>129400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>122000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>118100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>127000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>148100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>140200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>143400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>154100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>153200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>134500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>140300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>131600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>134800</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>134400</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>115300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>109700</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>105500</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>122500</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>129600</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>157300</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>300400</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>233600</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>278100</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>332400</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>354000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>301300</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>274500</v>
       </c>
     </row>
-    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>187100</v>
+      </c>
+      <c r="E61" s="3">
         <v>188300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>214700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>190700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>239900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>240100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>239600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>231500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>206800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>200400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>200000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>205000</v>
-      </c>
-      <c r="O61" s="3">
-        <v>175000</v>
       </c>
       <c r="P61" s="3">
         <v>175000</v>
@@ -4981,138 +5124,144 @@
         <v>175000</v>
       </c>
       <c r="R61" s="3">
+        <v>175000</v>
+      </c>
+      <c r="S61" s="3">
         <v>195000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>210000</v>
-      </c>
-      <c r="T61" s="3">
-        <v>255000</v>
       </c>
       <c r="U61" s="3">
         <v>255000</v>
       </c>
       <c r="V61" s="3">
+        <v>255000</v>
+      </c>
+      <c r="W61" s="3">
         <v>286500</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>286400</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>286200</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>452900</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>469000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>455600</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>495400</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>502700</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>510000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>517300</v>
       </c>
     </row>
-    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>52500</v>
+      </c>
+      <c r="E62" s="3">
         <v>53900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>27500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>57500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>57600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>60600</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>32400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>65000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>62000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>85600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>85500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>91500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>93100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>96000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>98300</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>96300</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>102400</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>105900</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>104500</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>106200</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>109000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>111800</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>69700</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>83200</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>83700</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>84700</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>69800</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>92400</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>99200</v>
       </c>
     </row>
-    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5200,8 +5349,11 @@
       <c r="AE63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5289,8 +5441,11 @@
       <c r="AE64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5378,97 +5533,103 @@
       <c r="AE65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>370600</v>
+      </c>
+      <c r="E66" s="3">
         <v>377300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>385300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>383700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>432400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>443900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>436000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>456500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>432400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>440100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>438700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>431000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>408400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>402700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>408000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>425800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>427600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>470600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>465100</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>515300</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>525000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>555300</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>823100</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>785700</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>817400</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>912500</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>926500</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>903800</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>891000</v>
       </c>
     </row>
-    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5500,8 +5661,9 @@
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
-    </row>
-    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF67" s="3"/>
+    </row>
+    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5589,8 +5751,11 @@
       <c r="AE68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5678,8 +5843,11 @@
       <c r="AE69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5767,8 +5935,11 @@
       <c r="AE70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5856,97 +6027,103 @@
       <c r="AE71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>290000</v>
+      </c>
+      <c r="E72" s="3">
         <v>279200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>261900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>245300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>222000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>1028900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>1011100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>991100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>978700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>974200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>966800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>959000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>957300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>956100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>953300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>950500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>925500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>922300</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>917700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>918600</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>923600</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>921500</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>915500</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>1184700</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>1152300</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>1149600</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>1167000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>1207100</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>1178000</v>
       </c>
     </row>
-    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6034,8 +6211,11 @@
       <c r="AE73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6123,8 +6303,11 @@
       <c r="AE74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6212,97 +6395,103 @@
       <c r="AE75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>406000</v>
+      </c>
+      <c r="E76" s="3">
         <v>398000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>392000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>365800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>336900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>321700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>326600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>336600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>340800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>334300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>318600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>366300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>413000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>409800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>412200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>416900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>381400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>367900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>359200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>336300</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>354400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>353300</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>301200</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>607400</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>585600</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>537600</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>558700</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>601000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>589300</v>
       </c>
     </row>
-    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6390,191 +6579,200 @@
       <c r="AE77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45716</v>
+      </c>
+      <c r="E80" s="2">
         <v>45626</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45535</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45443</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45351</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45260</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45169</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45077</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44985</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44895</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44804</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44712</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44620</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44530</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44439</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44347</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44255</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44165</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44074</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43982</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43890</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43799</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43708</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43616</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43524</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43434</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43343</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43251</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43159</v>
       </c>
     </row>
-    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>20900</v>
+      </c>
+      <c r="E81" s="3">
         <v>21700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>24400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>25800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>17800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>17700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>22200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>12400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>4500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>7500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>10000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>2800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>5300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>25000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>3200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>4600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>1400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-5000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>2200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>2100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-249100</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>32400</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>2800</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-17500</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-26600</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>41900</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-26600</v>
       </c>
     </row>
-    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6606,55 +6804,56 @@
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
-    </row>
-    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF82" s="3"/>
+    </row>
+    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E83" s="3">
         <v>2600</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>2800</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>2700</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>2900</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>2800</v>
-      </c>
-      <c r="I83" s="3">
-        <v>3000</v>
       </c>
       <c r="J83" s="3">
         <v>3000</v>
       </c>
       <c r="K83" s="3">
+        <v>3000</v>
+      </c>
+      <c r="L83" s="3">
         <v>3100</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>4200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>4600</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>4800</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>5000</v>
-      </c>
-      <c r="P83" s="3">
-        <v>5200</v>
       </c>
       <c r="Q83" s="3">
         <v>5200</v>
       </c>
       <c r="R83" s="3">
-        <v>5500</v>
+        <v>5200</v>
       </c>
       <c r="S83" s="3">
         <v>5500</v>
@@ -6663,7 +6862,7 @@
         <v>5500</v>
       </c>
       <c r="U83" s="3">
-        <v>5300</v>
+        <v>5500</v>
       </c>
       <c r="V83" s="3">
         <v>5300</v>
@@ -6672,31 +6871,34 @@
         <v>5300</v>
       </c>
       <c r="X83" s="3">
+        <v>5300</v>
+      </c>
+      <c r="Y83" s="3">
         <v>4800</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>20200</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>9300</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>7500</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>8900</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>40700</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>10400</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>10300</v>
       </c>
     </row>
-    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6784,8 +6986,11 @@
       <c r="AE84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6873,8 +7078,11 @@
       <c r="AE85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6962,8 +7170,11 @@
       <c r="AE86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7051,8 +7262,11 @@
       <c r="AE87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7140,97 +7354,103 @@
       <c r="AE88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>7500</v>
+      </c>
+      <c r="E89" s="3">
         <v>8600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>44400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>30300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>13300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-6700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>50600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>17300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-7800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>17500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>44500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>2500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>9400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-4700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>29300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>11600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>4600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>8700</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>12500</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>13000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-5800</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-22900</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>53800</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>52500</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-22200</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-29100</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>106100</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>57700</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-1600</v>
       </c>
     </row>
-    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7262,97 +7482,101 @@
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
-    </row>
-    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF90" s="3"/>
+    </row>
+    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-5700</v>
+      </c>
+      <c r="E91" s="3">
         <v>-5900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-6400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-2000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-2600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1600</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-2300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-2900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-3000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1400</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-2100</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1500</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-3300</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-2500</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-3900</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-3700</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-1900</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-2700</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-2300</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-3800</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-3200</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-14900</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-8100</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-11100</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-4600</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-11000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-6200</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-4600</v>
       </c>
     </row>
-    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7440,8 +7664,11 @@
       <c r="AE92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7529,97 +7756,103 @@
       <c r="AE93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-5700</v>
+      </c>
+      <c r="E94" s="3">
         <v>-33100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-6400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-3100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-2600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>19100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-2900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-2300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-2500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-3200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-2500</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>20800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-3200</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-1900</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>100</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-600</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-36800</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>213300</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>11000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-6800</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>28200</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-7700</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-62800</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-11900</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-12300</v>
       </c>
     </row>
-    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7651,17 +7884,18 @@
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
-    </row>
-    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF95" s="3"/>
+    </row>
+    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>0</v>
+      </c>
+      <c r="E96" s="3">
         <v>2200</v>
       </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
       <c r="F96" s="3">
         <v>0</v>
       </c>
@@ -7669,11 +7903,11 @@
         <v>0</v>
       </c>
       <c r="H96" s="3">
+        <v>0</v>
+      </c>
+      <c r="I96" s="3">
         <v>2200</v>
       </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
       <c r="J96" s="3">
         <v>0</v>
       </c>
@@ -7681,11 +7915,11 @@
         <v>0</v>
       </c>
       <c r="L96" s="3">
+        <v>0</v>
+      </c>
+      <c r="M96" s="3">
         <v>-2300</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
-      </c>
       <c r="N96" s="3">
         <v>0</v>
       </c>
@@ -7693,11 +7927,11 @@
         <v>0</v>
       </c>
       <c r="P96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="3">
         <v>-2400</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
-      </c>
       <c r="R96" s="3">
         <v>0</v>
       </c>
@@ -7705,11 +7939,11 @@
         <v>0</v>
       </c>
       <c r="T96" s="3">
+        <v>0</v>
+      </c>
+      <c r="U96" s="3">
         <v>-2400</v>
       </c>
-      <c r="U96" s="3">
-        <v>0</v>
-      </c>
       <c r="V96" s="3">
         <v>0</v>
       </c>
@@ -7717,31 +7951,34 @@
         <v>0</v>
       </c>
       <c r="X96" s="3">
-        <v>-2400</v>
+        <v>0</v>
       </c>
       <c r="Y96" s="3">
         <v>-2400</v>
       </c>
       <c r="Z96" s="3">
-        <v>0</v>
+        <v>-2400</v>
       </c>
       <c r="AA96" s="3">
         <v>0</v>
       </c>
       <c r="AB96" s="3">
-        <v>-2400</v>
+        <v>0</v>
       </c>
       <c r="AC96" s="3">
         <v>-2400</v>
       </c>
       <c r="AD96" s="3">
-        <v>0</v>
+        <v>-2400</v>
       </c>
       <c r="AE96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7829,8 +8066,11 @@
       <c r="AE97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7918,8 +8158,11 @@
       <c r="AE98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8007,271 +8250,283 @@
       <c r="AE99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-12300</v>
+      </c>
+      <c r="E100" s="3">
         <v>-12800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-4900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-49700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-4100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>2300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-57500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>4500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>5500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-5700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-40300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-6200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-1900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-3700</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-19800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-13200</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-46600</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-1800</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-32500</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-10000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-1200</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-195200</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-99500</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-12100</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-40800</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-9600</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-18000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-7500</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E101" s="3">
         <v>500</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>200</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-1500</v>
       </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
       <c r="H101" s="3">
+        <v>0</v>
+      </c>
+      <c r="I101" s="3">
         <v>-800</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-5800</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-4900</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>900</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-800</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-5800</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-4900</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>900</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-2200</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-2900</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>1800</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>1900</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>1400</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>8400</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-2200</v>
-      </c>
-      <c r="W101" s="3">
-        <v>400</v>
       </c>
       <c r="X101" s="3">
         <v>400</v>
       </c>
       <c r="Y101" s="3">
+        <v>400</v>
+      </c>
+      <c r="Z101" s="3">
         <v>-4700</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-2700</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>1800</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-700</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-4400</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-2300</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>2700</v>
       </c>
     </row>
-    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-11200</v>
+      </c>
+      <c r="E102" s="3">
         <v>-36400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>34700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-21300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>5700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-6500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>12400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>17300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-4600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>8500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-3000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-9700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>6900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-13800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>4100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>21000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-43300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>6400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-11400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>200</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-43300</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-4400</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-39300</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>30900</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-33100</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-47000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>20900</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>35900</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-11500</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/EPAC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/EPAC_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="92">
   <si>
     <t>EPAC</t>
   </si>
@@ -656,416 +656,429 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45808</v>
+      </c>
+      <c r="E7" s="2">
         <v>45716</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45626</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45535</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45443</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45351</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45260</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45169</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45077</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44985</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44895</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44804</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44712</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44620</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44530</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44439</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44347</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44255</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44165</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44074</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43982</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43890</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43799</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43708</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43616</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43524</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43434</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43343</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43251</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43159</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>158700</v>
+      </c>
+      <c r="E8" s="3">
         <v>145500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>145200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>158700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>150400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>138400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>142000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>160600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>156300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>142000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>139400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>151800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>151900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>136600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>130900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>145400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>143100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>120700</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>119400</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>111400</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>101900</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>133400</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>146700</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>654800</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>178100</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>159800</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>158600</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>641300</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>317100</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>275200</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>78800</v>
+      </c>
+      <c r="E9" s="3">
         <v>72100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>70500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>81300</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>71900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>66800</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>67600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>81400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>78000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>71400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>71500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>78100</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>79800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>76600</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>71300</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>79200</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>76300</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>65900</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>64200</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>66900</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>59900</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>71300</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>78000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>362100</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>96100</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>88500</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>88200</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>358000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>200600</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>185500</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>79900</v>
+      </c>
+      <c r="E10" s="3">
         <v>73400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>74700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>77400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>78500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>71700</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>74400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>79200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>78300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>70600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>67900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>73700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>72100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>60000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>59600</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>66200</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>66800</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>54800</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>55200</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>44500</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>42000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>62100</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>68700</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>292700</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>82000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>71300</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>70400</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>283300</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>116500</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>89700</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1098,8 +1111,9 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1109,11 +1123,11 @@
       <c r="E12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F12" s="3">
+      <c r="F12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G12" s="3">
         <v>12400</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>8</v>
@@ -1121,11 +1135,11 @@
       <c r="I12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J12" s="3">
+      <c r="J12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K12" s="3">
         <v>9000</v>
-      </c>
-      <c r="K12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="L12" s="3" t="s">
         <v>8</v>
@@ -1190,8 +1204,11 @@
       <c r="AF12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1282,100 +1299,106 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>8</v>
+      <c r="D14" s="3">
+        <v>5900</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F14" s="3">
+      <c r="F14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G14" s="3">
         <v>7200</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>3700</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>2000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>3700</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>3400</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>8200</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>14400</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>10400</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>4300</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>500</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>2900</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>2700</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>5600</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>-3800</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>1100</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>300</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>1400</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>1000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>1200</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>600</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>27000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>-11900</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>3600</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>23400</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>13500</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>1200</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>6400</v>
       </c>
     </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1386,7 +1409,7 @@
         <v>1200</v>
       </c>
       <c r="F15" s="3">
-        <v>800</v>
+        <v>1200</v>
       </c>
       <c r="G15" s="3">
         <v>800</v>
@@ -1398,34 +1421,34 @@
         <v>800</v>
       </c>
       <c r="J15" s="3">
+        <v>800</v>
+      </c>
+      <c r="K15" s="3">
         <v>1000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>1400</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>1300</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>1400</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>1600</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>1800</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>1900</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>2000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>1800</v>
-      </c>
-      <c r="S15" s="3">
-        <v>2100</v>
       </c>
       <c r="T15" s="3">
         <v>2100</v>
@@ -1434,40 +1457,43 @@
         <v>2100</v>
       </c>
       <c r="V15" s="3">
-        <v>2200</v>
+        <v>2100</v>
       </c>
       <c r="W15" s="3">
         <v>2200</v>
       </c>
       <c r="X15" s="3">
+        <v>2200</v>
+      </c>
+      <c r="Y15" s="3">
         <v>2100</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>1900</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>8900</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>2800</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>1900</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>2300</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>9300</v>
-      </c>
-      <c r="AE15" s="3">
-        <v>5200</v>
       </c>
       <c r="AF15" s="3">
         <v>5200</v>
       </c>
-    </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG15" s="3">
+        <v>5200</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1497,192 +1523,199 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>121100</v>
+      </c>
+      <c r="E17" s="3">
         <v>114700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>114100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>122400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>113300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>106900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>109600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>125900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>122700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>113600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>127100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>138700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>145300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>132100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>124500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>131800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>120400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>114900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>110400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>108100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>103900</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>124800</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>132300</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>607200</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>139900</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>147300</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>167100</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>591100</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>284400</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>265400</v>
       </c>
     </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>37500</v>
+      </c>
+      <c r="E18" s="3">
         <v>30800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>31100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>36300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>37100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>31500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>32400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>34700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>33600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>28400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>12300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>13100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>6600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>4500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>6400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>13600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>22700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>5800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>9000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>3300</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-2000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>8600</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>14400</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>47600</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>38200</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>12500</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-8500</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>50200</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>32700</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>9800</v>
       </c>
     </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1715,16 +1748,17 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>900</v>
+      </c>
+      <c r="E20" s="3">
         <v>800</v>
-      </c>
-      <c r="E20" s="3">
-        <v>500</v>
       </c>
       <c r="F20" s="3">
         <v>500</v>
@@ -1736,171 +1770,177 @@
         <v>500</v>
       </c>
       <c r="I20" s="3">
+        <v>500</v>
+      </c>
+      <c r="J20" s="3">
         <v>1000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>700</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>700</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-3500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-3000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-1200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-1400</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-1100</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-1800</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-2200</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-2000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-2200</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-3400</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-3900</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-7100</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-28800</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-6400</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-7700</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-7900</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-31000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-7700</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-8200</v>
       </c>
     </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>37800</v>
+      </c>
+      <c r="E21" s="3">
         <v>31300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>31800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>36700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>37300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>31800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>32200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>35100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>34400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>29000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>13000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>14700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>10300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>8400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>10100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>17600</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>26300</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>9100</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>12500</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>6500</v>
       </c>
-      <c r="W21" s="3">
-        <v>0</v>
-      </c>
       <c r="X21" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y21" s="3">
         <v>10000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>12100</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>38900</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>41100</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>16100</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-11300</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>39600</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>35400</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>11900</v>
       </c>
     </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1908,32 +1948,32 @@
         <v>2400</v>
       </c>
       <c r="E22" s="3">
+        <v>2400</v>
+      </c>
+      <c r="F22" s="3">
         <v>2800</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>4300</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>3400</v>
-      </c>
-      <c r="H22" s="3">
-        <v>3700</v>
       </c>
       <c r="I22" s="3">
         <v>3700</v>
       </c>
       <c r="J22" s="3">
+        <v>3700</v>
+      </c>
+      <c r="K22" s="3">
         <v>4900</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>3300</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>3100</v>
       </c>
-      <c r="M22" s="3">
-        <v>0</v>
-      </c>
       <c r="N22" s="3">
         <v>0</v>
       </c>
@@ -1991,192 +2031,201 @@
       <c r="AF22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>28300</v>
+      </c>
+      <c r="E23" s="3">
         <v>27700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>27900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>26800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>29400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>25300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>24000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>28300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>21700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>10100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>8800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>10100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>5400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>3500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>5000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>12400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>20900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>3600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>7100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>1100</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-5300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>4700</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>7300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>18700</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>31800</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>4800</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-16400</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>19200</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>25000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>6300</v>
+      </c>
+      <c r="E24" s="3">
         <v>6800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>6200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>3400</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>6800</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>7400</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>5700</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>5200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>4700</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>3000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>2400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>1400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>1300</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>1800</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-100</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-4400</v>
       </c>
-      <c r="T24" s="3">
-        <v>0</v>
-      </c>
       <c r="U24" s="3">
+        <v>0</v>
+      </c>
+      <c r="V24" s="3">
         <v>2300</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>3900</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-400</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>800</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>1000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>16500</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>5000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>4000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>100</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>14500</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>-4000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>19800</v>
       </c>
     </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2267,192 +2316,201 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>22000</v>
+      </c>
+      <c r="E26" s="3">
         <v>20900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>21700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>23400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>22600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>17900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>18300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>23100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>17000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>7200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>6400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>10200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>4100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>2100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>3200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>12500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>25300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>3600</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>4800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-2800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-4900</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>3900</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>6400</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>2300</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>26900</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>800</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-16400</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>4700</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>29000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-18200</v>
       </c>
     </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>22000</v>
+      </c>
+      <c r="E27" s="3">
         <v>20900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>21700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>24400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>25800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>17800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>17700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>22200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>12400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>4500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>6400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>10200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>4100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>2100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>3200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>12500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>25300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>3600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>4800</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-2800</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-4900</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>3900</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>6400</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>2300</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>26900</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>800</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-16400</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>4700</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>29000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-18200</v>
       </c>
     </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2543,8 +2601,11 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2555,88 +2616,91 @@
         <v>0</v>
       </c>
       <c r="F29" s="3">
+        <v>0</v>
+      </c>
+      <c r="G29" s="3">
         <v>1000</v>
       </c>
-      <c r="G29" s="3">
+      <c r="H29" s="3">
         <v>3200</v>
       </c>
-      <c r="H29" s="3">
+      <c r="I29" s="3">
         <v>-100</v>
       </c>
-      <c r="I29" s="3">
+      <c r="J29" s="3">
         <v>-600</v>
       </c>
-      <c r="J29" s="3">
+      <c r="K29" s="3">
         <v>-900</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>-4600</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>-2700</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>1000</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>-200</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>-2400</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>-900</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>-400</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <v>-7300</v>
       </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
         <v>-200</v>
       </c>
-      <c r="T29" s="3">
+      <c r="U29" s="3">
         <v>-400</v>
       </c>
-      <c r="U29" s="3">
+      <c r="V29" s="3">
         <v>-200</v>
       </c>
-      <c r="V29" s="3">
+      <c r="W29" s="3">
         <v>4200</v>
       </c>
-      <c r="W29" s="3">
+      <c r="X29" s="3">
         <v>-100</v>
       </c>
-      <c r="X29" s="3">
+      <c r="Y29" s="3">
         <v>-1800</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Z29" s="3">
         <v>-4300</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="AA29" s="3">
         <v>-251400</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AB29" s="3">
         <v>5600</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AC29" s="3">
         <v>2000</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AD29" s="3">
         <v>-1000</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AE29" s="3">
         <v>-31400</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AF29" s="3">
         <v>12900</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AG29" s="3">
         <v>-8400</v>
       </c>
     </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2727,8 +2791,11 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2819,16 +2886,19 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E32" s="3">
         <v>-800</v>
-      </c>
-      <c r="E32" s="3">
-        <v>-500</v>
       </c>
       <c r="F32" s="3">
         <v>-500</v>
@@ -2840,171 +2910,177 @@
         <v>-500</v>
       </c>
       <c r="I32" s="3">
+        <v>-500</v>
+      </c>
+      <c r="J32" s="3">
         <v>-1000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-700</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-700</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>3500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>3000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>1200</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>1000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>1400</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>1100</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>1800</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>2200</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>2000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>2200</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>3400</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>3900</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>7100</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>28800</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>6400</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>7700</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>7900</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>31000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>7700</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>8200</v>
       </c>
     </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>22000</v>
+      </c>
+      <c r="E33" s="3">
         <v>20900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>21700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>24400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>25800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>17800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>17700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>22200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>12400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>4500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>7500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>10000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>1200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>2800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>5300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>25000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>3200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>4600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>1400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-5000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>2200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>2100</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-249100</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>32400</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>2800</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-17500</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-26600</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>41900</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-26600</v>
       </c>
     </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3095,197 +3171,206 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>22000</v>
+      </c>
+      <c r="E35" s="3">
         <v>20900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>21700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>24400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>25800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>17800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>17700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>22200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>12400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>4500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>7500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>10000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>1200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>2800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>5300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>25000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>3200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>4600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>1400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-5000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>2200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>2100</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-249100</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>32400</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>2800</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-17500</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-26600</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>41900</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-26600</v>
       </c>
     </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45808</v>
+      </c>
+      <c r="E38" s="2">
         <v>45716</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45626</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45535</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45443</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45351</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45260</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45169</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45077</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44985</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44895</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44804</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44712</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44620</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44530</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44439</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44347</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44255</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44165</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44074</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43982</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43890</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43799</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43708</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43616</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43524</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43434</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43343</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43251</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43159</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3318,8 +3403,9 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3352,100 +3438,104 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>140500</v>
+      </c>
+      <c r="E41" s="3">
         <v>119500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>130700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>167100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>132400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>153700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>148000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>154400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>142000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>124700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>129200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>120700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>123700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>133400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>126500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>140400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>136300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>115300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>158600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>152200</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>163600</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>163400</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>206800</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>211200</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>201300</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>170400</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>203400</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>250500</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>189500</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>153600</v>
       </c>
     </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3536,376 +3626,391 @@
       <c r="AF42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>119900</v>
+      </c>
+      <c r="E43" s="3">
         <v>115000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>107400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>108900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>113500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>102100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>101400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>101600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>106600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>101800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>99100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>109100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>120800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>116400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>114700</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>111800</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>119600</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>102700</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>95600</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>90300</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>98400</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>118500</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>127000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>125900</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>202800</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>210200</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>191200</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>123300</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>212300</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>210700</v>
       </c>
     </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>87400</v>
+      </c>
+      <c r="E44" s="3">
         <v>80400</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>81200</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>72900</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>79100</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>82900</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>80100</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>74800</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>93000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>94200</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>90700</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>83700</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>86900</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>89500</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>83600</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>75300</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>74700</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>71800</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>70700</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>69200</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>78900</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>78000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>79500</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>77200</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>167600</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>161600</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>154800</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>72000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>167300</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>166200</v>
       </c>
     </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>34800</v>
+      </c>
+      <c r="E45" s="3">
         <v>34500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>30400</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>23400</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>22900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>28700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>30500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>24800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>31800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>34600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>33700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>28900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>34900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>34700</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>36200</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>30000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>41200</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>35700</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>32900</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>29500</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>39000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>38200</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>39500</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>316100</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>44500</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>111000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>157900</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>625000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>58700</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>60600</v>
       </c>
     </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>382600</v>
+      </c>
+      <c r="E46" s="3">
         <v>349400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>349800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>372300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>347800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>367300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>360000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>355600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>373400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>355300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>352700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>342400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>366300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>374100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>361100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>357400</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>371800</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>325400</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>357800</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>341100</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>379800</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>398200</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>452700</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>730300</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>616200</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>653200</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>707300</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>1047200</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>627800</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>591000</v>
       </c>
     </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3936,8 +4041,8 @@
       <c r="L47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
+      <c r="M47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N47" s="3">
         <v>0</v>
@@ -3996,192 +4101,201 @@
       <c r="AF47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>52900</v>
+      </c>
+      <c r="E48" s="3">
         <v>49000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>45800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>73200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>36200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>37000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>38000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>76700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>41800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>41200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>41800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>84600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>44400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>46500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>47700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>100200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>50100</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>61300</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>60200</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>110100</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>111600</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>116600</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>111700</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>56700</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>90000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>83100</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>79200</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>145200</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>100800</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>102400</v>
       </c>
     </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>335900</v>
+      </c>
+      <c r="E49" s="3">
         <v>323900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>322000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>305700</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>303100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>303000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>304300</v>
-      </c>
-      <c r="J49" s="3">
-        <v>303800</v>
       </c>
       <c r="K49" s="3">
         <v>303800</v>
       </c>
       <c r="L49" s="3">
+        <v>303800</v>
+      </c>
+      <c r="M49" s="3">
         <v>301900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>302700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>299500</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>312400</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>322000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>324700</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>332100</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>344600</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>343700</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>341100</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>343500</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>334000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>338300</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>315200</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>312800</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>649700</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>630200</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>630100</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>351800</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>749000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>762500</v>
       </c>
     </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4272,8 +4386,11 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4364,100 +4481,106 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>56700</v>
+      </c>
+      <c r="E52" s="3">
         <v>54300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>57800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>11500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>62400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>62000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>63400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>10700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>74100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>74800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>77300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>30800</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>74200</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>78900</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>79000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>30500</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>76200</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>78600</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>79500</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>29500</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>26100</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>26200</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>28900</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>24400</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>37300</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>36500</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>33500</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>31200</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>27200</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>24300</v>
       </c>
     </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4548,100 +4671,106 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>828100</v>
+      </c>
+      <c r="E54" s="3">
         <v>776600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>775400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>777300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>749500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>769300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>765600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>762600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>793100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>773200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>774400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>757300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>797300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>821500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>812500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>820200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>842700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>809000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>838600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>824300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>851500</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>879300</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>908500</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1124300</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1393200</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1403100</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>1450000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>1485200</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>1504800</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>1480300</v>
       </c>
     </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4674,8 +4803,9 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4708,138 +4838,142 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>45700</v>
+      </c>
+      <c r="E57" s="3">
         <v>43900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>46900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>43400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>41700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>44000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>45500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>50500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>47200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>54300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>74700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>72500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>65700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>66400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>63500</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>62000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>59900</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>49700</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>47000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>45100</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>52100</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>62300</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>68800</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>76900</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>126100</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>122500</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>124100</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>69600</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>142200</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>136900</v>
       </c>
     </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>5000</v>
+        <v>6300</v>
       </c>
       <c r="E58" s="3">
         <v>5000</v>
       </c>
       <c r="F58" s="3">
+        <v>5000</v>
+      </c>
+      <c r="G58" s="3">
         <v>14500</v>
-      </c>
-      <c r="G58" s="3">
-        <v>5000</v>
       </c>
       <c r="H58" s="3">
         <v>5000</v>
       </c>
       <c r="I58" s="3">
+        <v>5000</v>
+      </c>
+      <c r="J58" s="3">
         <v>4400</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>13500</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>3100</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>2500</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1900</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>4000</v>
-      </c>
-      <c r="O58" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="P58" s="3" t="s">
         <v>8</v>
@@ -4856,8 +4990,8 @@
       <c r="T58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U58" s="3">
-        <v>0</v>
+      <c r="U58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="V58" s="3">
         <v>0</v>
@@ -4872,13 +5006,13 @@
         <v>0</v>
       </c>
       <c r="Z58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA58" s="3">
         <v>7500</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>6300</v>
-      </c>
-      <c r="AB58" s="3">
-        <v>30000</v>
       </c>
       <c r="AC58" s="3">
         <v>30000</v>
@@ -4892,233 +5026,242 @@
       <c r="AF58" s="3">
         <v>30000</v>
       </c>
-    </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG58" s="3">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>52400</v>
+      </c>
+      <c r="E59" s="3">
         <v>46000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>49600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>45700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>51000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>48700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>55300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>50900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>61400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>62400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>77600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>76700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>68800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>73900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>68200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>72800</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>74500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>65500</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>62800</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>60500</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>70400</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>67300</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>88500</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>216000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>101200</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>125600</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>178300</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>298600</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>129100</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>107600</v>
       </c>
     </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>132000</v>
+      </c>
+      <c r="E60" s="3">
         <v>114000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>119900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>129400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>122000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>118100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>127000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>148100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>140200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>143400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>154100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>153200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>134500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>140300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>131600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>134800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>134400</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>115300</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>109700</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>105500</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>122500</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>129600</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>157300</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>300400</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>233600</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>278100</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>332400</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>354000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>301300</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>274500</v>
       </c>
     </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>184600</v>
+      </c>
+      <c r="E61" s="3">
         <v>187100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>188300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>214700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>190700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>239900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>240100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>239600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>231500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>206800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>200400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>200000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>205000</v>
-      </c>
-      <c r="P61" s="3">
-        <v>175000</v>
       </c>
       <c r="Q61" s="3">
         <v>175000</v>
@@ -5127,141 +5270,147 @@
         <v>175000</v>
       </c>
       <c r="S61" s="3">
+        <v>175000</v>
+      </c>
+      <c r="T61" s="3">
         <v>195000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>210000</v>
-      </c>
-      <c r="U61" s="3">
-        <v>255000</v>
       </c>
       <c r="V61" s="3">
         <v>255000</v>
       </c>
       <c r="W61" s="3">
+        <v>255000</v>
+      </c>
+      <c r="X61" s="3">
         <v>286500</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>286400</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>286200</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>452900</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>469000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>455600</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>495400</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>502700</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>510000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>517300</v>
       </c>
     </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>56800</v>
+      </c>
+      <c r="E62" s="3">
         <v>52500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>53900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>27500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>57500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>57600</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>60600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>32400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>65000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>62000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>85600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>85500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>91500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>93100</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>96000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>98300</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>96300</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>102400</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>105900</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>104500</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>106200</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>109000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>111800</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>69700</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>83200</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>83700</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>84700</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>69800</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>92400</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>99200</v>
       </c>
     </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5352,8 +5501,11 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5444,8 +5596,11 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5536,100 +5691,106 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>389900</v>
+      </c>
+      <c r="E66" s="3">
         <v>370600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>377300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>385300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>383700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>432400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>443900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>436000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>456500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>432400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>440100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>438700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>431000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>408400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>402700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>408000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>425800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>427600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>470600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>465100</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>515300</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>525000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>555300</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>823100</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>785700</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>817400</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>912500</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>926500</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>903800</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>891000</v>
       </c>
     </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5662,8 +5823,9 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5754,8 +5916,11 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5846,8 +6011,11 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5938,8 +6106,11 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6030,100 +6201,106 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>298100</v>
+      </c>
+      <c r="E72" s="3">
         <v>290000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>279200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>261900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>245300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>222000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>1028900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>1011100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>991100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>978700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>974200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>966800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>959000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>957300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>956100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>953300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>950500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>925500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>922300</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>917700</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>918600</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>923600</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>921500</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>915500</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>1184700</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>1152300</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>1149600</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>1167000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>1207100</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>1178000</v>
       </c>
     </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6214,8 +6391,11 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6306,8 +6486,11 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6398,100 +6581,106 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>438200</v>
+      </c>
+      <c r="E76" s="3">
         <v>406000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>398000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>392000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>365800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>336900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>321700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>326600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>336600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>340800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>334300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>318600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>366300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>413000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>409800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>412200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>416900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>381400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>367900</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>359200</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>336300</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>354400</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>353300</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>301200</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>607400</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>585600</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>537600</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>558700</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>601000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>589300</v>
       </c>
     </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6582,197 +6771,206 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45808</v>
+      </c>
+      <c r="E80" s="2">
         <v>45716</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45626</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45535</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45443</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45351</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45260</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45169</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45077</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44985</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44895</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44804</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44712</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44620</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44530</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44439</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44347</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44255</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44165</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44074</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43982</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43890</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43799</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43708</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43616</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43524</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43434</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43343</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43251</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43159</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>22000</v>
+      </c>
+      <c r="E81" s="3">
         <v>20900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>21700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>24400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>25800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>17800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>17700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>22200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>12400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>4500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>7500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>10000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>1200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>2800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>5300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>25000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>3200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>4600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>1400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-5000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>2200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>2100</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-249100</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>32400</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>2800</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-17500</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-26600</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>41900</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-26600</v>
       </c>
     </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6805,58 +7003,59 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E83" s="3">
         <v>2500</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>2600</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>2800</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>2700</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>2900</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>2800</v>
-      </c>
-      <c r="J83" s="3">
-        <v>3000</v>
       </c>
       <c r="K83" s="3">
         <v>3000</v>
       </c>
       <c r="L83" s="3">
+        <v>3000</v>
+      </c>
+      <c r="M83" s="3">
         <v>3100</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>4200</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>4600</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>4800</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>5000</v>
-      </c>
-      <c r="Q83" s="3">
-        <v>5200</v>
       </c>
       <c r="R83" s="3">
         <v>5200</v>
       </c>
       <c r="S83" s="3">
-        <v>5500</v>
+        <v>5200</v>
       </c>
       <c r="T83" s="3">
         <v>5500</v>
@@ -6865,7 +7064,7 @@
         <v>5500</v>
       </c>
       <c r="V83" s="3">
-        <v>5300</v>
+        <v>5500</v>
       </c>
       <c r="W83" s="3">
         <v>5300</v>
@@ -6874,31 +7073,34 @@
         <v>5300</v>
       </c>
       <c r="Y83" s="3">
+        <v>5300</v>
+      </c>
+      <c r="Z83" s="3">
         <v>4800</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>20200</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>9300</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>7500</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>8900</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>40700</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>10400</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>10300</v>
       </c>
     </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6989,8 +7191,11 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7081,8 +7286,11 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7173,8 +7381,11 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7265,8 +7476,11 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7357,100 +7571,106 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>39900</v>
+      </c>
+      <c r="E89" s="3">
         <v>7500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>8600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>44400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>30300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>13300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-6700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>50600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>17300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-7800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>17500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>44500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>2500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>9400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-4700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>29300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>11600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>4600</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>8700</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>12500</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>13000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-5800</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-22900</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>53800</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>52500</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-22200</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-29100</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>106100</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>57700</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-1600</v>
       </c>
     </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7483,100 +7703,104 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-4800</v>
+      </c>
+      <c r="E91" s="3">
         <v>-5700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-5900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-6400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-2000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-2600</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1600</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-2300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-2900</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-3000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-1400</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-2100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-1500</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-3300</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-2500</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-3900</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-3700</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-1900</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-2700</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-2300</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-3800</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-3200</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-14900</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-8100</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-11100</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-4600</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-11000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-6200</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-4600</v>
       </c>
     </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7667,8 +7891,11 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7759,100 +7986,106 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-4400</v>
+      </c>
+      <c r="E94" s="3">
         <v>-5700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-33100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-6400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-3100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-2600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>19100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-2900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-2300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-2500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-1500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-3200</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-2500</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>20800</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-3200</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-1900</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>100</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-600</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-36800</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>213300</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>11000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-6800</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>28200</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-7700</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-62800</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-11900</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-12300</v>
       </c>
     </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7885,8 +8118,9 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7894,11 +8128,11 @@
         <v>0</v>
       </c>
       <c r="E96" s="3">
+        <v>0</v>
+      </c>
+      <c r="F96" s="3">
         <v>2200</v>
       </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
       <c r="G96" s="3">
         <v>0</v>
       </c>
@@ -7906,11 +8140,11 @@
         <v>0</v>
       </c>
       <c r="I96" s="3">
+        <v>0</v>
+      </c>
+      <c r="J96" s="3">
         <v>2200</v>
       </c>
-      <c r="J96" s="3">
-        <v>0</v>
-      </c>
       <c r="K96" s="3">
         <v>0</v>
       </c>
@@ -7918,11 +8152,11 @@
         <v>0</v>
       </c>
       <c r="M96" s="3">
+        <v>0</v>
+      </c>
+      <c r="N96" s="3">
         <v>-2300</v>
       </c>
-      <c r="N96" s="3">
-        <v>0</v>
-      </c>
       <c r="O96" s="3">
         <v>0</v>
       </c>
@@ -7930,11 +8164,11 @@
         <v>0</v>
       </c>
       <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+      <c r="R96" s="3">
         <v>-2400</v>
       </c>
-      <c r="R96" s="3">
-        <v>0</v>
-      </c>
       <c r="S96" s="3">
         <v>0</v>
       </c>
@@ -7942,11 +8176,11 @@
         <v>0</v>
       </c>
       <c r="U96" s="3">
+        <v>0</v>
+      </c>
+      <c r="V96" s="3">
         <v>-2400</v>
       </c>
-      <c r="V96" s="3">
-        <v>0</v>
-      </c>
       <c r="W96" s="3">
         <v>0</v>
       </c>
@@ -7954,31 +8188,34 @@
         <v>0</v>
       </c>
       <c r="Y96" s="3">
-        <v>-2400</v>
+        <v>0</v>
       </c>
       <c r="Z96" s="3">
         <v>-2400</v>
       </c>
       <c r="AA96" s="3">
-        <v>0</v>
+        <v>-2400</v>
       </c>
       <c r="AB96" s="3">
         <v>0</v>
       </c>
       <c r="AC96" s="3">
-        <v>-2400</v>
+        <v>0</v>
       </c>
       <c r="AD96" s="3">
         <v>-2400</v>
       </c>
       <c r="AE96" s="3">
-        <v>0</v>
+        <v>-2400</v>
       </c>
       <c r="AF96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8069,8 +8306,11 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8161,8 +8401,11 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8253,280 +8496,292 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-14900</v>
+      </c>
+      <c r="E100" s="3">
         <v>-12300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-12800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-4900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-49700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-4100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>2300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-57500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>4500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>5500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-5700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-40300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-6200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-1900</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-3700</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-19800</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-13200</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-46600</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-1800</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-32500</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-10000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-1200</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-195200</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-99500</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-12100</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-40800</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-9600</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-18000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-7500</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E101" s="3">
         <v>-400</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>500</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>200</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-1500</v>
       </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
       <c r="I101" s="3">
+        <v>0</v>
+      </c>
+      <c r="J101" s="3">
         <v>-800</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-5800</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-4900</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>900</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-800</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-5800</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-4900</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>900</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-2200</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-2900</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>1800</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>1900</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>1400</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>8400</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-2200</v>
-      </c>
-      <c r="X101" s="3">
-        <v>400</v>
       </c>
       <c r="Y101" s="3">
         <v>400</v>
       </c>
       <c r="Z101" s="3">
+        <v>400</v>
+      </c>
+      <c r="AA101" s="3">
         <v>-4700</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-2700</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>1800</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-700</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-4400</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-2300</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>2700</v>
       </c>
     </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>21000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-11200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-36400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>34700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-21300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>5700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-6500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>12400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>17300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-4600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>8500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-3000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-9700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>6900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-13800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>4100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>21000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-43300</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>6400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-11400</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>200</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-43300</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-4400</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-39300</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>30900</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-33100</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-47000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>20900</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>35900</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-11500</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/EPAC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/EPAC_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="92">
   <si>
     <t>EPAC</t>
   </si>
@@ -656,442 +656,454 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45991</v>
+      </c>
+      <c r="E7" s="2">
         <v>45900</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45808</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45716</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45626</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45535</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45443</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45351</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45260</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45169</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45077</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44985</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44895</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44804</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44712</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44620</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44530</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44439</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44347</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44255</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44165</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44074</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43982</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43890</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43799</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43708</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43616</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43524</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43434</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43343</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43251</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43159</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>144200</v>
+      </c>
+      <c r="E8" s="3">
         <v>167500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>158700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>145500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>145200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>158700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>150400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>138400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>142000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>160600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>156300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>142000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>139400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>151800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>151900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>136600</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>130900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>145400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>143100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>120700</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>119400</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>111400</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>101900</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>133400</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>146700</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>654800</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>178100</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>159800</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>158600</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>641300</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>317100</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>275200</v>
       </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>71000</v>
+      </c>
+      <c r="E9" s="3">
         <v>83700</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>78800</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>72100</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>70500</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>81300</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>71900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>66800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>67600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>81400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>78000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>71400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>71500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>78100</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>79800</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>76600</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>71300</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>79200</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>76300</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>65900</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>64200</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>66900</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>59900</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>71300</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>78000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>362100</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>96100</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>88500</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>88200</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>358000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>200600</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>185500</v>
       </c>
     </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>73200</v>
+      </c>
+      <c r="E10" s="3">
         <v>83800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>79900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>73400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>74700</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>77400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>78500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>71700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>74400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>79200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>78300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>70600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>67900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>73700</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>72100</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>60000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>59600</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>66200</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>66800</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>54800</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>55200</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>44500</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>42000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>62100</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>68700</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>292700</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>82000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>71300</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>70400</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>283300</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>116500</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>89700</v>
       </c>
     </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1126,16 +1138,17 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="3">
+      <c r="D12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E12" s="3">
         <v>14500</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>8</v>
@@ -1143,11 +1156,11 @@
       <c r="G12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H12" s="3">
+      <c r="H12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I12" s="3">
         <v>12400</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>8</v>
@@ -1155,11 +1168,11 @@
       <c r="K12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L12" s="3">
+      <c r="L12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M12" s="3">
         <v>9000</v>
-      </c>
-      <c r="M12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="N12" s="3" t="s">
         <v>8</v>
@@ -1224,8 +1237,11 @@
       <c r="AH12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1322,114 +1338,120 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
         <v>5900</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H14" s="3">
+      <c r="H14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I14" s="3">
         <v>5200</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>3700</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>2000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>3700</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>3400</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>8200</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>14400</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>10400</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>4300</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>500</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>2900</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>2700</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>5600</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>-3800</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>1100</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>300</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>1400</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>1000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>1200</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>600</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>27000</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>-11900</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>3600</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>23400</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>13500</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>1200</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>6400</v>
       </c>
     </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E15" s="3">
         <v>2000</v>
-      </c>
-      <c r="E15" s="3">
-        <v>1200</v>
       </c>
       <c r="F15" s="3">
         <v>1200</v>
@@ -1438,7 +1460,7 @@
         <v>1200</v>
       </c>
       <c r="H15" s="3">
-        <v>800</v>
+        <v>1200</v>
       </c>
       <c r="I15" s="3">
         <v>800</v>
@@ -1450,34 +1472,34 @@
         <v>800</v>
       </c>
       <c r="L15" s="3">
+        <v>800</v>
+      </c>
+      <c r="M15" s="3">
         <v>1000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>1400</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>1300</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>1400</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>1600</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>1800</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>1900</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>2000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>1800</v>
-      </c>
-      <c r="U15" s="3">
-        <v>2100</v>
       </c>
       <c r="V15" s="3">
         <v>2100</v>
@@ -1486,40 +1508,43 @@
         <v>2100</v>
       </c>
       <c r="X15" s="3">
-        <v>2200</v>
+        <v>2100</v>
       </c>
       <c r="Y15" s="3">
         <v>2200</v>
       </c>
       <c r="Z15" s="3">
+        <v>2200</v>
+      </c>
+      <c r="AA15" s="3">
         <v>2100</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>1900</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>8900</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>2800</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>1900</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>2300</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>9300</v>
-      </c>
-      <c r="AG15" s="3">
-        <v>5200</v>
       </c>
       <c r="AH15" s="3">
         <v>5200</v>
       </c>
-    </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI15" s="3">
+        <v>5200</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1551,204 +1576,211 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
-    </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>115700</v>
+      </c>
+      <c r="E17" s="3">
         <v>128300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>121100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>114700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>114100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>124400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>113300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>106900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>109600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>125900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>122700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>113600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>127100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>138700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>145300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>132100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>124500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>131800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>120400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>114900</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>110400</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>108100</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>103900</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>124800</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>132300</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>607200</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>139900</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>147300</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>167100</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>591100</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>284400</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>265400</v>
       </c>
     </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>28500</v>
+      </c>
+      <c r="E18" s="3">
         <v>39200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>37500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>30800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>31100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>34300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>37100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>31500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>32400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>34700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>33600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>28400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>12300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>13100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>6600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>4500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>6400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>13600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>22700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>5800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>9000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>3300</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-2000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>8600</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>14400</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>47600</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>38200</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>12500</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-8500</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>50200</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>32700</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>9800</v>
       </c>
     </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1783,243 +1815,250 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
-    </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>700</v>
+      </c>
+      <c r="E20" s="3">
         <v>12300</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>900</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>800</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>500</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>15600</v>
-      </c>
-      <c r="I20" s="3">
-        <v>500</v>
       </c>
       <c r="J20" s="3">
         <v>500</v>
       </c>
       <c r="K20" s="3">
+        <v>500</v>
+      </c>
+      <c r="L20" s="3">
         <v>1000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>700</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>700</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-3500</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-3000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-1200</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-1000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-1400</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-1100</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-1800</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-2200</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-2000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-2200</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-3400</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-3900</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-7100</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-28800</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-6400</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-7700</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-7900</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-31000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-7700</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-8200</v>
       </c>
     </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>29400</v>
+      </c>
+      <c r="E21" s="3">
         <v>28900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>37800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>31300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>31800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>19500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>37300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>31800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>32200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>35100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>34400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>29000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>13000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>14700</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>10300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>8400</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>10100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>17600</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>26300</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>9100</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>12500</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>6500</v>
       </c>
-      <c r="Y21" s="3">
-        <v>0</v>
-      </c>
       <c r="Z21" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA21" s="3">
         <v>10000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>12100</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>38900</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>41100</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>16100</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>-11300</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>39600</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>35400</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>11900</v>
       </c>
     </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E22" s="3">
         <v>-7500</v>
-      </c>
-      <c r="E22" s="3">
-        <v>2400</v>
       </c>
       <c r="F22" s="3">
         <v>2400</v>
       </c>
       <c r="G22" s="3">
+        <v>2400</v>
+      </c>
+      <c r="H22" s="3">
         <v>2800</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>-10800</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>3400</v>
-      </c>
-      <c r="J22" s="3">
-        <v>3700</v>
       </c>
       <c r="K22" s="3">
         <v>3700</v>
       </c>
       <c r="L22" s="3">
+        <v>3700</v>
+      </c>
+      <c r="M22" s="3">
         <v>4900</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>3300</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>3100</v>
       </c>
-      <c r="O22" s="3">
-        <v>0</v>
-      </c>
       <c r="P22" s="3">
         <v>0</v>
       </c>
@@ -2077,204 +2116,213 @@
       <c r="AH22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>25600</v>
+      </c>
+      <c r="E23" s="3">
         <v>36800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>28300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>27700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>27900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>26800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>29400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>25300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>24000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>28300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>21700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>10100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>8800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>10100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>5400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>3500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>5000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>12400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>20900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>3600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>7100</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>1100</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-5300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>4700</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>7300</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>18700</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>31800</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>4800</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-16400</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>19200</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>25000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>6400</v>
+      </c>
+      <c r="E24" s="3">
         <v>8700</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>6300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>6800</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>6200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>3400</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>6800</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>7400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>5700</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>5200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>4700</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>3000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>2400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>1400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>1300</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>1800</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-100</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-4400</v>
       </c>
-      <c r="V24" s="3">
-        <v>0</v>
-      </c>
       <c r="W24" s="3">
+        <v>0</v>
+      </c>
+      <c r="X24" s="3">
         <v>2300</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>3900</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-400</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>800</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>1000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>16500</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>5000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>4000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>100</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>14500</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>-4000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>19800</v>
       </c>
     </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2371,204 +2419,213 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>19100</v>
+      </c>
+      <c r="E26" s="3">
         <v>28100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>22000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>20900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>21700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>23400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>22600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>17900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>18300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>23100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>17000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>7200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>6400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>10200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>4100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>2100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>3200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>12500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>25300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>3600</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>4800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-2800</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-4900</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>3900</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>6400</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>2300</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>26900</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>800</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-16400</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>4700</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>29000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-18200</v>
       </c>
     </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>19100</v>
+      </c>
+      <c r="E27" s="3">
         <v>28100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>22000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>20900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>21700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>24400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>25800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>17800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>17700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>22200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>12400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>4500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>6400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>10200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>4100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>2100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>3200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>12500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>25300</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>3600</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>4800</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-2800</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-4900</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>3900</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>6400</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>2300</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>26900</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>800</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-16400</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>4700</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>29000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-18200</v>
       </c>
     </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2665,8 +2722,11 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2683,88 +2743,91 @@
         <v>0</v>
       </c>
       <c r="H29" s="3">
+        <v>0</v>
+      </c>
+      <c r="I29" s="3">
         <v>1000</v>
       </c>
-      <c r="I29" s="3">
+      <c r="J29" s="3">
         <v>3200</v>
       </c>
-      <c r="J29" s="3">
+      <c r="K29" s="3">
         <v>-100</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>-600</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>-900</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>-4600</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>-2700</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>1000</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>-200</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>-2400</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <v>-900</v>
       </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
         <v>-400</v>
       </c>
-      <c r="T29" s="3">
+      <c r="U29" s="3">
         <v>-7300</v>
       </c>
-      <c r="U29" s="3">
+      <c r="V29" s="3">
         <v>-200</v>
       </c>
-      <c r="V29" s="3">
+      <c r="W29" s="3">
         <v>-400</v>
       </c>
-      <c r="W29" s="3">
+      <c r="X29" s="3">
         <v>-200</v>
       </c>
-      <c r="X29" s="3">
+      <c r="Y29" s="3">
         <v>4200</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Z29" s="3">
         <v>-100</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="AA29" s="3">
         <v>-1800</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AB29" s="3">
         <v>-4300</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AC29" s="3">
         <v>-251400</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AD29" s="3">
         <v>5600</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AE29" s="3">
         <v>2000</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AF29" s="3">
         <v>-1000</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AG29" s="3">
         <v>-31400</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AH29" s="3">
         <v>12900</v>
       </c>
-      <c r="AH29" s="3">
+      <c r="AI29" s="3">
         <v>-8400</v>
       </c>
     </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2861,8 +2924,11 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2959,204 +3025,213 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E32" s="3">
         <v>-12300</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-900</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-800</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-500</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-15600</v>
-      </c>
-      <c r="I32" s="3">
-        <v>-500</v>
       </c>
       <c r="J32" s="3">
         <v>-500</v>
       </c>
       <c r="K32" s="3">
+        <v>-500</v>
+      </c>
+      <c r="L32" s="3">
         <v>-1000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-700</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-700</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>3500</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>3000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>1200</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>1000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>1400</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>1100</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>1800</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>2200</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>2000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>2200</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>3400</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>3900</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>7100</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>28800</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>6400</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>7700</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>7900</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>31000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>7700</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>8200</v>
       </c>
     </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>19100</v>
+      </c>
+      <c r="E33" s="3">
         <v>28100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>22000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>20900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>21700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>24400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>25800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>17800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>17700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>22200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>12400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>4500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>7500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>10000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>1600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>1200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>2800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>5300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>25000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>3200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>4600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>1400</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-5000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>2200</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>2100</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-249100</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>32400</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>2800</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-17500</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-26600</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>41900</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-26600</v>
       </c>
     </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3253,209 +3328,218 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>19100</v>
+      </c>
+      <c r="E35" s="3">
         <v>28100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>22000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>20900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>21700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>24400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>25800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>17800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>17700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>22200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>12400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>4500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>7500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>10000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>1600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>1200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>2800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>5300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>25000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>3200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>4600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>1400</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-5000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>2200</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>2100</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-249100</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>32400</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>2800</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-17500</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-26600</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>41900</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-26600</v>
       </c>
     </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45991</v>
+      </c>
+      <c r="E38" s="2">
         <v>45900</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45808</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45716</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45626</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45535</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45443</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45351</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45260</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45169</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45077</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44985</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44895</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44804</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44712</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44620</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44530</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44439</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44347</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44255</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44165</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44074</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43982</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43890</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43799</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43708</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43616</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43524</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43434</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43343</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43251</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43159</v>
       </c>
     </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3490,8 +3574,9 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
-    </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3526,106 +3611,110 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
-    </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>139000</v>
+      </c>
+      <c r="E41" s="3">
         <v>151600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>140500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>119500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>130700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>167100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>132400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>153700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>148000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>154400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>142000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>124700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>129200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>120700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>123700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>133400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>126500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>140400</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>136300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>115300</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>158600</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>152200</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>163600</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>163400</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>206800</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>211200</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>201300</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>170400</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>203400</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>250500</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>189500</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>153600</v>
       </c>
     </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3722,400 +3811,415 @@
       <c r="AH42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>110100</v>
+      </c>
+      <c r="E43" s="3">
         <v>117800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>119900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>115000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>107400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>108900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>113500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>102100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>101400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>101600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>106600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>101800</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>99100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>109100</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>120800</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>116400</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>114700</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>111800</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>119600</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>102700</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>95600</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>90300</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>98400</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>118500</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>127000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>125900</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>202800</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>210200</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>191200</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>123300</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>212300</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>210700</v>
       </c>
     </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>90300</v>
+      </c>
+      <c r="E44" s="3">
         <v>78800</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>87400</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>80400</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>81200</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>72900</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>79100</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>82900</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>80100</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>74800</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>93000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>94200</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>90700</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>83700</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>86900</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>89500</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>83600</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>75300</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>74700</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>71800</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>70700</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>69200</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>78900</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>78000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>79500</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>77200</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>167600</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>161600</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>154800</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>72000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>167300</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>166200</v>
       </c>
     </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>33100</v>
+      </c>
+      <c r="E45" s="3">
         <v>27900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>34800</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>34500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>30400</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>23400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>22900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>28700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>30500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>24800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>31800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>34600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>33700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>28900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>34900</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>34700</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>36200</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>30000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>41200</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>35700</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>32900</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>29500</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>39000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>38200</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>39500</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>316100</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>44500</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>111000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>157900</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>625000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>58700</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>60600</v>
       </c>
     </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>372500</v>
+      </c>
+      <c r="E46" s="3">
         <v>376100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>382600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>349400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>349800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>372300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>347800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>367300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>360000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>355600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>373400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>355300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>352700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>342400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>366300</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>374100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>361100</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>357400</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>371800</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>325400</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>357800</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>341100</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>379800</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>398200</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>452700</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>730300</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>616200</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>653200</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>707300</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>1047200</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>627800</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>591000</v>
       </c>
     </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4152,8 +4256,8 @@
       <c r="N47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
+      <c r="O47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P47" s="3">
         <v>0</v>
@@ -4212,204 +4316,213 @@
       <c r="AH47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>52700</v>
+      </c>
+      <c r="E48" s="3">
         <v>88700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>52900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>49000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>45800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>73200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>36200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>37000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>38000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>76700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>41800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>41200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>41800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>84600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>44400</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>46500</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>47700</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>100200</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>50100</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>61300</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>60200</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>110100</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>111600</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>116600</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>111700</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>56700</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>90000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>83100</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>79200</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>145200</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>100800</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>102400</v>
       </c>
     </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>332900</v>
+      </c>
+      <c r="E49" s="3">
         <v>336700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>335900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>323900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>322000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>305700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>303100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>303000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>304300</v>
-      </c>
-      <c r="L49" s="3">
-        <v>303800</v>
       </c>
       <c r="M49" s="3">
         <v>303800</v>
       </c>
       <c r="N49" s="3">
+        <v>303800</v>
+      </c>
+      <c r="O49" s="3">
         <v>301900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>302700</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>299500</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>312400</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>322000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>324700</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>332100</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>344600</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>343700</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>341100</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>343500</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>334000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>338300</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>315200</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>312800</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>649700</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>630200</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>630100</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>351800</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>749000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>762500</v>
       </c>
     </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4506,8 +4619,11 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4604,106 +4720,112 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>59900</v>
+      </c>
+      <c r="E52" s="3">
         <v>12600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>56700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>54300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>57800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>11500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>62400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>62000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>63400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>10700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>74100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>74800</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>77300</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>30800</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>74200</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>78900</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>79000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>30500</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>76200</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>78600</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>79500</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>29500</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>26100</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>26200</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>28900</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>24400</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>37300</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>36500</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>33500</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>31200</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>27200</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>24300</v>
       </c>
     </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4800,106 +4922,112 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>818100</v>
+      </c>
+      <c r="E54" s="3">
         <v>827900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>828100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>776600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>775400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>777300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>749500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>769300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>765600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>762600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>793100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>773200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>774400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>757300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>797300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>821500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>812500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>820200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>842700</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>809000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>838600</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>824300</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>851500</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>879300</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>908500</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1124300</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>1393200</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>1403100</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>1450000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>1485200</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>1504800</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>1480300</v>
       </c>
     </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4934,8 +5062,9 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
-    </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4970,150 +5099,154 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
-    </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>41700</v>
+      </c>
+      <c r="E57" s="3">
         <v>42900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>45700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>43900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>46900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>43400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>41700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>44000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>45500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>50500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>47200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>54300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>74700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>72500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>65700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>66400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>63500</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>62000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>59900</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>49700</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>47000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>45100</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>52100</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>62300</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>68800</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>76900</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>126100</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>122500</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>124100</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>69600</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>142200</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>136900</v>
       </c>
     </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>8800</v>
+      </c>
+      <c r="E58" s="3">
         <v>17400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>6300</v>
-      </c>
-      <c r="F58" s="3">
-        <v>5000</v>
       </c>
       <c r="G58" s="3">
         <v>5000</v>
       </c>
       <c r="H58" s="3">
+        <v>5000</v>
+      </c>
+      <c r="I58" s="3">
         <v>14500</v>
-      </c>
-      <c r="I58" s="3">
-        <v>5000</v>
       </c>
       <c r="J58" s="3">
         <v>5000</v>
       </c>
       <c r="K58" s="3">
+        <v>5000</v>
+      </c>
+      <c r="L58" s="3">
         <v>4400</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>13500</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>3100</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>2500</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1900</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>4000</v>
-      </c>
-      <c r="Q58" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="R58" s="3" t="s">
         <v>8</v>
@@ -5130,8 +5263,8 @@
       <c r="V58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W58" s="3">
-        <v>0</v>
+      <c r="W58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="X58" s="3">
         <v>0</v>
@@ -5146,13 +5279,13 @@
         <v>0</v>
       </c>
       <c r="AB58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC58" s="3">
         <v>7500</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>6300</v>
-      </c>
-      <c r="AD58" s="3">
-        <v>30000</v>
       </c>
       <c r="AE58" s="3">
         <v>30000</v>
@@ -5166,251 +5299,260 @@
       <c r="AH58" s="3">
         <v>30000</v>
       </c>
-    </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI58" s="3">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>59600</v>
+      </c>
+      <c r="E59" s="3">
         <v>48700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>52400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>46000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>49600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>45700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>51000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>48700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>55300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>50900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>61400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>62400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>77600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>76700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>68800</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>73900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>68200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>72800</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>74500</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>65500</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>62800</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>60500</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>70400</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>67300</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>88500</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>216000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>101200</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>125600</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>178300</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>298600</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>129100</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>107600</v>
       </c>
     </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>131800</v>
+      </c>
+      <c r="E60" s="3">
         <v>137100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>132000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>114000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>119900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>129400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>122000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>118100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>127000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>148100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>140200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>143400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>154100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>153200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>134500</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>140300</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>131600</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>134800</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>134400</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>115300</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>109700</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>105500</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>122500</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>129600</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>157300</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>300400</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>233600</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>278100</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>332400</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>354000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>301300</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>274500</v>
       </c>
     </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>179700</v>
+      </c>
+      <c r="E61" s="3">
         <v>210400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>184600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>187100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>188300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>214700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>190700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>239900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>240100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>239600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>231500</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>206800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>200400</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>200000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>205000</v>
-      </c>
-      <c r="R61" s="3">
-        <v>175000</v>
       </c>
       <c r="S61" s="3">
         <v>175000</v>
@@ -5419,147 +5561,153 @@
         <v>175000</v>
       </c>
       <c r="U61" s="3">
+        <v>175000</v>
+      </c>
+      <c r="V61" s="3">
         <v>195000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>210000</v>
-      </c>
-      <c r="W61" s="3">
-        <v>255000</v>
       </c>
       <c r="X61" s="3">
         <v>255000</v>
       </c>
       <c r="Y61" s="3">
+        <v>255000</v>
+      </c>
+      <c r="Z61" s="3">
         <v>286500</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>286400</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>286200</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>452900</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>469000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>455600</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>495400</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>502700</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>510000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>517300</v>
       </c>
     </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>61400</v>
+      </c>
+      <c r="E62" s="3">
         <v>33300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>56800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>52500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>53900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>27500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>57500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>57600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>60600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>32400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>65000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>62000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>85600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>85500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>91500</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>93100</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>96000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>98300</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>96300</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>102400</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>105900</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>104500</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>106200</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>109000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>111800</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>69700</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>83200</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>83700</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>84700</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>69800</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>92400</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>99200</v>
       </c>
     </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5656,8 +5804,11 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5754,8 +5905,11 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5852,106 +6006,112 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>387000</v>
+      </c>
+      <c r="E66" s="3">
         <v>394200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>389900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>370600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>377300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>385300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>383700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>432400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>443900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>436000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>456500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>432400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>440100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>438700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>431000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>408400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>402700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>408000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>425800</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>427600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>470600</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>465100</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>515300</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>525000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>555300</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>823100</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>785700</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>817400</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>912500</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>926500</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>903800</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>891000</v>
       </c>
     </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5986,8 +6146,9 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
-    </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6084,8 +6245,11 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6182,8 +6346,11 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6280,8 +6447,11 @@
       <c r="AH70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6378,106 +6548,112 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>288400</v>
+      </c>
+      <c r="E72" s="3">
         <v>284100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>298100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>290000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>279200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>261900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>245300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>222000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>1028900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>1011100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>991100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>978700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>974200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>966800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>959000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>957300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>956100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>953300</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>950500</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>925500</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>922300</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>917700</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>918600</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>923600</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>921500</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>915500</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>1184700</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>1152300</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>1149600</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>1167000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>1207100</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>1178000</v>
       </c>
     </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6574,8 +6750,11 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6672,8 +6851,11 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6770,106 +6952,112 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>431100</v>
+      </c>
+      <c r="E76" s="3">
         <v>433700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>438200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>406000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>398000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>392000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>365800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>336900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>321700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>326600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>336600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>340800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>334300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>318600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>366300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>413000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>409800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>412200</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>416900</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>381400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>367900</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>359200</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>336300</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>354400</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>353300</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>301200</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>607400</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>585600</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>537600</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>558700</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>601000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>589300</v>
       </c>
     </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6966,209 +7154,218 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45991</v>
+      </c>
+      <c r="E80" s="2">
         <v>45900</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45808</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45716</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45626</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45535</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45443</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45351</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45260</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45169</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45077</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44985</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44895</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44804</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44712</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44620</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44530</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44439</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44347</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44255</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44165</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44074</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43982</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43890</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43799</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43708</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43616</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43524</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43434</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43343</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43251</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43159</v>
       </c>
     </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>19100</v>
+      </c>
+      <c r="E81" s="3">
         <v>28100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>22000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>20900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>21700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>24400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>25800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>17800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>17700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>22200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>12400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>4500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>7500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>10000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>1600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>1200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>2800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>5300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>25000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>3200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>4600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>1400</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-5000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>2200</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>2100</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-249100</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>32400</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>2800</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-17500</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-26600</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>41900</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-26600</v>
       </c>
     </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7203,64 +7400,65 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
-    </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E83" s="3">
         <v>2500</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>2400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>2500</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>2600</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>2800</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>2700</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>2900</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>2800</v>
-      </c>
-      <c r="L83" s="3">
-        <v>3000</v>
       </c>
       <c r="M83" s="3">
         <v>3000</v>
       </c>
       <c r="N83" s="3">
+        <v>3000</v>
+      </c>
+      <c r="O83" s="3">
         <v>3100</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>4200</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>4600</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>4800</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>5000</v>
-      </c>
-      <c r="S83" s="3">
-        <v>5200</v>
       </c>
       <c r="T83" s="3">
         <v>5200</v>
       </c>
       <c r="U83" s="3">
-        <v>5500</v>
+        <v>5200</v>
       </c>
       <c r="V83" s="3">
         <v>5500</v>
@@ -7269,7 +7467,7 @@
         <v>5500</v>
       </c>
       <c r="X83" s="3">
-        <v>5300</v>
+        <v>5500</v>
       </c>
       <c r="Y83" s="3">
         <v>5300</v>
@@ -7278,31 +7476,34 @@
         <v>5300</v>
       </c>
       <c r="AA83" s="3">
+        <v>5300</v>
+      </c>
+      <c r="AB83" s="3">
         <v>4800</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>20200</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>9300</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>7500</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>8900</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>40700</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>10400</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>10300</v>
       </c>
     </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7399,8 +7600,11 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7497,8 +7701,11 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7595,8 +7802,11 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7693,8 +7903,11 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7791,106 +8004,112 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>16000</v>
+      </c>
+      <c r="E89" s="3">
         <v>55300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>39900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>7500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>8600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>44400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>30300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>13300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-6700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>50600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>17300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-7800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>17500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>44500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>2500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>9400</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-4700</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>29300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>11600</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>4600</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>8700</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>12500</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>13000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-5800</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-22900</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>53800</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>52500</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-22200</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-29100</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>106100</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>57700</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>-1600</v>
       </c>
     </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7925,106 +8144,110 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
-    </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="E91" s="3">
         <v>-3000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-4800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-5700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-5900</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-6400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-2000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-2600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1600</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-2300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-2900</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-3000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-2100</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-1500</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-3300</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-2500</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-3900</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-3700</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-1900</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-2700</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-2300</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-3800</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-3200</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-14900</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-8100</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-11100</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-4600</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-11000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-6200</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-4600</v>
       </c>
     </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8121,8 +8344,11 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8219,106 +8445,112 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="E94" s="3">
         <v>-2900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-4400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-5700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-33100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-6400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-3100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-2600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>19100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-2900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-2300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-2500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-1100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-1500</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-3200</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-2500</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>20800</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-3200</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-1900</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>100</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-600</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-36800</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>213300</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>11000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-6800</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>28200</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-7700</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-62800</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-11900</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-12300</v>
       </c>
     </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8353,13 +8585,14 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
-    </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>0</v>
+        <v>2100</v>
       </c>
       <c r="E96" s="3">
         <v>0</v>
@@ -8368,11 +8601,11 @@
         <v>0</v>
       </c>
       <c r="G96" s="3">
+        <v>0</v>
+      </c>
+      <c r="H96" s="3">
         <v>2200</v>
       </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
       <c r="I96" s="3">
         <v>0</v>
       </c>
@@ -8380,11 +8613,11 @@
         <v>0</v>
       </c>
       <c r="K96" s="3">
+        <v>0</v>
+      </c>
+      <c r="L96" s="3">
         <v>2200</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
-      </c>
       <c r="M96" s="3">
         <v>0</v>
       </c>
@@ -8392,11 +8625,11 @@
         <v>0</v>
       </c>
       <c r="O96" s="3">
+        <v>0</v>
+      </c>
+      <c r="P96" s="3">
         <v>-2300</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
-      </c>
       <c r="Q96" s="3">
         <v>0</v>
       </c>
@@ -8404,11 +8637,11 @@
         <v>0</v>
       </c>
       <c r="S96" s="3">
+        <v>0</v>
+      </c>
+      <c r="T96" s="3">
         <v>-2400</v>
       </c>
-      <c r="T96" s="3">
-        <v>0</v>
-      </c>
       <c r="U96" s="3">
         <v>0</v>
       </c>
@@ -8416,11 +8649,11 @@
         <v>0</v>
       </c>
       <c r="W96" s="3">
+        <v>0</v>
+      </c>
+      <c r="X96" s="3">
         <v>-2400</v>
       </c>
-      <c r="X96" s="3">
-        <v>0</v>
-      </c>
       <c r="Y96" s="3">
         <v>0</v>
       </c>
@@ -8428,31 +8661,34 @@
         <v>0</v>
       </c>
       <c r="AA96" s="3">
-        <v>-2400</v>
+        <v>0</v>
       </c>
       <c r="AB96" s="3">
         <v>-2400</v>
       </c>
       <c r="AC96" s="3">
-        <v>0</v>
+        <v>-2400</v>
       </c>
       <c r="AD96" s="3">
         <v>0</v>
       </c>
       <c r="AE96" s="3">
-        <v>-2400</v>
+        <v>0</v>
       </c>
       <c r="AF96" s="3">
         <v>-2400</v>
       </c>
       <c r="AG96" s="3">
-        <v>0</v>
+        <v>-2400</v>
       </c>
       <c r="AH96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8549,8 +8785,11 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8647,8 +8886,11 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8745,298 +8987,310 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-23500</v>
+      </c>
+      <c r="E100" s="3">
         <v>-41500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-14900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-12300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-12800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-4900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-49700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-4100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>2300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-57500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>4500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>5500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-5700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-40300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-6200</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-1900</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-3700</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-19800</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-13200</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-46600</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-1800</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-32500</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-10000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-1200</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-195200</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-99500</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-12100</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-40800</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-9600</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-18000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-7500</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>800</v>
+      </c>
+      <c r="E101" s="3">
         <v>1700</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-200</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-400</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>500</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>200</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-1500</v>
       </c>
-      <c r="J101" s="3">
-        <v>0</v>
-      </c>
       <c r="K101" s="3">
+        <v>0</v>
+      </c>
+      <c r="L101" s="3">
         <v>-800</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-5800</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-4900</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>900</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-800</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-5800</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-4900</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>900</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-2200</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-2900</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>1800</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>1900</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>1400</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>8400</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-2200</v>
-      </c>
-      <c r="Z101" s="3">
-        <v>400</v>
       </c>
       <c r="AA101" s="3">
         <v>400</v>
       </c>
       <c r="AB101" s="3">
+        <v>400</v>
+      </c>
+      <c r="AC101" s="3">
         <v>-4700</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-2700</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>1800</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-700</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-4400</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-2300</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>2700</v>
       </c>
     </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-12500</v>
+      </c>
+      <c r="E102" s="3">
         <v>11100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>21000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-11200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-36400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>34700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-21300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>5700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-6500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>12400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>17300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-4600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>8500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-3000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-9700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>6900</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-13800</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>4100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>21000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-43300</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>6400</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-11400</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>200</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-43300</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-4400</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-39300</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>30900</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-33100</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-47000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>20900</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>35900</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-11500</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/EPAC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/EPAC_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="92">
   <si>
     <t>EPAC</t>
   </si>
@@ -656,454 +656,467 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AI102"/>
+  <dimension ref="A5:AJ102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46081</v>
+      </c>
+      <c r="E7" s="2">
         <v>45991</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45900</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45808</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45716</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45626</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45535</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45443</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45351</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45260</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45169</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45077</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44985</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44895</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44804</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44712</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44620</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44530</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44439</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44347</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44255</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44165</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44074</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43982</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43890</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43799</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43708</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43616</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43524</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43434</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43343</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43251</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43159</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>154800</v>
+      </c>
+      <c r="E8" s="3">
         <v>144200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>167500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>158700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>145500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>145200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>158700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>150400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>138400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>142000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>160600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>156300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>142000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>139400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>151800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>151900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>136600</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>130900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>145400</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>143100</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>120700</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>119400</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>111400</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>101900</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>133400</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>146700</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>654800</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>178100</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>159800</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>158600</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>641300</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>317100</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>275200</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>83000</v>
+      </c>
+      <c r="E9" s="3">
         <v>71000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>83700</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>78800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>72100</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>70500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>81300</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>71900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>66800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>67600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>81400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>78000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>71400</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>71500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>78100</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>79800</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>76600</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>71300</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>79200</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>76300</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>65900</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>64200</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>66900</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>59900</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>71300</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>78000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>362100</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>96100</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>88500</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>88200</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>358000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>200600</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>185500</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>71800</v>
+      </c>
+      <c r="E10" s="3">
         <v>73200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>83800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>79900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>73400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>74700</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>77400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>78500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>71700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>74400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>79200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>78300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>70600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>67900</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>73700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>72100</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>60000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>59600</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>66200</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>66800</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>54800</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>55200</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>44500</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>42000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>62100</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>68700</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>292700</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>82000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>71300</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>70400</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>283300</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>116500</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>89700</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1139,19 +1152,20 @@
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E12" s="3">
+      <c r="E12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" s="3">
         <v>14500</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>8</v>
@@ -1159,11 +1173,11 @@
       <c r="H12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I12" s="3">
+      <c r="I12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J12" s="3">
         <v>12400</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>8</v>
@@ -1171,11 +1185,11 @@
       <c r="L12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M12" s="3">
+      <c r="M12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N12" s="3">
         <v>9000</v>
-      </c>
-      <c r="N12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="O12" s="3" t="s">
         <v>8</v>
@@ -1240,8 +1254,11 @@
       <c r="AI12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1341,120 +1358,126 @@
       <c r="AI13" s="3">
         <v>0</v>
       </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="D14" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
       <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3">
         <v>5900</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I14" s="3">
+      <c r="I14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J14" s="3">
         <v>5200</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>3700</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>2000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>3700</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>3400</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>8200</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>14400</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>10400</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>4300</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>500</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>2900</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>2700</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>5600</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>-3800</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>1100</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>300</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>1400</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>1000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>1200</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>600</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>27000</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>-11900</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>3600</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>23400</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>13500</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>1200</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>6400</v>
       </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E15" s="3">
         <v>1600</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>2000</v>
-      </c>
-      <c r="F15" s="3">
-        <v>1200</v>
       </c>
       <c r="G15" s="3">
         <v>1200</v>
@@ -1463,7 +1486,7 @@
         <v>1200</v>
       </c>
       <c r="I15" s="3">
-        <v>800</v>
+        <v>1200</v>
       </c>
       <c r="J15" s="3">
         <v>800</v>
@@ -1475,34 +1498,34 @@
         <v>800</v>
       </c>
       <c r="M15" s="3">
+        <v>800</v>
+      </c>
+      <c r="N15" s="3">
         <v>1000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>1400</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>1300</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>1400</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>1600</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>1800</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>1900</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>2000</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>1800</v>
-      </c>
-      <c r="V15" s="3">
-        <v>2100</v>
       </c>
       <c r="W15" s="3">
         <v>2100</v>
@@ -1511,40 +1534,43 @@
         <v>2100</v>
       </c>
       <c r="Y15" s="3">
-        <v>2200</v>
+        <v>2100</v>
       </c>
       <c r="Z15" s="3">
         <v>2200</v>
       </c>
       <c r="AA15" s="3">
+        <v>2200</v>
+      </c>
+      <c r="AB15" s="3">
         <v>2100</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>1900</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>8900</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>2800</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>1900</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>2300</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>9300</v>
-      </c>
-      <c r="AH15" s="3">
-        <v>5200</v>
       </c>
       <c r="AI15" s="3">
         <v>5200</v>
       </c>
+      <c r="AJ15" s="3">
+        <v>5200</v>
+      </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1577,210 +1603,217 @@
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
     </row>
-    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>126500</v>
+      </c>
+      <c r="E17" s="3">
         <v>115700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>128300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>121100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>114700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>114100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>124400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>113300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>106900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>109600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>125900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>122700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>113600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>127100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>138700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>145300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>132100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>124500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>131800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>120400</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>114900</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>110400</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>108100</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>103900</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>124800</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>132300</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>607200</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>139900</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>147300</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>167100</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>591100</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>284400</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>265400</v>
       </c>
     </row>
-    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>28300</v>
+      </c>
+      <c r="E18" s="3">
         <v>28500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>39200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>37500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>30800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>31100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>34300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>37100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>31500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>32400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>34700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>33600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>28400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>12300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>13100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>6600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>4500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>6400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>13600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>22700</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>5800</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>9000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>3300</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-2000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>8600</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>14400</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>47600</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>38200</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>12500</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-8500</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>50200</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>32700</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>9800</v>
       </c>
     </row>
-    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1816,252 +1849,259 @@
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
     </row>
-    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>800</v>
+      </c>
+      <c r="E20" s="3">
         <v>700</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>12300</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>900</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>800</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>500</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>15600</v>
-      </c>
-      <c r="J20" s="3">
-        <v>500</v>
       </c>
       <c r="K20" s="3">
         <v>500</v>
       </c>
       <c r="L20" s="3">
+        <v>500</v>
+      </c>
+      <c r="M20" s="3">
         <v>1000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>700</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>500</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>700</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-3500</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-3000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-1200</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-1000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-1400</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-1100</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-1800</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-2200</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-2000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-2200</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-3400</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-3900</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-7100</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-28800</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-6400</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-7700</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-7900</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-31000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-7700</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-8200</v>
       </c>
     </row>
-    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>29000</v>
+      </c>
+      <c r="E21" s="3">
         <v>29400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>28900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>37800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>31300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>31800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>19500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>37300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>31800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>32200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>35100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>34400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>29000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>13000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>14700</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>10300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>8400</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>10100</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>17600</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>26300</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>9100</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>12500</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>6500</v>
       </c>
-      <c r="Z21" s="3">
-        <v>0</v>
-      </c>
       <c r="AA21" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB21" s="3">
         <v>10000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>12100</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>38900</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>41100</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>16100</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>-11300</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>39600</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>35400</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>11900</v>
       </c>
     </row>
-    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E22" s="3">
         <v>2300</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>-7500</v>
-      </c>
-      <c r="F22" s="3">
-        <v>2400</v>
       </c>
       <c r="G22" s="3">
         <v>2400</v>
       </c>
       <c r="H22" s="3">
+        <v>2400</v>
+      </c>
+      <c r="I22" s="3">
         <v>2800</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>-10800</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>3400</v>
-      </c>
-      <c r="K22" s="3">
-        <v>3700</v>
       </c>
       <c r="L22" s="3">
         <v>3700</v>
       </c>
       <c r="M22" s="3">
+        <v>3700</v>
+      </c>
+      <c r="N22" s="3">
         <v>4900</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>3300</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>3100</v>
       </c>
-      <c r="P22" s="3">
-        <v>0</v>
-      </c>
       <c r="Q22" s="3">
         <v>0</v>
       </c>
@@ -2119,210 +2159,219 @@
       <c r="AI22" s="3">
         <v>0</v>
       </c>
+      <c r="AJ22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>22100</v>
+      </c>
+      <c r="E23" s="3">
         <v>25600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>36800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>28300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>27700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>27900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>26800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>29400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>25300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>24000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>28300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>21700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>10100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>8800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>10100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>5400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>3500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>5000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>12400</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>20900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>3600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>7100</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>1100</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-5300</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>4700</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>7300</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>18700</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>31800</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>4800</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-16400</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>19200</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>25000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>5800</v>
+      </c>
+      <c r="E24" s="3">
         <v>6400</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>8700</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>6300</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>6800</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>6200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>3400</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>6800</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>7400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>5700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>5200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>4700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>3000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>2400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-100</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>1400</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>1300</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>1800</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-100</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-4400</v>
       </c>
-      <c r="W24" s="3">
-        <v>0</v>
-      </c>
       <c r="X24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y24" s="3">
         <v>2300</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>3900</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-400</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>800</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>1000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>16500</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>5000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>4000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>100</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>14500</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>-4000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>19800</v>
       </c>
     </row>
-    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2422,210 +2471,219 @@
       <c r="AI25" s="3">
         <v>0</v>
       </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>16300</v>
+      </c>
+      <c r="E26" s="3">
         <v>19100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>28100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>22000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>20900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>21700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>23400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>22600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>17900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>18300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>23100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>17000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>7200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>6400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>10200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>4100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>2100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>3200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>12500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>25300</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>3600</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>4800</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-2800</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-4900</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>3900</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>6400</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>2300</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>26900</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>800</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-16400</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>4700</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>29000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>-18200</v>
       </c>
     </row>
-    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>16300</v>
+      </c>
+      <c r="E27" s="3">
         <v>19100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>28100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>22000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>20900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>21700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>24400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>25800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>17800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>17700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>22200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>12400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>4500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>6400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>10200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>4100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>2100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>3200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>12500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>25300</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>3600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>4800</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-2800</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-4900</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>3900</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>6400</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>2300</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>26900</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>800</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-16400</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>4700</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>29000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>-18200</v>
       </c>
     </row>
-    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2725,8 +2783,11 @@
       <c r="AI28" s="3">
         <v>0</v>
       </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2746,88 +2807,91 @@
         <v>0</v>
       </c>
       <c r="I29" s="3">
+        <v>0</v>
+      </c>
+      <c r="J29" s="3">
         <v>1000</v>
       </c>
-      <c r="J29" s="3">
+      <c r="K29" s="3">
         <v>3200</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>-100</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>-600</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>-900</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>-4600</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>-2700</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>1000</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>-200</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <v>-2400</v>
       </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
         <v>-900</v>
       </c>
-      <c r="T29" s="3">
+      <c r="U29" s="3">
         <v>-400</v>
       </c>
-      <c r="U29" s="3">
+      <c r="V29" s="3">
         <v>-7300</v>
       </c>
-      <c r="V29" s="3">
+      <c r="W29" s="3">
         <v>-200</v>
       </c>
-      <c r="W29" s="3">
+      <c r="X29" s="3">
         <v>-400</v>
       </c>
-      <c r="X29" s="3">
+      <c r="Y29" s="3">
         <v>-200</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Z29" s="3">
         <v>4200</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="AA29" s="3">
         <v>-100</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AB29" s="3">
         <v>-1800</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AC29" s="3">
         <v>-4300</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AD29" s="3">
         <v>-251400</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AE29" s="3">
         <v>5600</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AF29" s="3">
         <v>2000</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AG29" s="3">
         <v>-1000</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AH29" s="3">
         <v>-31400</v>
       </c>
-      <c r="AH29" s="3">
+      <c r="AI29" s="3">
         <v>12900</v>
       </c>
-      <c r="AI29" s="3">
+      <c r="AJ29" s="3">
         <v>-8400</v>
       </c>
     </row>
-    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2927,8 +2991,11 @@
       <c r="AI30" s="3">
         <v>0</v>
       </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3028,210 +3095,219 @@
       <c r="AI31" s="3">
         <v>0</v>
       </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E32" s="3">
         <v>-700</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-12300</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-900</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-800</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-500</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-15600</v>
-      </c>
-      <c r="J32" s="3">
-        <v>-500</v>
       </c>
       <c r="K32" s="3">
         <v>-500</v>
       </c>
       <c r="L32" s="3">
+        <v>-500</v>
+      </c>
+      <c r="M32" s="3">
         <v>-1000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-700</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-500</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-700</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>3500</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>3000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>1200</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>1000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>1400</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>1100</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>1800</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>2200</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>2000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>2200</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>3400</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>3900</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>7100</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>28800</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>6400</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>7700</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>7900</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>31000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>7700</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>8200</v>
       </c>
     </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>16300</v>
+      </c>
+      <c r="E33" s="3">
         <v>19100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>28100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>22000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>20900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>21700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>24400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>25800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>17800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>17700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>22200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>12400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>4500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>7500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>10000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>1600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>1200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>2800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>5300</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>25000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>3200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>4600</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>1400</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-5000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>2200</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>2100</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-249100</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>32400</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>2800</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-17500</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-26600</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>41900</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>-26600</v>
       </c>
     </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3331,215 +3407,224 @@
       <c r="AI34" s="3">
         <v>0</v>
       </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>16300</v>
+      </c>
+      <c r="E35" s="3">
         <v>19100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>28100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>22000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>20900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>21700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>24400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>25800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>17800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>17700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>22200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>12400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>4500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>7500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>10000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>1600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>1200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>2800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>5300</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>25000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>3200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>4600</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>1400</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-5000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>2200</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>2100</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-249100</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>32400</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>2800</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-17500</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-26600</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>41900</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>-26600</v>
       </c>
     </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46081</v>
+      </c>
+      <c r="E38" s="2">
         <v>45991</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45900</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45808</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45716</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45626</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45535</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45443</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45351</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45260</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45169</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45077</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44985</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44895</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44804</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44712</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44620</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44530</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44439</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44347</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44255</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44165</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44074</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43982</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43890</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43799</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43708</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43616</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43524</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43434</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43343</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43251</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43159</v>
       </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3575,8 +3660,9 @@
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
     </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3612,109 +3698,113 @@
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>98700</v>
+      </c>
+      <c r="E41" s="3">
         <v>139000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>151600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>140500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>119500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>130700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>167100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>132400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>153700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>148000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>154400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>142000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>124700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>129200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>120700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>123700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>133400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>126500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>140400</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>136300</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>115300</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>158600</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>152200</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>163600</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>163400</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>206800</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>211200</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>201300</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>170400</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>203400</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>250500</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>189500</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>153600</v>
       </c>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3814,210 +3904,219 @@
       <c r="AI42" s="3">
         <v>0</v>
       </c>
+      <c r="AJ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>124700</v>
+      </c>
+      <c r="E43" s="3">
         <v>110100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>117800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>119900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>115000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>107400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>108900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>113500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>102100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>101400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>101600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>106600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>101800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>99100</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>109100</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>120800</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>116400</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>114700</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>111800</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>119600</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>102700</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>95600</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>90300</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>98400</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>118500</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>127000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>125900</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>202800</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>210200</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>191200</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>123300</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>212300</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>210700</v>
       </c>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>92600</v>
+      </c>
+      <c r="E44" s="3">
         <v>90300</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>78800</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>87400</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>80400</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>81200</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>72900</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>79100</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>82900</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>80100</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>74800</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>93000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>94200</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>90700</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>83700</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>86900</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>89500</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>83600</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>75300</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>74700</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>71800</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>70700</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>69200</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>78900</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>78000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>79500</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>77200</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>167600</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>161600</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>154800</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>72000</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>167300</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>166200</v>
       </c>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4025,201 +4124,207 @@
         <v>33100</v>
       </c>
       <c r="E45" s="3">
+        <v>33100</v>
+      </c>
+      <c r="F45" s="3">
         <v>27900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>34800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>34500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>30400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>23400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>22900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>28700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>30500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>24800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>31800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>34600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>33700</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>28900</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>34900</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>34700</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>36200</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>30000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>41200</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>35700</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>32900</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>29500</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>39000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>38200</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>39500</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>316100</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>44500</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>111000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>157900</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>625000</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>58700</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>60600</v>
       </c>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>349100</v>
+      </c>
+      <c r="E46" s="3">
         <v>372500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>376100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>382600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>349400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>349800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>372300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>347800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>367300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>360000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>355600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>373400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>355300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>352700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>342400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>366300</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>374100</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>361100</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>357400</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>371800</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>325400</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>357800</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>341100</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>379800</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>398200</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>452700</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>730300</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>616200</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>653200</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>707300</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>1047200</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>627800</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>591000</v>
       </c>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4259,8 +4364,8 @@
       <c r="O47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P47" s="3">
-        <v>0</v>
+      <c r="P47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q47" s="3">
         <v>0</v>
@@ -4319,210 +4424,219 @@
       <c r="AI47" s="3">
         <v>0</v>
       </c>
+      <c r="AJ47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>53000</v>
+      </c>
+      <c r="E48" s="3">
         <v>52700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>88700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>52900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>49000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>45800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>73200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>36200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>37000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>38000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>76700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>41800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>41200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>41800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>84600</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>44400</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>46500</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>47700</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>100200</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>50100</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>61300</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>60200</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>110100</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>111600</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>116600</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>111700</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>56700</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>90000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>83100</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>79200</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>145200</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>100800</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>102400</v>
       </c>
     </row>
-    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>334900</v>
+      </c>
+      <c r="E49" s="3">
         <v>332900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>336700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>335900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>323900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>322000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>305700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>303100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>303000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>304300</v>
-      </c>
-      <c r="M49" s="3">
-        <v>303800</v>
       </c>
       <c r="N49" s="3">
         <v>303800</v>
       </c>
       <c r="O49" s="3">
+        <v>303800</v>
+      </c>
+      <c r="P49" s="3">
         <v>301900</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>302700</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>299500</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>312400</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>322000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>324700</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>332100</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>344600</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>343700</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>341100</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>343500</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>334000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>338300</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>315200</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>312800</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>649700</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>630200</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>630100</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>351800</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>749000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>762500</v>
       </c>
     </row>
-    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4622,8 +4736,11 @@
       <c r="AI50" s="3">
         <v>0</v>
       </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4723,109 +4840,115 @@
       <c r="AI51" s="3">
         <v>0</v>
       </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>58600</v>
+      </c>
+      <c r="E52" s="3">
         <v>59900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>12600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>56700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>54300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>57800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>11500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>62400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>62000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>63400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>10700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>74100</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>74800</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>77300</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>30800</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>74200</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>78900</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>79000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>30500</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>76200</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>78600</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>79500</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>29500</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>26100</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>26200</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>28900</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>24400</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>37300</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>36500</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>33500</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>31200</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>27200</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>24300</v>
       </c>
     </row>
-    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4925,109 +5048,115 @@
       <c r="AI53" s="3">
         <v>0</v>
       </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>795500</v>
+      </c>
+      <c r="E54" s="3">
         <v>818100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>827900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>828100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>776600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>775400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>777300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>749500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>769300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>765600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>762600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>793100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>773200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>774400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>757300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>797300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>821500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>812500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>820200</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>842700</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>809000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>838600</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>824300</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>851500</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>879300</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>908500</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>1124300</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>1393200</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>1403100</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>1450000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>1485200</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>1504800</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>1480300</v>
       </c>
     </row>
-    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5063,8 +5192,9 @@
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
     </row>
-    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5100,156 +5230,160 @@
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
     </row>
-    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>42300</v>
+      </c>
+      <c r="E57" s="3">
         <v>41700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>42900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>45700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>43900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>46900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>43400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>41700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>44000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>45500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>50500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>47200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>54300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>74700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>72500</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>65700</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>66400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>63500</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>62000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>59900</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>49700</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>47000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>45100</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>52100</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>62300</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>68800</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>76900</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>126100</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>122500</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>124100</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>69600</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>142200</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>136900</v>
       </c>
     </row>
-    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>10000</v>
+      </c>
+      <c r="E58" s="3">
         <v>8800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>17400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>6300</v>
-      </c>
-      <c r="G58" s="3">
-        <v>5000</v>
       </c>
       <c r="H58" s="3">
         <v>5000</v>
       </c>
       <c r="I58" s="3">
+        <v>5000</v>
+      </c>
+      <c r="J58" s="3">
         <v>14500</v>
-      </c>
-      <c r="J58" s="3">
-        <v>5000</v>
       </c>
       <c r="K58" s="3">
         <v>5000</v>
       </c>
       <c r="L58" s="3">
+        <v>5000</v>
+      </c>
+      <c r="M58" s="3">
         <v>4400</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>13500</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>3100</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>2500</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>1900</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>4000</v>
-      </c>
-      <c r="R58" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="S58" s="3" t="s">
         <v>8</v>
@@ -5266,8 +5400,8 @@
       <c r="W58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X58" s="3">
-        <v>0</v>
+      <c r="X58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Y58" s="3">
         <v>0</v>
@@ -5282,13 +5416,13 @@
         <v>0</v>
       </c>
       <c r="AC58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD58" s="3">
         <v>7500</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>6300</v>
-      </c>
-      <c r="AE58" s="3">
-        <v>30000</v>
       </c>
       <c r="AF58" s="3">
         <v>30000</v>
@@ -5302,260 +5436,269 @@
       <c r="AI58" s="3">
         <v>30000</v>
       </c>
+      <c r="AJ58" s="3">
+        <v>30000</v>
+      </c>
     </row>
-    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>65700</v>
+      </c>
+      <c r="E59" s="3">
         <v>59600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>48700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>52400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>46000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>49600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>45700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>51000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>48700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>55300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>50900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>61400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>62400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>77600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>76700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>68800</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>73900</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>68200</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>72800</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>74500</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>65500</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>62800</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>60500</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>70400</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>67300</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>88500</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>216000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>101200</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>125600</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>178300</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>298600</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>129100</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>107600</v>
       </c>
     </row>
-    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>136400</v>
+      </c>
+      <c r="E60" s="3">
         <v>131800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>137100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>132000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>114000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>119900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>129400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>122000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>118100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>127000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>148100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>140200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>143400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>154100</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>153200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>134500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>140300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>131600</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>134800</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>134400</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>115300</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>109700</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>105500</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>122500</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>129600</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>157300</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>300400</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>233600</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>278100</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>332400</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>354000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>301300</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>274500</v>
       </c>
     </row>
-    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>177300</v>
+      </c>
+      <c r="E61" s="3">
         <v>179700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>210400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>184600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>187100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>188300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>214700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>190700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>239900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>240100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>239600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>231500</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>206800</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>200400</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>200000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>205000</v>
-      </c>
-      <c r="S61" s="3">
-        <v>175000</v>
       </c>
       <c r="T61" s="3">
         <v>175000</v>
@@ -5564,150 +5707,156 @@
         <v>175000</v>
       </c>
       <c r="V61" s="3">
+        <v>175000</v>
+      </c>
+      <c r="W61" s="3">
         <v>195000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>210000</v>
-      </c>
-      <c r="X61" s="3">
-        <v>255000</v>
       </c>
       <c r="Y61" s="3">
         <v>255000</v>
       </c>
       <c r="Z61" s="3">
+        <v>255000</v>
+      </c>
+      <c r="AA61" s="3">
         <v>286500</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>286400</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>286200</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>452900</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>469000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>455600</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>495400</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>502700</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>510000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>517300</v>
       </c>
     </row>
-    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>60200</v>
+      </c>
+      <c r="E62" s="3">
         <v>61400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>33300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>56800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>52500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>53900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>27500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>57500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>57600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>60600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>32400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>65000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>62000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>85600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>85500</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>91500</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>93100</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>96000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>98300</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>96300</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>102400</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>105900</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>104500</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>106200</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>109000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>111800</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>69700</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>83200</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>83700</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>84700</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>69800</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>92400</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>99200</v>
       </c>
     </row>
-    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5807,8 +5956,11 @@
       <c r="AI63" s="3">
         <v>0</v>
       </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5908,8 +6060,11 @@
       <c r="AI64" s="3">
         <v>0</v>
       </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6009,109 +6164,115 @@
       <c r="AI65" s="3">
         <v>0</v>
       </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>388000</v>
+      </c>
+      <c r="E66" s="3">
         <v>387000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>394200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>389900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>370600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>377300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>385300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>383700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>432400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>443900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>436000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>456500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>432400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>440100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>438700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>431000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>408400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>402700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>408000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>425800</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>427600</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>470600</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>465100</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>515300</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>525000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>555300</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>823100</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>785700</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>817400</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>912500</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>926500</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>903800</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>891000</v>
       </c>
     </row>
-    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6147,8 +6308,9 @@
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
     </row>
-    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6248,8 +6410,11 @@
       <c r="AI68" s="3">
         <v>0</v>
       </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6349,8 +6514,11 @@
       <c r="AI69" s="3">
         <v>0</v>
       </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6450,8 +6618,11 @@
       <c r="AI70" s="3">
         <v>0</v>
       </c>
+      <c r="AJ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6551,109 +6722,115 @@
       <c r="AI71" s="3">
         <v>0</v>
       </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>253900</v>
+      </c>
+      <c r="E72" s="3">
         <v>288400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>284100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>298100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>290000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>279200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>261900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>245300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>222000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>1028900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>1011100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>991100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>978700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>974200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>966800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>959000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>957300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>956100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>953300</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>950500</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>925500</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>922300</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>917700</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>918600</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>923600</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>921500</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>915500</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>1184700</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>1152300</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>1149600</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>1167000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>1207100</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>1178000</v>
       </c>
     </row>
-    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6753,8 +6930,11 @@
       <c r="AI73" s="3">
         <v>0</v>
       </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6854,8 +7034,11 @@
       <c r="AI74" s="3">
         <v>0</v>
       </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6955,109 +7138,115 @@
       <c r="AI75" s="3">
         <v>0</v>
       </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>407500</v>
+      </c>
+      <c r="E76" s="3">
         <v>431100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>433700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>438200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>406000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>398000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>392000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>365800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>336900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>321700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>326600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>336600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>340800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>334300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>318600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>366300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>413000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>409800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>412200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>416900</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>381400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>367900</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>359200</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>336300</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>354400</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>353300</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>301200</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>607400</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>585600</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>537600</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>558700</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>601000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>589300</v>
       </c>
     </row>
-    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7157,215 +7346,224 @@
       <c r="AI77" s="3">
         <v>0</v>
       </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46081</v>
+      </c>
+      <c r="E80" s="2">
         <v>45991</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45900</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45808</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45716</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45626</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45535</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45443</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45351</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45260</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45169</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45077</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44985</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44895</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44804</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44712</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44620</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44530</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44439</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44347</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44255</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44165</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44074</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43982</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43890</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43799</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43708</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43616</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43524</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43434</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43343</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43251</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43159</v>
       </c>
     </row>
-    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>16300</v>
+      </c>
+      <c r="E81" s="3">
         <v>19100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>28100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>22000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>20900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>21700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>24400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>25800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>17800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>17700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>22200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>12400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>4500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>7500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>10000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>1600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>1200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>2800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>5300</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>25000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>3200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>4600</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>1400</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-5000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>2200</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>2100</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-249100</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>32400</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>2800</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-17500</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-26600</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>41900</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>-26600</v>
       </c>
     </row>
-    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7401,8 +7599,9 @@
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
     </row>
-    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7410,58 +7609,58 @@
         <v>2300</v>
       </c>
       <c r="E83" s="3">
+        <v>2300</v>
+      </c>
+      <c r="F83" s="3">
         <v>2500</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>2400</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>2500</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>2600</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>2800</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>2700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>2900</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>2800</v>
-      </c>
-      <c r="M83" s="3">
-        <v>3000</v>
       </c>
       <c r="N83" s="3">
         <v>3000</v>
       </c>
       <c r="O83" s="3">
+        <v>3000</v>
+      </c>
+      <c r="P83" s="3">
         <v>3100</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>4200</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>4600</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>4800</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>5000</v>
-      </c>
-      <c r="T83" s="3">
-        <v>5200</v>
       </c>
       <c r="U83" s="3">
         <v>5200</v>
       </c>
       <c r="V83" s="3">
-        <v>5500</v>
+        <v>5200</v>
       </c>
       <c r="W83" s="3">
         <v>5500</v>
@@ -7470,7 +7669,7 @@
         <v>5500</v>
       </c>
       <c r="Y83" s="3">
-        <v>5300</v>
+        <v>5500</v>
       </c>
       <c r="Z83" s="3">
         <v>5300</v>
@@ -7479,31 +7678,34 @@
         <v>5300</v>
       </c>
       <c r="AB83" s="3">
+        <v>5300</v>
+      </c>
+      <c r="AC83" s="3">
         <v>4800</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>20200</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>9300</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>7500</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>8900</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>40700</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>10400</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>10300</v>
       </c>
     </row>
-    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7603,8 +7805,11 @@
       <c r="AI84" s="3">
         <v>0</v>
       </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7704,8 +7909,11 @@
       <c r="AI85" s="3">
         <v>0</v>
       </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7805,8 +8013,11 @@
       <c r="AI86" s="3">
         <v>0</v>
       </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7906,8 +8117,11 @@
       <c r="AI87" s="3">
         <v>0</v>
       </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8007,109 +8221,115 @@
       <c r="AI88" s="3">
         <v>0</v>
       </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>13100</v>
+      </c>
+      <c r="E89" s="3">
         <v>16000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>55300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>39900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>7500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>8600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>44400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>30300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>13300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-6700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>50600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>17300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-7800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>17500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>44500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>2500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>9400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-4700</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>29300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>11600</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>4600</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>8700</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>12500</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>13000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-5800</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-22900</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>53800</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>52500</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-22200</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-29100</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>106100</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>57700</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>-1600</v>
       </c>
     </row>
-    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8145,109 +8365,113 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
     </row>
-    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-2700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-3000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-4800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-5700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-5900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-6400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-2000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-2600</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1600</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-2300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-2900</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-3000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-1400</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-2100</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-1500</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-3300</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-2500</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-3900</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-3700</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-1900</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-2700</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-2300</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-3800</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-3200</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-14900</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-8100</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-11100</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-4600</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-11000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-6200</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-4600</v>
       </c>
     </row>
-    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8347,8 +8571,11 @@
       <c r="AI92" s="3">
         <v>0</v>
       </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8448,109 +8675,115 @@
       <c r="AI93" s="3">
         <v>0</v>
       </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-3600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-2900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-4400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-5700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-33100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-6400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-3100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-2600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>19100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-2900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-2300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-2500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-1400</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-1100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-1500</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-3200</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-2500</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>20800</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-3200</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-1900</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>100</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-600</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-36800</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>213300</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>11000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-6800</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>28200</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-7700</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-62800</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-11900</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-12300</v>
       </c>
     </row>
-    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8586,17 +8819,18 @@
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
     </row>
-    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>0</v>
+      </c>
+      <c r="E96" s="3">
         <v>2100</v>
       </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
       <c r="F96" s="3">
         <v>0</v>
       </c>
@@ -8604,11 +8838,11 @@
         <v>0</v>
       </c>
       <c r="H96" s="3">
+        <v>0</v>
+      </c>
+      <c r="I96" s="3">
         <v>2200</v>
       </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
       <c r="J96" s="3">
         <v>0</v>
       </c>
@@ -8616,11 +8850,11 @@
         <v>0</v>
       </c>
       <c r="L96" s="3">
+        <v>0</v>
+      </c>
+      <c r="M96" s="3">
         <v>2200</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
-      </c>
       <c r="N96" s="3">
         <v>0</v>
       </c>
@@ -8628,11 +8862,11 @@
         <v>0</v>
       </c>
       <c r="P96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="3">
         <v>-2300</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
-      </c>
       <c r="R96" s="3">
         <v>0</v>
       </c>
@@ -8640,11 +8874,11 @@
         <v>0</v>
       </c>
       <c r="T96" s="3">
+        <v>0</v>
+      </c>
+      <c r="U96" s="3">
         <v>-2400</v>
       </c>
-      <c r="U96" s="3">
-        <v>0</v>
-      </c>
       <c r="V96" s="3">
         <v>0</v>
       </c>
@@ -8652,11 +8886,11 @@
         <v>0</v>
       </c>
       <c r="X96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y96" s="3">
         <v>-2400</v>
       </c>
-      <c r="Y96" s="3">
-        <v>0</v>
-      </c>
       <c r="Z96" s="3">
         <v>0</v>
       </c>
@@ -8664,31 +8898,34 @@
         <v>0</v>
       </c>
       <c r="AB96" s="3">
-        <v>-2400</v>
+        <v>0</v>
       </c>
       <c r="AC96" s="3">
         <v>-2400</v>
       </c>
       <c r="AD96" s="3">
-        <v>0</v>
+        <v>-2400</v>
       </c>
       <c r="AE96" s="3">
         <v>0</v>
       </c>
       <c r="AF96" s="3">
-        <v>-2400</v>
+        <v>0</v>
       </c>
       <c r="AG96" s="3">
         <v>-2400</v>
       </c>
       <c r="AH96" s="3">
-        <v>0</v>
+        <v>-2400</v>
       </c>
       <c r="AI96" s="3">
         <v>0</v>
       </c>
+      <c r="AJ96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8788,8 +9025,11 @@
       <c r="AI97" s="3">
         <v>0</v>
       </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8889,8 +9129,11 @@
       <c r="AI98" s="3">
         <v>0</v>
       </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8990,307 +9233,319 @@
       <c r="AI99" s="3">
         <v>0</v>
       </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-51800</v>
+      </c>
+      <c r="E100" s="3">
         <v>-23500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-41500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-14900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-12300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-12800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-4900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-49700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-4100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>2300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-57500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>4500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>5500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-5700</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-40300</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-6200</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-1900</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-3700</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-19800</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-13200</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-46600</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-1800</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-32500</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-10000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-1200</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-195200</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-99500</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-12100</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-40800</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-9600</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-18000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-7500</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E101" s="3">
         <v>800</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>1700</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-200</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-400</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>500</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>200</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-1500</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
-      </c>
       <c r="L101" s="3">
+        <v>0</v>
+      </c>
+      <c r="M101" s="3">
         <v>-800</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-5800</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-4900</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>900</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-800</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-5800</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-4900</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>900</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-2200</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-2900</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>1800</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>1900</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>1400</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>8400</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-2200</v>
-      </c>
-      <c r="AA101" s="3">
-        <v>400</v>
       </c>
       <c r="AB101" s="3">
         <v>400</v>
       </c>
       <c r="AC101" s="3">
+        <v>400</v>
+      </c>
+      <c r="AD101" s="3">
         <v>-4700</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-2700</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>1800</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-700</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-4400</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-2300</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>2700</v>
       </c>
     </row>
-    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-40300</v>
+      </c>
+      <c r="E102" s="3">
         <v>-12500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>11100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>21000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-11200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-36400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>34700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-21300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>5700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-6500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>12400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>17300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-4600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>8500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-3000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-9700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>6900</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-13800</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>4100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>21000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-43300</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>6400</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-11400</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>200</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-43300</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-4400</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-39300</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>30900</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-33100</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-47000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>20900</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>35900</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-11500</v>
       </c>
     </row>
